--- a/dune-results/dr_comparison_2026.xlsx
+++ b/dune-results/dr_comparison_2026.xlsx
@@ -402,9 +402,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G58"/>
+  <dimension ref="A1:G60"/>
   <cols>
-    <col min="1" max="1" width="14.83203125" customWidth="1"/>
+    <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="13.83203125" customWidth="1"/>
     <col min="3" max="3" width="13.83203125" customWidth="1"/>
     <col min="4" max="4" width="13.83203125" customWidth="1"/>
@@ -438,91 +438,91 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>-999999</v>
+        <v>0</v>
       </c>
       <c r="B2">
-        <v>17418.88</v>
+        <v>79854.22</v>
       </c>
       <c r="C2">
-        <v>10907.25</v>
+        <v>65755.52</v>
       </c>
       <c r="D2">
-        <v>25305.28</v>
+        <v>73485.07</v>
       </c>
       <c r="E2">
-        <v>18026.83</v>
+        <v>75538.34</v>
       </c>
       <c r="F2">
-        <v>15780.23</v>
+        <v>75621.85</v>
       </c>
       <c r="G2">
-        <v>87438.47</v>
+        <v>370255</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B3">
-        <v>79854.22</v>
+        <v>129628.4</v>
       </c>
       <c r="C3">
-        <v>65755.52</v>
+        <v>96894.31</v>
       </c>
       <c r="D3">
-        <v>73485.07</v>
+        <v>120811.71</v>
       </c>
       <c r="E3">
-        <v>75538.34</v>
+        <v>116182.88</v>
       </c>
       <c r="F3">
-        <v>75621.85</v>
+        <v>129037.41</v>
       </c>
       <c r="G3">
-        <v>370255</v>
+        <v>592554.71</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B4">
-        <v>129628.4</v>
+        <v>0</v>
       </c>
       <c r="C4">
-        <v>96894.31</v>
+        <v>0</v>
       </c>
       <c r="D4">
-        <v>120811.71</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>116182.88</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>129037.41</v>
+        <v>0</v>
       </c>
       <c r="G4">
-        <v>592554.71</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>2</v>
-      </c>
-      <c r="B5">
-        <v>0</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="B5" t="str">
+        <v/>
+      </c>
+      <c r="C5" t="str">
+        <v/>
+      </c>
+      <c r="D5" t="str">
+        <v/>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
       </c>
       <c r="G5">
         <v>0</v>
@@ -530,7 +530,7 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="B6" t="str">
         <v/>
@@ -553,536 +553,536 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>99</v>
+        <v>127</v>
       </c>
       <c r="B7">
-        <v>1602756.97</v>
+        <v>3037.15</v>
       </c>
       <c r="C7">
-        <v>1541979.87</v>
+        <v>2639.18</v>
       </c>
       <c r="D7">
-        <v>1790892.59</v>
+        <v>2167.44</v>
       </c>
       <c r="E7">
-        <v>1722310.47</v>
+        <v>1447.5</v>
       </c>
       <c r="F7">
-        <v>1895178.54</v>
+        <v>730.93</v>
       </c>
       <c r="G7">
-        <v>8553118.44</v>
+        <v>10022.2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>100</v>
-      </c>
-      <c r="B8" t="str">
-        <v/>
-      </c>
-      <c r="C8" t="str">
-        <v/>
-      </c>
-      <c r="D8" t="str">
-        <v/>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
+        <v>128</v>
+      </c>
+      <c r="B8">
+        <v>826847.7</v>
+      </c>
+      <c r="C8">
+        <v>837591.56</v>
+      </c>
+      <c r="D8">
+        <v>1199709.46</v>
+      </c>
+      <c r="E8">
+        <v>1321957.96</v>
+      </c>
+      <c r="F8">
+        <v>1461137.84</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>5647244.52</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B9">
-        <v>3037.15</v>
+        <v>1.03</v>
       </c>
       <c r="C9">
-        <v>2639.18</v>
+        <v>0.52</v>
       </c>
       <c r="D9">
-        <v>2167.44</v>
+        <v>0.67</v>
       </c>
       <c r="E9">
-        <v>1447.5</v>
+        <v>0.77</v>
       </c>
       <c r="F9">
-        <v>730.93</v>
+        <v>1.13</v>
       </c>
       <c r="G9">
-        <v>10022.2</v>
+        <v>4.12</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>128</v>
+        <v>170</v>
       </c>
       <c r="B10">
-        <v>826847.7</v>
+        <v>0</v>
       </c>
       <c r="C10">
-        <v>837591.56</v>
+        <v>0</v>
       </c>
       <c r="D10">
-        <v>1199709.46</v>
+        <v>0</v>
       </c>
       <c r="E10">
-        <v>1321957.96</v>
+        <v>0</v>
       </c>
       <c r="F10">
-        <v>1461137.84</v>
+        <v>0</v>
       </c>
       <c r="G10">
-        <v>5647244.52</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>129</v>
+        <v>171</v>
       </c>
       <c r="B11">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="C11">
-        <v>0.52</v>
+        <v>0</v>
       </c>
       <c r="D11">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="E11">
-        <v>0.77</v>
+        <v>0</v>
       </c>
       <c r="F11">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="G11">
-        <v>4.12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>21333.38</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>13278.93</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>11113.76</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>9912.97</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>11847.6</v>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>67486.64</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B14">
-        <v>0.01</v>
+        <v>467.21</v>
       </c>
       <c r="C14">
-        <v>0.01</v>
+        <v>638.59</v>
       </c>
       <c r="D14">
-        <v>0.01</v>
+        <v>1188.8</v>
       </c>
       <c r="E14">
-        <v>0.01</v>
+        <v>1386.57</v>
       </c>
       <c r="F14">
-        <v>0.01</v>
+        <v>1241.16</v>
       </c>
       <c r="G14">
-        <v>0.05</v>
+        <v>4922.33</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="B15">
-        <v>21333.38</v>
+        <v>475.33</v>
       </c>
       <c r="C15">
-        <v>13278.93</v>
+        <v>108.27</v>
       </c>
       <c r="D15">
-        <v>11113.76</v>
+        <v>7201.39</v>
       </c>
       <c r="E15">
-        <v>9912.97</v>
+        <v>14582.19</v>
       </c>
       <c r="F15">
-        <v>11847.6</v>
+        <v>11608.11</v>
       </c>
       <c r="G15">
-        <v>67486.64</v>
+        <v>33975.29</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B16">
-        <v>467.21</v>
+        <v>10427.71</v>
       </c>
       <c r="C16">
-        <v>638.59</v>
+        <v>5314.13</v>
       </c>
       <c r="D16">
-        <v>1188.8</v>
+        <v>4209.1</v>
       </c>
       <c r="E16">
-        <v>1386.57</v>
+        <v>2912.07</v>
       </c>
       <c r="F16">
-        <v>1241.16</v>
+        <v>2740.89</v>
       </c>
       <c r="G16">
-        <v>4922.33</v>
+        <v>25603.9</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="B17">
-        <v>475.33</v>
+        <v>3326.25</v>
       </c>
       <c r="C17">
-        <v>108.27</v>
+        <v>5352.96</v>
       </c>
       <c r="D17">
-        <v>7201.39</v>
+        <v>8218.73</v>
       </c>
       <c r="E17">
-        <v>14582.19</v>
+        <v>12123.38</v>
       </c>
       <c r="F17">
-        <v>11608.11</v>
+        <v>23241.91</v>
       </c>
       <c r="G17">
-        <v>33975.29</v>
+        <v>52263.23</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B18">
-        <v>10427.71</v>
+        <v>22700.54</v>
       </c>
       <c r="C18">
-        <v>5314.13</v>
+        <v>16725.41</v>
       </c>
       <c r="D18">
-        <v>4209.1</v>
+        <v>19342.47</v>
       </c>
       <c r="E18">
-        <v>2912.07</v>
+        <v>15097.77</v>
       </c>
       <c r="F18">
-        <v>2740.89</v>
+        <v>10576.24</v>
       </c>
       <c r="G18">
-        <v>25603.9</v>
+        <v>84442.43</v>
       </c>
     </row>
     <row r="19">
       <c r="A19">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B19">
-        <v>3326.25</v>
+        <v>1.99</v>
       </c>
       <c r="C19">
-        <v>5352.96</v>
+        <v>1.7</v>
       </c>
       <c r="D19">
-        <v>8218.73</v>
+        <v>1.88</v>
       </c>
       <c r="E19">
-        <v>12123.38</v>
+        <v>1.72</v>
       </c>
       <c r="F19">
-        <v>23241.91</v>
+        <v>1.75</v>
       </c>
       <c r="G19">
-        <v>52263.23</v>
+        <v>9.04</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="B20">
-        <v>22700.54</v>
+        <v>1554.29</v>
       </c>
       <c r="C20">
-        <v>16725.41</v>
+        <v>669.49</v>
       </c>
       <c r="D20">
-        <v>19342.47</v>
+        <v>3049.96</v>
       </c>
       <c r="E20">
-        <v>15097.77</v>
+        <v>1990.3</v>
       </c>
       <c r="F20">
-        <v>10576.24</v>
+        <v>1235.01</v>
       </c>
       <c r="G20">
-        <v>84442.43</v>
+        <v>8499.05</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B21">
-        <v>1.99</v>
+        <v>0.01</v>
       </c>
       <c r="C21">
-        <v>1.7</v>
+        <v>0.09</v>
       </c>
       <c r="D21">
-        <v>1.88</v>
+        <v>0.1</v>
       </c>
       <c r="E21">
-        <v>1.72</v>
+        <v>0.1</v>
       </c>
       <c r="F21">
-        <v>1.75</v>
+        <v>0.1</v>
       </c>
       <c r="G21">
-        <v>9.04</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B22">
-        <v>1554.29</v>
+        <v>6824.99</v>
       </c>
       <c r="C22">
-        <v>669.49</v>
+        <v>6314.15</v>
       </c>
       <c r="D22">
-        <v>3049.96</v>
+        <v>5576.07</v>
       </c>
       <c r="E22">
-        <v>1990.3</v>
+        <v>8508.93</v>
       </c>
       <c r="F22">
-        <v>1235.01</v>
+        <v>10729.88</v>
       </c>
       <c r="G22">
-        <v>8499.05</v>
+        <v>37954.02</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B23">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="C23">
-        <v>0.09</v>
+        <v>0.02</v>
       </c>
       <c r="D23">
+        <v>0.02</v>
+      </c>
+      <c r="E23">
+        <v>0.02</v>
+      </c>
+      <c r="F23">
+        <v>0.02</v>
+      </c>
+      <c r="G23">
         <v>0.1</v>
-      </c>
-      <c r="E23">
-        <v>0.1</v>
-      </c>
-      <c r="F23">
-        <v>0.1</v>
-      </c>
-      <c r="G23">
-        <v>0.4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="B24">
-        <v>6824.99</v>
+        <v>1.96</v>
       </c>
       <c r="C24">
-        <v>6314.15</v>
+        <v>0.65</v>
       </c>
       <c r="D24">
-        <v>5576.07</v>
+        <v>5.79</v>
       </c>
       <c r="E24">
-        <v>8508.93</v>
+        <v>32.59</v>
       </c>
       <c r="F24">
-        <v>10729.88</v>
+        <v>91.6</v>
       </c>
       <c r="G24">
-        <v>37954.02</v>
+        <v>132.59</v>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="B25">
-        <v>0.02</v>
+        <v>28.54</v>
       </c>
       <c r="C25">
-        <v>0.02</v>
+        <v>32.89</v>
       </c>
       <c r="D25">
-        <v>0.02</v>
+        <v>42.56</v>
       </c>
       <c r="E25">
-        <v>0.02</v>
+        <v>39.75</v>
       </c>
       <c r="F25">
-        <v>0.02</v>
+        <v>33.27</v>
       </c>
       <c r="G25">
-        <v>0.1</v>
+        <v>177.01</v>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <v>200</v>
-      </c>
-      <c r="B26">
-        <v>1.96</v>
+        <v>204</v>
+      </c>
+      <c r="B26" t="str">
+        <v/>
       </c>
       <c r="C26">
-        <v>0.65</v>
+        <v>1.61</v>
       </c>
       <c r="D26">
-        <v>5.79</v>
+        <v>16.91</v>
       </c>
       <c r="E26">
-        <v>32.59</v>
+        <v>34.05</v>
       </c>
       <c r="F26">
-        <v>91.6</v>
+        <v>30.45</v>
       </c>
       <c r="G26">
-        <v>132.59</v>
+        <v>83.02</v>
       </c>
     </row>
     <row r="27">
       <c r="A27">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B27">
-        <v>28.54</v>
+        <v>0</v>
       </c>
       <c r="C27">
-        <v>32.89</v>
+        <v>0.02</v>
       </c>
       <c r="D27">
-        <v>42.56</v>
+        <v>0.2</v>
       </c>
       <c r="E27">
-        <v>39.75</v>
+        <v>0.21</v>
       </c>
       <c r="F27">
-        <v>33.27</v>
+        <v>0.21</v>
       </c>
       <c r="G27">
-        <v>177.01</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="28">
       <c r="A28">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B28" t="str">
         <v/>
       </c>
-      <c r="C28">
-        <v>1.61</v>
-      </c>
-      <c r="D28">
-        <v>16.91</v>
-      </c>
-      <c r="E28">
-        <v>34.05</v>
+      <c r="C28" t="str">
+        <v/>
+      </c>
+      <c r="D28" t="str">
+        <v/>
+      </c>
+      <c r="E28" t="str">
+        <v/>
       </c>
       <c r="F28">
-        <v>30.45</v>
+        <v>0</v>
       </c>
       <c r="G28">
-        <v>83.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29">
-        <v>205</v>
-      </c>
-      <c r="B29">
-        <v>0</v>
-      </c>
-      <c r="C29">
-        <v>0.02</v>
-      </c>
-      <c r="D29">
-        <v>0.2</v>
-      </c>
-      <c r="E29">
-        <v>0.21</v>
+        <v>214</v>
+      </c>
+      <c r="B29" t="str">
+        <v/>
+      </c>
+      <c r="C29" t="str">
+        <v/>
+      </c>
+      <c r="D29" t="str">
+        <v/>
+      </c>
+      <c r="E29" t="str">
+        <v/>
       </c>
       <c r="F29">
-        <v>0.21</v>
+        <v>0</v>
       </c>
       <c r="G29">
-        <v>0.64</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="B30" t="str">
         <v/>
@@ -1090,22 +1090,22 @@
       <c r="C30" t="str">
         <v/>
       </c>
-      <c r="D30" t="str">
-        <v/>
-      </c>
-      <c r="E30" t="str">
-        <v/>
+      <c r="D30">
+        <v>86.77</v>
+      </c>
+      <c r="E30">
+        <v>151.21</v>
       </c>
       <c r="F30">
-        <v>0</v>
+        <v>189.04</v>
       </c>
       <c r="G30">
-        <v>0</v>
+        <v>427.02</v>
       </c>
     </row>
     <row r="31">
       <c r="A31">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="B31" t="str">
         <v/>
@@ -1116,19 +1116,19 @@
       <c r="D31" t="str">
         <v/>
       </c>
-      <c r="E31" t="str">
-        <v/>
-      </c>
-      <c r="F31">
-        <v>0</v>
+      <c r="E31">
+        <v>14.26</v>
+      </c>
+      <c r="F31" t="str">
+        <v/>
       </c>
       <c r="G31">
-        <v>0</v>
+        <v>14.26</v>
       </c>
     </row>
     <row r="32">
       <c r="A32">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="B32" t="str">
         <v/>
@@ -1136,22 +1136,22 @@
       <c r="C32" t="str">
         <v/>
       </c>
-      <c r="D32">
-        <v>86.77</v>
-      </c>
-      <c r="E32">
-        <v>151.21</v>
+      <c r="D32" t="str">
+        <v/>
+      </c>
+      <c r="E32" t="str">
+        <v/>
       </c>
       <c r="F32">
-        <v>189.04</v>
+        <v>0</v>
       </c>
       <c r="G32">
-        <v>427.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="B33" t="str">
         <v/>
@@ -1162,31 +1162,31 @@
       <c r="D33" t="str">
         <v/>
       </c>
-      <c r="E33">
-        <v>14.26</v>
-      </c>
-      <c r="F33" t="str">
-        <v/>
+      <c r="E33" t="str">
+        <v/>
+      </c>
+      <c r="F33">
+        <v>4582.17</v>
       </c>
       <c r="G33">
-        <v>14.26</v>
+        <v>4582.17</v>
       </c>
     </row>
     <row r="34">
       <c r="A34">
-        <v>223</v>
-      </c>
-      <c r="B34" t="str">
-        <v/>
-      </c>
-      <c r="C34" t="str">
-        <v/>
-      </c>
-      <c r="D34" t="str">
-        <v/>
-      </c>
-      <c r="E34" t="str">
-        <v/>
+        <v>303</v>
+      </c>
+      <c r="B34">
+        <v>0</v>
+      </c>
+      <c r="C34">
+        <v>0</v>
+      </c>
+      <c r="D34">
+        <v>0</v>
+      </c>
+      <c r="E34">
+        <v>0</v>
       </c>
       <c r="F34">
         <v>0</v>
@@ -1197,237 +1197,237 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>224</v>
-      </c>
-      <c r="B35" t="str">
-        <v/>
-      </c>
-      <c r="C35" t="str">
-        <v/>
-      </c>
-      <c r="D35" t="str">
-        <v/>
-      </c>
-      <c r="E35" t="str">
-        <v/>
+        <v>555</v>
+      </c>
+      <c r="B35">
+        <v>0</v>
+      </c>
+      <c r="C35">
+        <v>0</v>
+      </c>
+      <c r="D35">
+        <v>0</v>
+      </c>
+      <c r="E35">
+        <v>0</v>
       </c>
       <c r="F35">
-        <v>4582.17</v>
+        <v>0</v>
       </c>
       <c r="G35">
-        <v>4582.17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36">
-        <v>303</v>
+        <v>1001</v>
       </c>
       <c r="B36">
-        <v>0</v>
+        <v>2254.8</v>
       </c>
       <c r="C36">
-        <v>0</v>
+        <v>1601.44</v>
       </c>
       <c r="D36">
-        <v>0</v>
+        <v>1655.49</v>
       </c>
       <c r="E36">
-        <v>0</v>
+        <v>1433.94</v>
       </c>
       <c r="F36">
-        <v>0</v>
+        <v>912.57</v>
       </c>
       <c r="G36">
-        <v>0</v>
+        <v>7858.24</v>
       </c>
     </row>
     <row r="37">
       <c r="A37">
-        <v>555</v>
+        <v>1002</v>
       </c>
       <c r="B37">
-        <v>0</v>
+        <v>1969.51</v>
       </c>
       <c r="C37">
-        <v>0</v>
+        <v>2970.51</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>29195.53</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>28955.22</v>
       </c>
       <c r="F37">
-        <v>0</v>
+        <v>33175.15</v>
       </c>
       <c r="G37">
-        <v>0</v>
+        <v>96265.92</v>
       </c>
     </row>
     <row r="38">
       <c r="A38">
-        <v>1001</v>
+        <v>1004</v>
       </c>
       <c r="B38">
-        <v>2254.8</v>
+        <v>0.01</v>
       </c>
       <c r="C38">
-        <v>1601.44</v>
+        <v>0</v>
       </c>
       <c r="D38">
-        <v>1655.49</v>
+        <v>0.01</v>
       </c>
       <c r="E38">
-        <v>1433.94</v>
+        <v>0.01</v>
       </c>
       <c r="F38">
-        <v>912.57</v>
+        <v>0.01</v>
       </c>
       <c r="G38">
-        <v>7858.24</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="39">
       <c r="A39">
-        <v>1002</v>
+        <v>1007</v>
       </c>
       <c r="B39">
-        <v>1969.51</v>
+        <v>10082.51</v>
       </c>
       <c r="C39">
-        <v>2970.51</v>
+        <v>13745.06</v>
       </c>
       <c r="D39">
-        <v>29195.53</v>
+        <v>15859.43</v>
       </c>
       <c r="E39">
-        <v>28955.22</v>
+        <v>14112.17</v>
       </c>
       <c r="F39">
-        <v>33175.15</v>
+        <v>10762.39</v>
       </c>
       <c r="G39">
-        <v>96265.92</v>
+        <v>64561.56</v>
       </c>
     </row>
     <row r="40">
       <c r="A40">
-        <v>1004</v>
+        <v>1015</v>
       </c>
       <c r="B40">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="C40">
         <v>0</v>
       </c>
       <c r="D40">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="E40">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="F40">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="G40">
-        <v>0.04</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41">
-        <v>1007</v>
+        <v>1016</v>
       </c>
       <c r="B41">
-        <v>10082.51</v>
+        <v>1201.05</v>
       </c>
       <c r="C41">
-        <v>13745.06</v>
+        <v>167.54</v>
       </c>
       <c r="D41">
-        <v>15859.43</v>
+        <v>8.98</v>
       </c>
       <c r="E41">
-        <v>14112.17</v>
-      </c>
-      <c r="F41">
-        <v>10762.39</v>
+        <v>0.59</v>
+      </c>
+      <c r="F41" t="str">
+        <v/>
       </c>
       <c r="G41">
-        <v>64561.56</v>
+        <v>1378.16</v>
       </c>
     </row>
     <row r="42">
       <c r="A42">
-        <v>1015</v>
+        <v>1017</v>
       </c>
       <c r="B42">
-        <v>0</v>
+        <v>215.45</v>
       </c>
       <c r="C42">
-        <v>0</v>
+        <v>140.34</v>
       </c>
       <c r="D42">
-        <v>0</v>
+        <v>148.1</v>
       </c>
       <c r="E42">
-        <v>0</v>
+        <v>85.99</v>
       </c>
       <c r="F42">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="G42">
-        <v>0</v>
+        <v>593.4</v>
       </c>
     </row>
     <row r="43">
       <c r="A43">
-        <v>1016</v>
-      </c>
-      <c r="B43">
-        <v>1201.05</v>
-      </c>
-      <c r="C43">
-        <v>167.54</v>
-      </c>
-      <c r="D43">
-        <v>8.98</v>
+        <v>2000</v>
+      </c>
+      <c r="B43" t="str">
+        <v/>
+      </c>
+      <c r="C43" t="str">
+        <v/>
+      </c>
+      <c r="D43" t="str">
+        <v/>
       </c>
       <c r="E43">
-        <v>0.59</v>
-      </c>
-      <c r="F43" t="str">
-        <v/>
+        <v>0</v>
+      </c>
+      <c r="F43">
+        <v>0</v>
       </c>
       <c r="G43">
-        <v>1378.16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44">
-        <v>1017</v>
-      </c>
-      <c r="B44">
-        <v>215.45</v>
+        <v>2001</v>
+      </c>
+      <c r="B44" t="str">
+        <v/>
       </c>
       <c r="C44">
-        <v>140.34</v>
+        <v>0</v>
       </c>
       <c r="D44">
-        <v>148.1</v>
+        <v>0</v>
       </c>
       <c r="E44">
-        <v>85.99</v>
+        <v>82.24</v>
       </c>
       <c r="F44">
-        <v>3.52</v>
+        <v>8467.99</v>
       </c>
       <c r="G44">
-        <v>593.4</v>
+        <v>8550.23</v>
       </c>
     </row>
     <row r="45">
       <c r="A45">
-        <v>2000</v>
+        <v>2002</v>
       </c>
       <c r="B45" t="str">
         <v/>
@@ -1435,45 +1435,45 @@
       <c r="C45" t="str">
         <v/>
       </c>
-      <c r="D45" t="str">
-        <v/>
+      <c r="D45">
+        <v>174574.28</v>
       </c>
       <c r="E45">
-        <v>0</v>
+        <v>116737.37</v>
       </c>
       <c r="F45">
         <v>0</v>
       </c>
       <c r="G45">
-        <v>0</v>
+        <v>291311.65</v>
       </c>
     </row>
     <row r="46">
       <c r="A46">
-        <v>2001</v>
+        <v>2003</v>
       </c>
       <c r="B46" t="str">
         <v/>
       </c>
-      <c r="C46">
-        <v>0</v>
-      </c>
-      <c r="D46">
-        <v>0</v>
+      <c r="C46" t="str">
+        <v/>
+      </c>
+      <c r="D46" t="str">
+        <v/>
       </c>
       <c r="E46">
-        <v>82.24</v>
+        <v>0</v>
       </c>
       <c r="F46">
-        <v>8467.99</v>
+        <v>0</v>
       </c>
       <c r="G46">
-        <v>8550.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47">
-        <v>2002</v>
+        <v>2005</v>
       </c>
       <c r="B47" t="str">
         <v/>
@@ -1482,21 +1482,21 @@
         <v/>
       </c>
       <c r="D47">
-        <v>174574.28</v>
+        <v>17144.97</v>
       </c>
       <c r="E47">
-        <v>116737.37</v>
-      </c>
-      <c r="F47">
-        <v>0</v>
+        <v>8259.88</v>
+      </c>
+      <c r="F47" t="str">
+        <v/>
       </c>
       <c r="G47">
-        <v>291311.65</v>
+        <v>25404.85</v>
       </c>
     </row>
     <row r="48">
       <c r="A48">
-        <v>2003</v>
+        <v>2008</v>
       </c>
       <c r="B48" t="str">
         <v/>
@@ -1507,19 +1507,19 @@
       <c r="D48" t="str">
         <v/>
       </c>
-      <c r="E48">
-        <v>0</v>
+      <c r="E48" t="str">
+        <v/>
       </c>
       <c r="F48">
-        <v>0</v>
+        <v>12035.78</v>
       </c>
       <c r="G48">
-        <v>0</v>
+        <v>12035.78</v>
       </c>
     </row>
     <row r="49">
       <c r="A49">
-        <v>2005</v>
+        <v>2222</v>
       </c>
       <c r="B49" t="str">
         <v/>
@@ -1527,22 +1527,22 @@
       <c r="C49" t="str">
         <v/>
       </c>
-      <c r="D49">
-        <v>17144.97</v>
+      <c r="D49" t="str">
+        <v/>
       </c>
       <c r="E49">
-        <v>8259.88</v>
-      </c>
-      <c r="F49" t="str">
-        <v/>
+        <v>10.68</v>
+      </c>
+      <c r="F49">
+        <v>14.75</v>
       </c>
       <c r="G49">
-        <v>25404.85</v>
+        <v>25.43</v>
       </c>
     </row>
     <row r="50">
       <c r="A50">
-        <v>2008</v>
+        <v>3000</v>
       </c>
       <c r="B50" t="str">
         <v/>
@@ -1553,19 +1553,19 @@
       <c r="D50" t="str">
         <v/>
       </c>
-      <c r="E50" t="str">
-        <v/>
+      <c r="E50">
+        <v>0</v>
       </c>
       <c r="F50">
-        <v>12035.78</v>
+        <v>0</v>
       </c>
       <c r="G50">
-        <v>12035.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51">
-        <v>2222</v>
+        <v>3001</v>
       </c>
       <c r="B51" t="str">
         <v/>
@@ -1576,42 +1576,42 @@
       <c r="D51" t="str">
         <v/>
       </c>
-      <c r="E51">
-        <v>10.68</v>
+      <c r="E51" t="str">
+        <v/>
       </c>
       <c r="F51">
-        <v>14.75</v>
+        <v>0</v>
       </c>
       <c r="G51">
-        <v>25.43</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52">
-        <v>3000</v>
-      </c>
-      <c r="B52" t="str">
-        <v/>
-      </c>
-      <c r="C52" t="str">
-        <v/>
-      </c>
-      <c r="D52" t="str">
-        <v/>
+        <v>3333</v>
+      </c>
+      <c r="B52">
+        <v>0.71</v>
+      </c>
+      <c r="C52">
+        <v>0.41</v>
+      </c>
+      <c r="D52">
+        <v>0.48</v>
       </c>
       <c r="E52">
-        <v>0</v>
+        <v>0.49</v>
       </c>
       <c r="F52">
-        <v>0</v>
+        <v>0.48</v>
       </c>
       <c r="G52">
-        <v>0</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="53">
       <c r="A53">
-        <v>3001</v>
+        <v>4011</v>
       </c>
       <c r="B53" t="str">
         <v/>
@@ -1626,139 +1626,185 @@
         <v/>
       </c>
       <c r="F53">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="G53">
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="54">
       <c r="A54">
-        <v>3333</v>
-      </c>
-      <c r="B54">
-        <v>0.71</v>
-      </c>
-      <c r="C54">
-        <v>0.41</v>
-      </c>
-      <c r="D54">
-        <v>0.48</v>
-      </c>
-      <c r="E54">
-        <v>0.49</v>
+        <v>4012</v>
+      </c>
+      <c r="B54" t="str">
+        <v/>
+      </c>
+      <c r="C54" t="str">
+        <v/>
+      </c>
+      <c r="D54" t="str">
+        <v/>
+      </c>
+      <c r="E54" t="str">
+        <v/>
       </c>
       <c r="F54">
-        <v>0.48</v>
+        <v>0</v>
       </c>
       <c r="G54">
-        <v>2.57</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55">
-        <v>4011</v>
-      </c>
-      <c r="B55" t="str">
-        <v/>
-      </c>
-      <c r="C55" t="str">
-        <v/>
-      </c>
-      <c r="D55" t="str">
-        <v/>
-      </c>
-      <c r="E55" t="str">
-        <v/>
+        <v>9998</v>
+      </c>
+      <c r="B55">
+        <v>0</v>
+      </c>
+      <c r="C55">
+        <v>0</v>
+      </c>
+      <c r="D55">
+        <v>0</v>
+      </c>
+      <c r="E55">
+        <v>0</v>
       </c>
       <c r="F55">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="G55">
-        <v>0.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56">
-        <v>4012</v>
-      </c>
-      <c r="B56" t="str">
-        <v/>
-      </c>
-      <c r="C56" t="str">
-        <v/>
-      </c>
-      <c r="D56" t="str">
-        <v/>
-      </c>
-      <c r="E56" t="str">
-        <v/>
+        <v>13425</v>
+      </c>
+      <c r="B56">
+        <v>858.01</v>
+      </c>
+      <c r="C56">
+        <v>774.97</v>
+      </c>
+      <c r="D56">
+        <v>858.01</v>
+      </c>
+      <c r="E56">
+        <v>641.16</v>
       </c>
       <c r="F56">
-        <v>0</v>
+        <v>9.67</v>
       </c>
       <c r="G56">
-        <v>0</v>
+        <v>3141.82</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57">
-        <v>9998</v>
-      </c>
-      <c r="B57">
-        <v>0</v>
-      </c>
-      <c r="C57">
-        <v>0</v>
-      </c>
-      <c r="D57">
-        <v>0</v>
-      </c>
-      <c r="E57">
-        <v>0</v>
-      </c>
-      <c r="F57">
-        <v>0</v>
-      </c>
-      <c r="G57">
-        <v>0</v>
+      <c r="A57" t="str">
+        <v/>
+      </c>
+      <c r="B57" t="str">
+        <v/>
+      </c>
+      <c r="C57" t="str">
+        <v/>
+      </c>
+      <c r="D57" t="str">
+        <v/>
+      </c>
+      <c r="E57" t="str">
+        <v/>
+      </c>
+      <c r="F57" t="str">
+        <v/>
+      </c>
+      <c r="G57" t="str">
+        <v/>
       </c>
     </row>
     <row r="58">
-      <c r="A58">
-        <v>13425</v>
-      </c>
-      <c r="B58">
-        <v>858.01</v>
-      </c>
-      <c r="C58">
-        <v>774.97</v>
-      </c>
-      <c r="D58">
-        <v>858.01</v>
-      </c>
-      <c r="E58">
-        <v>641.16</v>
-      </c>
-      <c r="F58">
-        <v>9.67</v>
-      </c>
-      <c r="G58">
-        <v>3141.82</v>
+      <c r="A58" t="str">
+        <v>── untagged ──</v>
+      </c>
+      <c r="B58" t="str">
+        <v/>
+      </c>
+      <c r="C58" t="str">
+        <v/>
+      </c>
+      <c r="D58" t="str">
+        <v/>
+      </c>
+      <c r="E58" t="str">
+        <v/>
+      </c>
+      <c r="F58" t="str">
+        <v/>
+      </c>
+      <c r="G58" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>-999999</v>
+      </c>
+      <c r="B59">
+        <v>17418.88</v>
+      </c>
+      <c r="C59">
+        <v>10907.25</v>
+      </c>
+      <c r="D59">
+        <v>25305.28</v>
+      </c>
+      <c r="E59">
+        <v>18026.83</v>
+      </c>
+      <c r="F59">
+        <v>15780.23</v>
+      </c>
+      <c r="G59">
+        <v>87438.47</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>99</v>
+      </c>
+      <c r="B60">
+        <v>1602756.97</v>
+      </c>
+      <c r="C60">
+        <v>1541979.87</v>
+      </c>
+      <c r="D60">
+        <v>1790892.59</v>
+      </c>
+      <c r="E60">
+        <v>1722310.47</v>
+      </c>
+      <c r="F60">
+        <v>1895178.54</v>
+      </c>
+      <c r="G60">
+        <v>8553118.44</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G58"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G60"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G59"/>
+  <dimension ref="A1:G61"/>
   <cols>
-    <col min="1" max="1" width="14.83203125" customWidth="1"/>
+    <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="13.83203125" customWidth="1"/>
     <col min="3" max="3" width="13.83203125" customWidth="1"/>
     <col min="4" max="4" width="13.83203125" customWidth="1"/>
@@ -1861,145 +1907,145 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>99</v>
+        <v>126</v>
       </c>
       <c r="B5">
-        <v>1417549.48</v>
+        <v>106392.55</v>
       </c>
       <c r="C5">
-        <v>1285231.35</v>
+        <v>114516.89</v>
       </c>
       <c r="D5">
-        <v>1513204.59</v>
+        <v>122957.88</v>
       </c>
       <c r="E5">
-        <v>1445734.27</v>
+        <v>115359.51</v>
       </c>
       <c r="F5">
-        <v>1598658.68</v>
+        <v>118567.8</v>
       </c>
       <c r="G5">
-        <v>7260378.37</v>
+        <v>577794.63</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B6">
-        <v>106392.55</v>
+        <v>3482.42</v>
       </c>
       <c r="C6">
-        <v>114516.89</v>
+        <v>2847.77</v>
       </c>
       <c r="D6">
-        <v>122957.88</v>
+        <v>2518.92</v>
       </c>
       <c r="E6">
-        <v>115359.51</v>
+        <v>1845.23</v>
       </c>
       <c r="F6">
-        <v>118567.8</v>
+        <v>903.41</v>
       </c>
       <c r="G6">
-        <v>577794.63</v>
+        <v>11597.75</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B7">
-        <v>3482.42</v>
+        <v>822783.59</v>
       </c>
       <c r="C7">
-        <v>2847.77</v>
+        <v>833426.1</v>
       </c>
       <c r="D7">
-        <v>2518.92</v>
+        <v>1200614.86</v>
       </c>
       <c r="E7">
-        <v>1845.23</v>
+        <v>1323989.36</v>
       </c>
       <c r="F7">
-        <v>903.41</v>
+        <v>1462735.31</v>
       </c>
       <c r="G7">
-        <v>11597.75</v>
+        <v>5643549.22</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B8">
-        <v>822783.59</v>
+        <v>1.03</v>
       </c>
       <c r="C8">
-        <v>833426.1</v>
+        <v>0.52</v>
       </c>
       <c r="D8">
-        <v>1200614.86</v>
+        <v>0.67</v>
       </c>
       <c r="E8">
-        <v>1323989.36</v>
+        <v>0.77</v>
       </c>
       <c r="F8">
-        <v>1462735.31</v>
+        <v>1.13</v>
       </c>
       <c r="G8">
-        <v>5643549.22</v>
+        <v>4.12</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B9">
-        <v>1.03</v>
+        <v>266.96</v>
       </c>
       <c r="C9">
-        <v>0.52</v>
+        <v>252.94</v>
       </c>
       <c r="D9">
-        <v>0.67</v>
+        <v>3701.44</v>
       </c>
       <c r="E9">
-        <v>0.77</v>
+        <v>4353.38</v>
       </c>
       <c r="F9">
-        <v>1.13</v>
+        <v>3885.67</v>
       </c>
       <c r="G9">
-        <v>4.12</v>
+        <v>12460.39</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>130</v>
+        <v>170</v>
       </c>
       <c r="B10">
-        <v>266.96</v>
+        <v>0</v>
       </c>
       <c r="C10">
-        <v>252.94</v>
+        <v>0</v>
       </c>
       <c r="D10">
-        <v>3701.44</v>
+        <v>0</v>
       </c>
       <c r="E10">
-        <v>4353.38</v>
+        <v>0</v>
       </c>
       <c r="F10">
-        <v>3885.67</v>
+        <v>0</v>
       </c>
       <c r="G10">
-        <v>12460.39</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -2022,398 +2068,398 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B13">
-        <v>0.01</v>
+        <v>21333.38</v>
       </c>
       <c r="C13">
-        <v>0.01</v>
+        <v>13278.93</v>
       </c>
       <c r="D13">
-        <v>0.01</v>
+        <v>11113.76</v>
       </c>
       <c r="E13">
-        <v>0.01</v>
+        <v>9912.97</v>
       </c>
       <c r="F13">
-        <v>0.01</v>
+        <v>11847.6</v>
       </c>
       <c r="G13">
-        <v>0.05</v>
+        <v>67486.64</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B14">
-        <v>21333.38</v>
+        <v>467.21</v>
       </c>
       <c r="C14">
-        <v>13278.93</v>
+        <v>638.59</v>
       </c>
       <c r="D14">
-        <v>11113.76</v>
+        <v>1188.8</v>
       </c>
       <c r="E14">
-        <v>9912.97</v>
+        <v>1386.57</v>
       </c>
       <c r="F14">
-        <v>11847.6</v>
+        <v>1241.16</v>
       </c>
       <c r="G14">
-        <v>67486.64</v>
+        <v>4922.33</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B15">
-        <v>467.21</v>
+        <v>475.32</v>
       </c>
       <c r="C15">
-        <v>638.59</v>
+        <v>108.26</v>
       </c>
       <c r="D15">
-        <v>1188.8</v>
+        <v>9656.79</v>
       </c>
       <c r="E15">
-        <v>1386.57</v>
+        <v>14909.91</v>
       </c>
       <c r="F15">
-        <v>1241.16</v>
+        <v>11718.71</v>
       </c>
       <c r="G15">
-        <v>4922.33</v>
+        <v>36868.99</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B16">
-        <v>475.32</v>
+        <v>10427.71</v>
       </c>
       <c r="C16">
-        <v>108.26</v>
+        <v>5314.13</v>
       </c>
       <c r="D16">
-        <v>9656.79</v>
+        <v>4209.1</v>
       </c>
       <c r="E16">
-        <v>14909.91</v>
+        <v>2912.07</v>
       </c>
       <c r="F16">
-        <v>11718.71</v>
+        <v>2740.89</v>
       </c>
       <c r="G16">
-        <v>36868.99</v>
+        <v>25603.9</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B17">
-        <v>10427.71</v>
+        <v>3326.25</v>
       </c>
       <c r="C17">
-        <v>5314.13</v>
+        <v>5352.96</v>
       </c>
       <c r="D17">
-        <v>4209.1</v>
+        <v>8218.73</v>
       </c>
       <c r="E17">
-        <v>2912.07</v>
+        <v>12123.38</v>
       </c>
       <c r="F17">
-        <v>2740.89</v>
+        <v>23241.91</v>
       </c>
       <c r="G17">
-        <v>25603.9</v>
+        <v>52263.23</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B18">
-        <v>3326.25</v>
+        <v>22700.54</v>
       </c>
       <c r="C18">
-        <v>5352.96</v>
+        <v>16725.41</v>
       </c>
       <c r="D18">
-        <v>8218.73</v>
+        <v>19342.47</v>
       </c>
       <c r="E18">
-        <v>12123.38</v>
+        <v>15097.77</v>
       </c>
       <c r="F18">
-        <v>23241.91</v>
+        <v>10576.24</v>
       </c>
       <c r="G18">
-        <v>52263.23</v>
+        <v>84442.43</v>
       </c>
     </row>
     <row r="19">
       <c r="A19">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B19">
-        <v>22700.54</v>
+        <v>1.99</v>
       </c>
       <c r="C19">
-        <v>16725.41</v>
+        <v>1.7</v>
       </c>
       <c r="D19">
-        <v>19342.47</v>
+        <v>1.88</v>
       </c>
       <c r="E19">
-        <v>15097.77</v>
+        <v>1.72</v>
       </c>
       <c r="F19">
-        <v>10576.24</v>
+        <v>1.75</v>
       </c>
       <c r="G19">
-        <v>84442.43</v>
+        <v>9.04</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B20">
-        <v>1.99</v>
+        <v>1554.29</v>
       </c>
       <c r="C20">
-        <v>1.7</v>
+        <v>669.49</v>
       </c>
       <c r="D20">
-        <v>1.88</v>
+        <v>3049.96</v>
       </c>
       <c r="E20">
-        <v>1.72</v>
+        <v>1990.3</v>
       </c>
       <c r="F20">
-        <v>1.75</v>
+        <v>1235.01</v>
       </c>
       <c r="G20">
-        <v>9.04</v>
+        <v>8499.05</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B21">
-        <v>1554.29</v>
+        <v>0.01</v>
       </c>
       <c r="C21">
-        <v>669.49</v>
+        <v>0.09</v>
       </c>
       <c r="D21">
-        <v>3049.96</v>
+        <v>0.1</v>
       </c>
       <c r="E21">
-        <v>1990.3</v>
+        <v>0.1</v>
       </c>
       <c r="F21">
-        <v>1235.01</v>
+        <v>0.1</v>
       </c>
       <c r="G21">
-        <v>8499.05</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B22">
-        <v>0.01</v>
+        <v>6824.99</v>
       </c>
       <c r="C22">
-        <v>0.09</v>
+        <v>6314.15</v>
       </c>
       <c r="D22">
-        <v>0.1</v>
+        <v>5576.07</v>
       </c>
       <c r="E22">
-        <v>0.1</v>
+        <v>8508.93</v>
       </c>
       <c r="F22">
-        <v>0.1</v>
+        <v>10729.88</v>
       </c>
       <c r="G22">
-        <v>0.4</v>
+        <v>37954.02</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B23">
-        <v>6824.99</v>
+        <v>0.02</v>
       </c>
       <c r="C23">
-        <v>6314.15</v>
+        <v>0.02</v>
       </c>
       <c r="D23">
-        <v>5576.07</v>
+        <v>0.02</v>
       </c>
       <c r="E23">
-        <v>8508.93</v>
+        <v>0.02</v>
       </c>
       <c r="F23">
-        <v>10729.88</v>
+        <v>0.02</v>
       </c>
       <c r="G23">
-        <v>37954.02</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B24">
-        <v>0.02</v>
+        <v>1.96</v>
       </c>
       <c r="C24">
-        <v>0.02</v>
+        <v>0.65</v>
       </c>
       <c r="D24">
-        <v>0.02</v>
+        <v>5.79</v>
       </c>
       <c r="E24">
-        <v>0.02</v>
+        <v>32.59</v>
       </c>
       <c r="F24">
-        <v>0.02</v>
+        <v>91.6</v>
       </c>
       <c r="G24">
-        <v>0.1</v>
+        <v>132.59</v>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B25">
-        <v>1.96</v>
+        <v>28.54</v>
       </c>
       <c r="C25">
-        <v>0.65</v>
+        <v>32.89</v>
       </c>
       <c r="D25">
-        <v>5.79</v>
+        <v>42.56</v>
       </c>
       <c r="E25">
-        <v>32.59</v>
+        <v>39.75</v>
       </c>
       <c r="F25">
-        <v>91.6</v>
+        <v>33.27</v>
       </c>
       <c r="G25">
-        <v>132.59</v>
+        <v>177.01</v>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <v>202</v>
-      </c>
-      <c r="B26">
-        <v>28.54</v>
+        <v>204</v>
+      </c>
+      <c r="B26" t="str">
+        <v/>
       </c>
       <c r="C26">
-        <v>32.89</v>
+        <v>1.61</v>
       </c>
       <c r="D26">
-        <v>42.56</v>
+        <v>16.91</v>
       </c>
       <c r="E26">
-        <v>39.75</v>
+        <v>34.05</v>
       </c>
       <c r="F26">
-        <v>33.27</v>
+        <v>30.45</v>
       </c>
       <c r="G26">
-        <v>177.01</v>
+        <v>83.02</v>
       </c>
     </row>
     <row r="27">
       <c r="A27">
-        <v>204</v>
-      </c>
-      <c r="B27" t="str">
-        <v/>
+        <v>205</v>
+      </c>
+      <c r="B27">
+        <v>0</v>
       </c>
       <c r="C27">
-        <v>1.61</v>
+        <v>0.02</v>
       </c>
       <c r="D27">
-        <v>16.91</v>
+        <v>0.2</v>
       </c>
       <c r="E27">
-        <v>34.05</v>
+        <v>0.21</v>
       </c>
       <c r="F27">
-        <v>30.45</v>
+        <v>0.21</v>
       </c>
       <c r="G27">
-        <v>83.02</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="28">
       <c r="A28">
-        <v>205</v>
-      </c>
-      <c r="B28">
-        <v>0</v>
-      </c>
-      <c r="C28">
-        <v>0.02</v>
-      </c>
-      <c r="D28">
-        <v>0.2</v>
-      </c>
-      <c r="E28">
-        <v>0.21</v>
+        <v>206</v>
+      </c>
+      <c r="B28" t="str">
+        <v/>
+      </c>
+      <c r="C28" t="str">
+        <v/>
+      </c>
+      <c r="D28" t="str">
+        <v/>
+      </c>
+      <c r="E28" t="str">
+        <v/>
       </c>
       <c r="F28">
-        <v>0.21</v>
+        <v>0</v>
       </c>
       <c r="G28">
-        <v>0.64</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="B29" t="str">
         <v/>
@@ -2436,7 +2482,7 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B30" t="str">
         <v/>
@@ -2444,22 +2490,22 @@
       <c r="C30" t="str">
         <v/>
       </c>
-      <c r="D30" t="str">
-        <v/>
-      </c>
-      <c r="E30" t="str">
-        <v/>
+      <c r="D30">
+        <v>86.77</v>
+      </c>
+      <c r="E30">
+        <v>151.21</v>
       </c>
       <c r="F30">
-        <v>0</v>
+        <v>189.04</v>
       </c>
       <c r="G30">
-        <v>0</v>
+        <v>427.02</v>
       </c>
     </row>
     <row r="31">
       <c r="A31">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="B31" t="str">
         <v/>
@@ -2467,22 +2513,22 @@
       <c r="C31" t="str">
         <v/>
       </c>
-      <c r="D31">
-        <v>86.77</v>
+      <c r="D31" t="str">
+        <v/>
       </c>
       <c r="E31">
-        <v>151.21</v>
-      </c>
-      <c r="F31">
-        <v>189.04</v>
+        <v>14.26</v>
+      </c>
+      <c r="F31" t="str">
+        <v/>
       </c>
       <c r="G31">
-        <v>427.02</v>
+        <v>14.26</v>
       </c>
     </row>
     <row r="32">
       <c r="A32">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B32" t="str">
         <v/>
@@ -2493,19 +2539,19 @@
       <c r="D32" t="str">
         <v/>
       </c>
-      <c r="E32">
-        <v>14.26</v>
-      </c>
-      <c r="F32" t="str">
-        <v/>
+      <c r="E32" t="str">
+        <v/>
+      </c>
+      <c r="F32">
+        <v>0</v>
       </c>
       <c r="G32">
-        <v>14.26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B33" t="str">
         <v/>
@@ -2520,38 +2566,38 @@
         <v/>
       </c>
       <c r="F33">
-        <v>0</v>
+        <v>4582.17</v>
       </c>
       <c r="G33">
-        <v>0</v>
+        <v>4582.17</v>
       </c>
     </row>
     <row r="34">
       <c r="A34">
-        <v>224</v>
-      </c>
-      <c r="B34" t="str">
-        <v/>
-      </c>
-      <c r="C34" t="str">
-        <v/>
-      </c>
-      <c r="D34" t="str">
-        <v/>
-      </c>
-      <c r="E34" t="str">
-        <v/>
+        <v>303</v>
+      </c>
+      <c r="B34">
+        <v>0</v>
+      </c>
+      <c r="C34">
+        <v>0</v>
+      </c>
+      <c r="D34">
+        <v>0</v>
+      </c>
+      <c r="E34">
+        <v>0</v>
       </c>
       <c r="F34">
-        <v>4582.17</v>
+        <v>0</v>
       </c>
       <c r="G34">
-        <v>4582.17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35">
-        <v>303</v>
+        <v>555</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -2574,237 +2620,237 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>555</v>
+        <v>1001</v>
       </c>
       <c r="B36">
-        <v>0</v>
+        <v>2171.72</v>
       </c>
       <c r="C36">
-        <v>0</v>
+        <v>1561.38</v>
       </c>
       <c r="D36">
-        <v>0</v>
+        <v>1611.23</v>
       </c>
       <c r="E36">
-        <v>0</v>
+        <v>1391.66</v>
       </c>
       <c r="F36">
-        <v>0</v>
+        <v>868.97</v>
       </c>
       <c r="G36">
-        <v>0</v>
+        <v>7604.96</v>
       </c>
     </row>
     <row r="37">
       <c r="A37">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="B37">
-        <v>2171.72</v>
+        <v>1968.87</v>
       </c>
       <c r="C37">
-        <v>1561.38</v>
+        <v>2969.94</v>
       </c>
       <c r="D37">
-        <v>1611.23</v>
+        <v>29194.65</v>
       </c>
       <c r="E37">
-        <v>1391.66</v>
+        <v>28954.6</v>
       </c>
       <c r="F37">
-        <v>868.97</v>
+        <v>33174.52</v>
       </c>
       <c r="G37">
-        <v>7604.96</v>
+        <v>96262.58</v>
       </c>
     </row>
     <row r="38">
       <c r="A38">
-        <v>1002</v>
+        <v>1004</v>
       </c>
       <c r="B38">
-        <v>1968.87</v>
+        <v>0.01</v>
       </c>
       <c r="C38">
-        <v>2969.94</v>
+        <v>0</v>
       </c>
       <c r="D38">
-        <v>29194.65</v>
+        <v>0.01</v>
       </c>
       <c r="E38">
-        <v>28954.6</v>
+        <v>0.01</v>
       </c>
       <c r="F38">
-        <v>33174.52</v>
+        <v>0.01</v>
       </c>
       <c r="G38">
-        <v>96262.58</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="39">
       <c r="A39">
-        <v>1004</v>
+        <v>1007</v>
       </c>
       <c r="B39">
-        <v>0.01</v>
+        <v>10082.51</v>
       </c>
       <c r="C39">
-        <v>0</v>
+        <v>13745.06</v>
       </c>
       <c r="D39">
-        <v>0.01</v>
+        <v>15859.43</v>
       </c>
       <c r="E39">
-        <v>0.01</v>
+        <v>14112.17</v>
       </c>
       <c r="F39">
-        <v>0.01</v>
+        <v>10762.39</v>
       </c>
       <c r="G39">
-        <v>0.04</v>
+        <v>64561.56</v>
       </c>
     </row>
     <row r="40">
       <c r="A40">
-        <v>1007</v>
+        <v>1015</v>
       </c>
       <c r="B40">
-        <v>10082.51</v>
+        <v>0</v>
       </c>
       <c r="C40">
-        <v>13745.06</v>
+        <v>0</v>
       </c>
       <c r="D40">
-        <v>15859.43</v>
+        <v>0</v>
       </c>
       <c r="E40">
-        <v>14112.17</v>
+        <v>0</v>
       </c>
       <c r="F40">
-        <v>10762.39</v>
+        <v>0</v>
       </c>
       <c r="G40">
-        <v>64561.56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="B41">
-        <v>0</v>
+        <v>1201.05</v>
       </c>
       <c r="C41">
-        <v>0</v>
+        <v>167.54</v>
       </c>
       <c r="D41">
-        <v>0</v>
+        <v>8.98</v>
       </c>
       <c r="E41">
-        <v>0</v>
+        <v>0.59</v>
       </c>
       <c r="F41">
         <v>0</v>
       </c>
       <c r="G41">
-        <v>0</v>
+        <v>1378.16</v>
       </c>
     </row>
     <row r="42">
       <c r="A42">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="B42">
-        <v>1201.05</v>
+        <v>215.45</v>
       </c>
       <c r="C42">
-        <v>167.54</v>
+        <v>140.34</v>
       </c>
       <c r="D42">
-        <v>8.98</v>
+        <v>148.1</v>
       </c>
       <c r="E42">
-        <v>0.59</v>
+        <v>85.99</v>
       </c>
       <c r="F42">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="G42">
-        <v>1378.16</v>
+        <v>593.4</v>
       </c>
     </row>
     <row r="43">
       <c r="A43">
-        <v>1017</v>
-      </c>
-      <c r="B43">
-        <v>215.45</v>
-      </c>
-      <c r="C43">
-        <v>140.34</v>
-      </c>
-      <c r="D43">
-        <v>148.1</v>
+        <v>2000</v>
+      </c>
+      <c r="B43" t="str">
+        <v/>
+      </c>
+      <c r="C43" t="str">
+        <v/>
+      </c>
+      <c r="D43" t="str">
+        <v/>
       </c>
       <c r="E43">
-        <v>85.99</v>
+        <v>0</v>
       </c>
       <c r="F43">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="G43">
-        <v>593.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44">
-        <v>2000</v>
+        <v>2001</v>
       </c>
       <c r="B44" t="str">
         <v/>
       </c>
-      <c r="C44" t="str">
-        <v/>
-      </c>
-      <c r="D44" t="str">
-        <v/>
+      <c r="C44">
+        <v>0</v>
+      </c>
+      <c r="D44">
+        <v>0</v>
       </c>
       <c r="E44">
-        <v>0</v>
+        <v>82.24</v>
       </c>
       <c r="F44">
-        <v>0</v>
+        <v>8467.99</v>
       </c>
       <c r="G44">
-        <v>0</v>
+        <v>8550.23</v>
       </c>
     </row>
     <row r="45">
       <c r="A45">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="B45" t="str">
         <v/>
       </c>
-      <c r="C45">
-        <v>0</v>
+      <c r="C45" t="str">
+        <v/>
       </c>
       <c r="D45">
-        <v>0</v>
+        <v>174574.28</v>
       </c>
       <c r="E45">
-        <v>82.24</v>
+        <v>116737.37</v>
       </c>
       <c r="F45">
-        <v>8467.99</v>
+        <v>0</v>
       </c>
       <c r="G45">
-        <v>8550.23</v>
+        <v>291311.65</v>
       </c>
     </row>
     <row r="46">
       <c r="A46">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="B46" t="str">
         <v/>
@@ -2812,22 +2858,22 @@
       <c r="C46" t="str">
         <v/>
       </c>
-      <c r="D46">
-        <v>174574.28</v>
+      <c r="D46" t="str">
+        <v/>
       </c>
       <c r="E46">
-        <v>116737.37</v>
+        <v>0</v>
       </c>
       <c r="F46">
         <v>0</v>
       </c>
       <c r="G46">
-        <v>291311.65</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47">
-        <v>2003</v>
+        <v>2005</v>
       </c>
       <c r="B47" t="str">
         <v/>
@@ -2835,22 +2881,22 @@
       <c r="C47" t="str">
         <v/>
       </c>
-      <c r="D47" t="str">
-        <v/>
+      <c r="D47">
+        <v>17144.97</v>
       </c>
       <c r="E47">
-        <v>0</v>
-      </c>
-      <c r="F47">
-        <v>0</v>
+        <v>8259.88</v>
+      </c>
+      <c r="F47" t="str">
+        <v/>
       </c>
       <c r="G47">
-        <v>0</v>
+        <v>25404.85</v>
       </c>
     </row>
     <row r="48">
       <c r="A48">
-        <v>2005</v>
+        <v>2008</v>
       </c>
       <c r="B48" t="str">
         <v/>
@@ -2858,22 +2904,22 @@
       <c r="C48" t="str">
         <v/>
       </c>
-      <c r="D48">
-        <v>17144.97</v>
-      </c>
-      <c r="E48">
-        <v>8259.88</v>
-      </c>
-      <c r="F48" t="str">
-        <v/>
+      <c r="D48" t="str">
+        <v/>
+      </c>
+      <c r="E48" t="str">
+        <v/>
+      </c>
+      <c r="F48">
+        <v>12035.78</v>
       </c>
       <c r="G48">
-        <v>25404.85</v>
+        <v>12035.78</v>
       </c>
     </row>
     <row r="49">
       <c r="A49">
-        <v>2008</v>
+        <v>2222</v>
       </c>
       <c r="B49" t="str">
         <v/>
@@ -2884,19 +2930,19 @@
       <c r="D49" t="str">
         <v/>
       </c>
-      <c r="E49" t="str">
-        <v/>
+      <c r="E49">
+        <v>10.68</v>
       </c>
       <c r="F49">
-        <v>12035.78</v>
+        <v>14.75</v>
       </c>
       <c r="G49">
-        <v>12035.78</v>
+        <v>25.43</v>
       </c>
     </row>
     <row r="50">
       <c r="A50">
-        <v>2222</v>
+        <v>3000</v>
       </c>
       <c r="B50" t="str">
         <v/>
@@ -2908,18 +2954,18 @@
         <v/>
       </c>
       <c r="E50">
-        <v>10.68</v>
+        <v>0</v>
       </c>
       <c r="F50">
-        <v>14.75</v>
+        <v>0</v>
       </c>
       <c r="G50">
-        <v>25.43</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51">
-        <v>3000</v>
+        <v>3001</v>
       </c>
       <c r="B51" t="str">
         <v/>
@@ -2930,8 +2976,8 @@
       <c r="D51" t="str">
         <v/>
       </c>
-      <c r="E51">
-        <v>0</v>
+      <c r="E51" t="str">
+        <v/>
       </c>
       <c r="F51">
         <v>0</v>
@@ -2942,53 +2988,53 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>3001</v>
-      </c>
-      <c r="B52" t="str">
-        <v/>
-      </c>
-      <c r="C52" t="str">
-        <v/>
-      </c>
-      <c r="D52" t="str">
-        <v/>
-      </c>
-      <c r="E52" t="str">
-        <v/>
+        <v>3333</v>
+      </c>
+      <c r="B52">
+        <v>0.71</v>
+      </c>
+      <c r="C52">
+        <v>0.41</v>
+      </c>
+      <c r="D52">
+        <v>0.48</v>
+      </c>
+      <c r="E52">
+        <v>0.49</v>
       </c>
       <c r="F52">
-        <v>0</v>
+        <v>0.48</v>
       </c>
       <c r="G52">
-        <v>0</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="53">
       <c r="A53">
-        <v>3333</v>
-      </c>
-      <c r="B53">
-        <v>0.71</v>
-      </c>
-      <c r="C53">
-        <v>0.41</v>
-      </c>
-      <c r="D53">
-        <v>0.48</v>
-      </c>
-      <c r="E53">
-        <v>0.49</v>
+        <v>4011</v>
+      </c>
+      <c r="B53" t="str">
+        <v/>
+      </c>
+      <c r="C53" t="str">
+        <v/>
+      </c>
+      <c r="D53" t="str">
+        <v/>
+      </c>
+      <c r="E53" t="str">
+        <v/>
       </c>
       <c r="F53">
-        <v>0.48</v>
+        <v>0.01</v>
       </c>
       <c r="G53">
-        <v>2.57</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="54">
       <c r="A54">
-        <v>4011</v>
+        <v>4012</v>
       </c>
       <c r="B54" t="str">
         <v/>
@@ -3003,27 +3049,27 @@
         <v/>
       </c>
       <c r="F54">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="G54">
-        <v>0.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55">
-        <v>4012</v>
-      </c>
-      <c r="B55" t="str">
-        <v/>
-      </c>
-      <c r="C55" t="str">
-        <v/>
-      </c>
-      <c r="D55" t="str">
-        <v/>
-      </c>
-      <c r="E55" t="str">
-        <v/>
+        <v>9998</v>
+      </c>
+      <c r="B55">
+        <v>0</v>
+      </c>
+      <c r="C55">
+        <v>0</v>
+      </c>
+      <c r="D55">
+        <v>0</v>
+      </c>
+      <c r="E55">
+        <v>0</v>
       </c>
       <c r="F55">
         <v>0</v>
@@ -3034,108 +3080,154 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>9998</v>
+        <v>13425</v>
       </c>
       <c r="B56">
-        <v>0</v>
+        <v>858.01</v>
       </c>
       <c r="C56">
-        <v>0</v>
+        <v>774.97</v>
       </c>
       <c r="D56">
-        <v>0</v>
+        <v>858.01</v>
       </c>
       <c r="E56">
-        <v>0</v>
+        <v>641.16</v>
       </c>
       <c r="F56">
-        <v>0</v>
+        <v>9.67</v>
       </c>
       <c r="G56">
-        <v>0</v>
+        <v>3141.82</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57">
-        <v>13425</v>
-      </c>
-      <c r="B57">
-        <v>858.01</v>
-      </c>
-      <c r="C57">
-        <v>774.97</v>
-      </c>
-      <c r="D57">
-        <v>858.01</v>
-      </c>
-      <c r="E57">
-        <v>641.16</v>
-      </c>
-      <c r="F57">
-        <v>9.67</v>
-      </c>
-      <c r="G57">
-        <v>3141.82</v>
+      <c r="A57" t="str">
+        <v/>
+      </c>
+      <c r="B57" t="str">
+        <v/>
+      </c>
+      <c r="C57" t="str">
+        <v/>
+      </c>
+      <c r="D57" t="str">
+        <v/>
+      </c>
+      <c r="E57" t="str">
+        <v/>
+      </c>
+      <c r="F57" t="str">
+        <v/>
+      </c>
+      <c r="G57" t="str">
+        <v/>
       </c>
     </row>
     <row r="58">
-      <c r="A58">
-        <v>123623963915635</v>
-      </c>
-      <c r="B58">
-        <v>0</v>
-      </c>
-      <c r="C58">
-        <v>0</v>
-      </c>
-      <c r="D58">
-        <v>0.01</v>
-      </c>
-      <c r="E58">
-        <v>0</v>
-      </c>
-      <c r="F58">
-        <v>0.01</v>
-      </c>
-      <c r="G58">
-        <v>0.02</v>
+      <c r="A58" t="str">
+        <v>── untagged ──</v>
+      </c>
+      <c r="B58" t="str">
+        <v/>
+      </c>
+      <c r="C58" t="str">
+        <v/>
+      </c>
+      <c r="D58" t="str">
+        <v/>
+      </c>
+      <c r="E58" t="str">
+        <v/>
+      </c>
+      <c r="F58" t="str">
+        <v/>
+      </c>
+      <c r="G58" t="str">
+        <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59">
+        <v>99</v>
+      </c>
+      <c r="B59">
+        <v>1417549.48</v>
+      </c>
+      <c r="C59">
+        <v>1285231.35</v>
+      </c>
+      <c r="D59">
+        <v>1513204.59</v>
+      </c>
+      <c r="E59">
+        <v>1445734.27</v>
+      </c>
+      <c r="F59">
+        <v>1598658.68</v>
+      </c>
+      <c r="G59">
+        <v>7260378.37</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>123623963915635</v>
+      </c>
+      <c r="B60">
+        <v>0</v>
+      </c>
+      <c r="C60">
+        <v>0</v>
+      </c>
+      <c r="D60">
+        <v>0.01</v>
+      </c>
+      <c r="E60">
+        <v>0</v>
+      </c>
+      <c r="F60">
+        <v>0.01</v>
+      </c>
+      <c r="G60">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
         <v>90000000000000000000</v>
       </c>
-      <c r="B59">
+      <c r="B61">
         <v>0.06</v>
       </c>
-      <c r="C59">
+      <c r="C61">
         <v>0.01</v>
       </c>
-      <c r="D59">
-        <v>0</v>
-      </c>
-      <c r="E59">
-        <v>0</v>
-      </c>
-      <c r="F59">
-        <v>0</v>
-      </c>
-      <c r="G59">
+      <c r="D61">
+        <v>0</v>
+      </c>
+      <c r="E61">
+        <v>0</v>
+      </c>
+      <c r="F61">
+        <v>0</v>
+      </c>
+      <c r="G61">
         <v>0.07</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G59"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G61"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:E43"/>
   <cols>
-    <col min="1" max="1" width="14.83203125" customWidth="1"/>
+    <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="13.83203125" customWidth="1"/>
     <col min="3" max="3" width="13.83203125" customWidth="1"/>
     <col min="4" max="4" width="13.83203125" customWidth="1"/>
@@ -3824,33 +3916,67 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
+        <v/>
+      </c>
+      <c r="B41" t="str">
+        <v/>
+      </c>
+      <c r="C41" t="str">
+        <v/>
+      </c>
+      <c r="D41" t="str">
+        <v/>
+      </c>
+      <c r="E41" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>── untagged ──</v>
+      </c>
+      <c r="B42" t="str">
+        <v/>
+      </c>
+      <c r="C42" t="str">
+        <v/>
+      </c>
+      <c r="D42" t="str">
+        <v/>
+      </c>
+      <c r="E42" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
         <v>untagged</v>
       </c>
-      <c r="B41">
+      <c r="B43">
         <v>1558291.2</v>
       </c>
-      <c r="C41">
+      <c r="C43">
         <v>1509689.9</v>
       </c>
-      <c r="D41">
+      <c r="D43">
         <v>1745376.5</v>
       </c>
-      <c r="E41">
+      <c r="E43">
         <v>4813357.6</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E41"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E43"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H62"/>
+  <dimension ref="A1:I64"/>
   <cols>
-    <col min="1" max="1" width="14.83203125" customWidth="1"/>
+    <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
     <col min="3" max="3" width="13.83203125" customWidth="1"/>
     <col min="4" max="4" width="13.83203125" customWidth="1"/>
@@ -3858,6 +3984,7 @@
     <col min="6" max="6" width="13.83203125" customWidth="1"/>
     <col min="7" max="7" width="13.83203125" customWidth="1"/>
     <col min="8" max="8" width="13.83203125" customWidth="1"/>
+    <col min="9" max="9" width="55.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3885,91 +4012,103 @@
       <c r="H1" t="str">
         <v>total_diff</v>
       </c>
+      <c r="I1" t="str">
+        <v>notes</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2">
-        <v>-999999</v>
+        <v>0</v>
       </c>
       <c r="B2" t="str">
-        <v>ours only</v>
+        <v>both</v>
       </c>
       <c r="C2">
-        <v>17418.88</v>
+        <v>0</v>
       </c>
       <c r="D2">
-        <v>10907.25</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>25305.28</v>
+        <v>324.58</v>
       </c>
       <c r="F2">
-        <v>18026.83</v>
+        <v>1121.44</v>
       </c>
       <c r="G2">
-        <v>15780.23</v>
+        <v>340.4</v>
       </c>
       <c r="H2">
-        <v>87438.47</v>
+        <v>1786.42</v>
+      </c>
+      <c r="I2" t="str">
+        <v>Diff vs Spark = Chronicle farm (USDS-CLE) only. Spark does not track this farm.</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B3" t="str">
         <v>both</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>5139.57</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>4193.83</v>
       </c>
       <c r="E3">
-        <v>324.58</v>
+        <v>6259.94</v>
       </c>
       <c r="F3">
-        <v>1121.44</v>
+        <v>5552.85</v>
       </c>
       <c r="G3">
-        <v>340.4</v>
+        <v>8195.2</v>
       </c>
       <c r="H3">
-        <v>1786.42</v>
+        <v>29341.39</v>
+      </c>
+      <c r="I3" t="str">
+        <v>Diff vs Spark = Chronicle farm (USDS-CLE) only. Spark does not track this farm.</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B4" t="str">
         <v>both</v>
       </c>
       <c r="C4">
-        <v>5139.57</v>
+        <v>0</v>
       </c>
       <c r="D4">
-        <v>4193.83</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>6259.94</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>5552.85</v>
+        <v>0</v>
       </c>
       <c r="G4">
-        <v>8195.2</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>29341.39</v>
+        <v>0</v>
+      </c>
+      <c r="I4" t="str">
+        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="B5" t="str">
-        <v>both</v>
+        <v>ours only</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -3988,11 +4127,14 @@
       </c>
       <c r="H5">
         <v>0</v>
+      </c>
+      <c r="I5" t="str">
+        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="B6" t="str">
         <v>ours only</v>
@@ -4015,140 +4157,158 @@
       <c r="H6">
         <v>0</v>
       </c>
+      <c r="I6" t="str">
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>99</v>
+        <v>126</v>
       </c>
       <c r="B7" t="str">
-        <v>both</v>
+        <v>spark only</v>
       </c>
       <c r="C7">
-        <v>185207.49</v>
+        <v>-106392.55</v>
       </c>
       <c r="D7">
-        <v>256748.52</v>
+        <v>-114516.89</v>
       </c>
       <c r="E7">
-        <v>277688</v>
+        <v>-122957.88</v>
       </c>
       <c r="F7">
-        <v>276576.2</v>
+        <v>-115359.51</v>
       </c>
       <c r="G7">
-        <v>296519.86</v>
+        <v>-118567.8</v>
       </c>
       <c r="H7">
-        <v>1292740.07</v>
+        <v>-577794.63</v>
+      </c>
+      <c r="I7" t="str">
+        <v>Subproxy holdings, no DR applied. Handled in Supply Side MSC.</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="B8" t="str">
-        <v>ours only</v>
+        <v>both</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>-445.27</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>-208.59</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>-351.49</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>-397.73</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>-172.48</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>-1575.56</v>
+      </c>
+      <c r="I8" t="str">
+        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B9" t="str">
-        <v>spark only</v>
+        <v>both</v>
       </c>
       <c r="C9">
-        <v>-106392.55</v>
+        <v>4064.11</v>
       </c>
       <c r="D9">
-        <v>-114516.89</v>
+        <v>4165.46</v>
       </c>
       <c r="E9">
-        <v>-122957.88</v>
+        <v>-905.41</v>
       </c>
       <c r="F9">
-        <v>-115359.51</v>
+        <v>-2031.4</v>
       </c>
       <c r="G9">
-        <v>-118567.8</v>
+        <v>-1597.47</v>
       </c>
       <c r="H9">
-        <v>-577794.63</v>
+        <v>3695.29</v>
+      </c>
+      <c r="I9" t="str">
+        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B10" t="str">
         <v>both</v>
       </c>
       <c r="C10">
-        <v>-445.27</v>
+        <v>0</v>
       </c>
       <c r="D10">
-        <v>-208.59</v>
+        <v>0</v>
       </c>
       <c r="E10">
-        <v>-351.49</v>
+        <v>0</v>
       </c>
       <c r="F10">
-        <v>-397.73</v>
+        <v>0</v>
       </c>
       <c r="G10">
-        <v>-172.48</v>
+        <v>0</v>
       </c>
       <c r="H10">
-        <v>-1575.56</v>
+        <v>0</v>
+      </c>
+      <c r="I10" t="str">
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B11" t="str">
-        <v>both</v>
+        <v>spark only</v>
       </c>
       <c r="C11">
-        <v>4064.11</v>
+        <v>-266.96</v>
       </c>
       <c r="D11">
-        <v>4165.46</v>
+        <v>-252.94</v>
       </c>
       <c r="E11">
-        <v>-905.41</v>
+        <v>-3701.44</v>
       </c>
       <c r="F11">
-        <v>-2031.4</v>
+        <v>-4353.38</v>
       </c>
       <c r="G11">
-        <v>-1597.47</v>
+        <v>-3885.67</v>
       </c>
       <c r="H11">
-        <v>3695.29</v>
+        <v>-12460.39</v>
+      </c>
+      <c r="I11" t="str">
+        <v>Found in Spark datasets only, no onchain events.</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>129</v>
+        <v>170</v>
       </c>
       <c r="B12" t="str">
         <v>both</v>
@@ -4170,37 +4330,43 @@
       </c>
       <c r="H12">
         <v>0</v>
+      </c>
+      <c r="I12" t="str">
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>130</v>
+        <v>171</v>
       </c>
       <c r="B13" t="str">
-        <v>spark only</v>
+        <v>both</v>
       </c>
       <c r="C13">
-        <v>-266.96</v>
+        <v>0</v>
       </c>
       <c r="D13">
-        <v>-252.94</v>
+        <v>0</v>
       </c>
       <c r="E13">
-        <v>-3701.44</v>
+        <v>0</v>
       </c>
       <c r="F13">
-        <v>-4353.38</v>
+        <v>0</v>
       </c>
       <c r="G13">
-        <v>-3885.67</v>
+        <v>0</v>
       </c>
       <c r="H13">
-        <v>-12460.39</v>
+        <v>0</v>
+      </c>
+      <c r="I13" t="str">
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="B14" t="str">
         <v>both</v>
@@ -4222,11 +4388,14 @@
       </c>
       <c r="H14">
         <v>0</v>
+      </c>
+      <c r="I14" t="str">
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="B15" t="str">
         <v>both</v>
@@ -4248,11 +4417,14 @@
       </c>
       <c r="H15">
         <v>0</v>
+      </c>
+      <c r="I15" t="str">
+        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B16" t="str">
         <v>both</v>
@@ -4274,37 +4446,43 @@
       </c>
       <c r="H16">
         <v>0</v>
+      </c>
+      <c r="I16" t="str">
+        <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="B17" t="str">
         <v>both</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>-2455.39</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>-327.72</v>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>-110.6</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>-2893.69</v>
+      </c>
+      <c r="I17" t="str">
+        <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B18" t="str">
         <v>both</v>
@@ -4326,37 +4504,43 @@
       </c>
       <c r="H18">
         <v>0</v>
+      </c>
+      <c r="I18" t="str">
+        <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="B19" t="str">
         <v>both</v>
       </c>
       <c r="C19">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="D19">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="E19">
-        <v>-2455.39</v>
+        <v>0</v>
       </c>
       <c r="F19">
-        <v>-327.72</v>
+        <v>0</v>
       </c>
       <c r="G19">
-        <v>-110.6</v>
+        <v>0</v>
       </c>
       <c r="H19">
-        <v>-2893.69</v>
+        <v>0</v>
+      </c>
+      <c r="I19" t="str">
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B20" t="str">
         <v>both</v>
@@ -4378,11 +4562,14 @@
       </c>
       <c r="H20">
         <v>0</v>
+      </c>
+      <c r="I20" t="str">
+        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B21" t="str">
         <v>both</v>
@@ -4404,11 +4591,14 @@
       </c>
       <c r="H21">
         <v>0</v>
+      </c>
+      <c r="I21" t="str">
+        <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="B22" t="str">
         <v>both</v>
@@ -4430,11 +4620,14 @@
       </c>
       <c r="H22">
         <v>0</v>
+      </c>
+      <c r="I22" t="str">
+        <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B23" t="str">
         <v>both</v>
@@ -4456,11 +4649,14 @@
       </c>
       <c r="H23">
         <v>0</v>
+      </c>
+      <c r="I23" t="str">
+        <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B24" t="str">
         <v>both</v>
@@ -4482,11 +4678,14 @@
       </c>
       <c r="H24">
         <v>0</v>
+      </c>
+      <c r="I24" t="str">
+        <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B25" t="str">
         <v>both</v>
@@ -4508,11 +4707,14 @@
       </c>
       <c r="H25">
         <v>0</v>
+      </c>
+      <c r="I25" t="str">
+        <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="B26" t="str">
         <v>both</v>
@@ -4534,11 +4736,14 @@
       </c>
       <c r="H26">
         <v>0</v>
+      </c>
+      <c r="I26" t="str">
+        <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="B27" t="str">
         <v>both</v>
@@ -4560,11 +4765,14 @@
       </c>
       <c r="H27">
         <v>0</v>
+      </c>
+      <c r="I27" t="str">
+        <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B28" t="str">
         <v>both</v>
@@ -4586,11 +4794,14 @@
       </c>
       <c r="H28">
         <v>0</v>
+      </c>
+      <c r="I28" t="str">
+        <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B29" t="str">
         <v>both</v>
@@ -4612,11 +4823,14 @@
       </c>
       <c r="H29">
         <v>0</v>
+      </c>
+      <c r="I29" t="str">
+        <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B30" t="str">
         <v>both</v>
@@ -4638,11 +4852,14 @@
       </c>
       <c r="H30">
         <v>0</v>
+      </c>
+      <c r="I30" t="str">
+        <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="B31" t="str">
         <v>both</v>
@@ -4664,11 +4881,14 @@
       </c>
       <c r="H31">
         <v>0</v>
+      </c>
+      <c r="I31" t="str">
+        <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="B32" t="str">
         <v>both</v>
@@ -4690,11 +4910,14 @@
       </c>
       <c r="H32">
         <v>0</v>
+      </c>
+      <c r="I32" t="str">
+        <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="B33" t="str">
         <v>both</v>
@@ -4716,11 +4939,14 @@
       </c>
       <c r="H33">
         <v>0</v>
+      </c>
+      <c r="I33" t="str">
+        <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="B34" t="str">
         <v>both</v>
@@ -4742,11 +4968,14 @@
       </c>
       <c r="H34">
         <v>0</v>
+      </c>
+      <c r="I34" t="str">
+        <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="B35" t="str">
         <v>both</v>
@@ -4768,11 +4997,14 @@
       </c>
       <c r="H35">
         <v>0</v>
+      </c>
+      <c r="I35" t="str">
+        <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36">
-        <v>223</v>
+        <v>303</v>
       </c>
       <c r="B36" t="str">
         <v>both</v>
@@ -4794,11 +5026,14 @@
       </c>
       <c r="H36">
         <v>0</v>
+      </c>
+      <c r="I36" t="str">
+        <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37">
-        <v>224</v>
+        <v>555</v>
       </c>
       <c r="B37" t="str">
         <v>both</v>
@@ -4820,115 +5055,130 @@
       </c>
       <c r="H37">
         <v>0</v>
+      </c>
+      <c r="I37" t="str">
+        <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38">
-        <v>303</v>
+        <v>1001</v>
       </c>
       <c r="B38" t="str">
         <v>both</v>
       </c>
       <c r="C38">
-        <v>0</v>
+        <v>83.09</v>
       </c>
       <c r="D38">
-        <v>0</v>
+        <v>40.06</v>
       </c>
       <c r="E38">
-        <v>0</v>
+        <v>44.25</v>
       </c>
       <c r="F38">
-        <v>0</v>
+        <v>42.28</v>
       </c>
       <c r="G38">
-        <v>0</v>
+        <v>43.6</v>
       </c>
       <c r="H38">
-        <v>0</v>
+        <v>253.28</v>
+      </c>
+      <c r="I38" t="str">
+        <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39">
-        <v>555</v>
+        <v>1002</v>
       </c>
       <c r="B39" t="str">
         <v>both</v>
       </c>
       <c r="C39">
-        <v>0</v>
+        <v>0.64</v>
       </c>
       <c r="D39">
-        <v>0</v>
+        <v>0.57</v>
       </c>
       <c r="E39">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="F39">
-        <v>0</v>
+        <v>0.62</v>
       </c>
       <c r="G39">
-        <v>0</v>
+        <v>0.64</v>
       </c>
       <c r="H39">
-        <v>0</v>
+        <v>3.35</v>
+      </c>
+      <c r="I39" t="str">
+        <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40">
-        <v>1001</v>
+        <v>1004</v>
       </c>
       <c r="B40" t="str">
         <v>both</v>
       </c>
       <c r="C40">
-        <v>83.09</v>
+        <v>0</v>
       </c>
       <c r="D40">
-        <v>40.06</v>
+        <v>0</v>
       </c>
       <c r="E40">
-        <v>44.25</v>
+        <v>0</v>
       </c>
       <c r="F40">
-        <v>42.28</v>
+        <v>0</v>
       </c>
       <c r="G40">
-        <v>43.6</v>
+        <v>0</v>
       </c>
       <c r="H40">
-        <v>253.28</v>
+        <v>0</v>
+      </c>
+      <c r="I40" t="str">
+        <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41">
-        <v>1002</v>
+        <v>1007</v>
       </c>
       <c r="B41" t="str">
         <v>both</v>
       </c>
       <c r="C41">
-        <v>0.64</v>
+        <v>0</v>
       </c>
       <c r="D41">
-        <v>0.57</v>
+        <v>0</v>
       </c>
       <c r="E41">
-        <v>0.88</v>
+        <v>0</v>
       </c>
       <c r="F41">
-        <v>0.62</v>
+        <v>0</v>
       </c>
       <c r="G41">
-        <v>0.64</v>
+        <v>0</v>
       </c>
       <c r="H41">
-        <v>3.35</v>
+        <v>0</v>
+      </c>
+      <c r="I41" t="str">
+        <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42">
-        <v>1004</v>
+        <v>1015</v>
       </c>
       <c r="B42" t="str">
         <v>both</v>
@@ -4950,11 +5200,14 @@
       </c>
       <c r="H42">
         <v>0</v>
+      </c>
+      <c r="I42" t="str">
+        <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43">
-        <v>1007</v>
+        <v>1016</v>
       </c>
       <c r="B43" t="str">
         <v>both</v>
@@ -4976,11 +5229,14 @@
       </c>
       <c r="H43">
         <v>0</v>
+      </c>
+      <c r="I43" t="str">
+        <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44">
-        <v>1015</v>
+        <v>1017</v>
       </c>
       <c r="B44" t="str">
         <v>both</v>
@@ -5002,11 +5258,14 @@
       </c>
       <c r="H44">
         <v>0</v>
+      </c>
+      <c r="I44" t="str">
+        <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45">
-        <v>1016</v>
+        <v>2000</v>
       </c>
       <c r="B45" t="str">
         <v>both</v>
@@ -5028,11 +5287,14 @@
       </c>
       <c r="H45">
         <v>0</v>
+      </c>
+      <c r="I45" t="str">
+        <v/>
       </c>
     </row>
     <row r="46">
       <c r="A46">
-        <v>1017</v>
+        <v>2001</v>
       </c>
       <c r="B46" t="str">
         <v>both</v>
@@ -5054,11 +5316,14 @@
       </c>
       <c r="H46">
         <v>0</v>
+      </c>
+      <c r="I46" t="str">
+        <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47">
-        <v>2000</v>
+        <v>2002</v>
       </c>
       <c r="B47" t="str">
         <v>both</v>
@@ -5080,11 +5345,14 @@
       </c>
       <c r="H47">
         <v>0</v>
+      </c>
+      <c r="I47" t="str">
+        <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48">
-        <v>2001</v>
+        <v>2003</v>
       </c>
       <c r="B48" t="str">
         <v>both</v>
@@ -5106,11 +5374,14 @@
       </c>
       <c r="H48">
         <v>0</v>
+      </c>
+      <c r="I48" t="str">
+        <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49">
-        <v>2002</v>
+        <v>2005</v>
       </c>
       <c r="B49" t="str">
         <v>both</v>
@@ -5132,11 +5403,14 @@
       </c>
       <c r="H49">
         <v>0</v>
+      </c>
+      <c r="I49" t="str">
+        <v/>
       </c>
     </row>
     <row r="50">
       <c r="A50">
-        <v>2003</v>
+        <v>2008</v>
       </c>
       <c r="B50" t="str">
         <v>both</v>
@@ -5158,11 +5432,14 @@
       </c>
       <c r="H50">
         <v>0</v>
+      </c>
+      <c r="I50" t="str">
+        <v/>
       </c>
     </row>
     <row r="51">
       <c r="A51">
-        <v>2005</v>
+        <v>2222</v>
       </c>
       <c r="B51" t="str">
         <v>both</v>
@@ -5184,11 +5461,14 @@
       </c>
       <c r="H51">
         <v>0</v>
+      </c>
+      <c r="I51" t="str">
+        <v/>
       </c>
     </row>
     <row r="52">
       <c r="A52">
-        <v>2008</v>
+        <v>3000</v>
       </c>
       <c r="B52" t="str">
         <v>both</v>
@@ -5210,11 +5490,14 @@
       </c>
       <c r="H52">
         <v>0</v>
+      </c>
+      <c r="I52" t="str">
+        <v/>
       </c>
     </row>
     <row r="53">
       <c r="A53">
-        <v>2222</v>
+        <v>3001</v>
       </c>
       <c r="B53" t="str">
         <v>both</v>
@@ -5236,11 +5519,14 @@
       </c>
       <c r="H53">
         <v>0</v>
+      </c>
+      <c r="I53" t="str">
+        <v/>
       </c>
     </row>
     <row r="54">
       <c r="A54">
-        <v>3000</v>
+        <v>3333</v>
       </c>
       <c r="B54" t="str">
         <v>both</v>
@@ -5262,11 +5548,14 @@
       </c>
       <c r="H54">
         <v>0</v>
+      </c>
+      <c r="I54" t="str">
+        <v/>
       </c>
     </row>
     <row r="55">
       <c r="A55">
-        <v>3001</v>
+        <v>4011</v>
       </c>
       <c r="B55" t="str">
         <v>both</v>
@@ -5288,11 +5577,14 @@
       </c>
       <c r="H55">
         <v>0</v>
+      </c>
+      <c r="I55" t="str">
+        <v/>
       </c>
     </row>
     <row r="56">
       <c r="A56">
-        <v>3333</v>
+        <v>4012</v>
       </c>
       <c r="B56" t="str">
         <v>both</v>
@@ -5314,11 +5606,14 @@
       </c>
       <c r="H56">
         <v>0</v>
+      </c>
+      <c r="I56" t="str">
+        <v/>
       </c>
     </row>
     <row r="57">
       <c r="A57">
-        <v>4011</v>
+        <v>9998</v>
       </c>
       <c r="B57" t="str">
         <v>both</v>
@@ -5340,11 +5635,14 @@
       </c>
       <c r="H57">
         <v>0</v>
+      </c>
+      <c r="I57" t="str">
+        <v/>
       </c>
     </row>
     <row r="58">
       <c r="A58">
-        <v>4012</v>
+        <v>13425</v>
       </c>
       <c r="B58" t="str">
         <v>both</v>
@@ -5367,128 +5665,202 @@
       <c r="H58">
         <v>0</v>
       </c>
+      <c r="I58" t="str">
+        <v/>
+      </c>
     </row>
     <row r="59">
-      <c r="A59">
-        <v>9998</v>
+      <c r="A59" t="str">
+        <v/>
       </c>
       <c r="B59" t="str">
-        <v>both</v>
-      </c>
-      <c r="C59">
-        <v>0</v>
-      </c>
-      <c r="D59">
-        <v>0</v>
-      </c>
-      <c r="E59">
-        <v>0</v>
-      </c>
-      <c r="F59">
-        <v>0</v>
-      </c>
-      <c r="G59">
-        <v>0</v>
-      </c>
-      <c r="H59">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="C59" t="str">
+        <v/>
+      </c>
+      <c r="D59" t="str">
+        <v/>
+      </c>
+      <c r="E59" t="str">
+        <v/>
+      </c>
+      <c r="F59" t="str">
+        <v/>
+      </c>
+      <c r="G59" t="str">
+        <v/>
+      </c>
+      <c r="H59" t="str">
+        <v/>
+      </c>
+      <c r="I59" t="str">
+        <v/>
       </c>
     </row>
     <row r="60">
-      <c r="A60">
-        <v>13425</v>
+      <c r="A60" t="str">
+        <v>── untagged ──</v>
       </c>
       <c r="B60" t="str">
-        <v>both</v>
-      </c>
-      <c r="C60">
-        <v>0</v>
-      </c>
-      <c r="D60">
-        <v>0</v>
-      </c>
-      <c r="E60">
-        <v>0</v>
-      </c>
-      <c r="F60">
-        <v>0</v>
-      </c>
-      <c r="G60">
-        <v>0</v>
-      </c>
-      <c r="H60">
-        <v>0</v>
+        <v/>
+      </c>
+      <c r="C60" t="str">
+        <v/>
+      </c>
+      <c r="D60" t="str">
+        <v/>
+      </c>
+      <c r="E60" t="str">
+        <v/>
+      </c>
+      <c r="F60" t="str">
+        <v/>
+      </c>
+      <c r="G60" t="str">
+        <v/>
+      </c>
+      <c r="H60" t="str">
+        <v/>
+      </c>
+      <c r="I60" t="str">
+        <v/>
       </c>
     </row>
     <row r="61">
       <c r="A61">
-        <v>123623963915635</v>
+        <v>-999999</v>
       </c>
       <c r="B61" t="str">
-        <v>spark only</v>
+        <v>ours only</v>
       </c>
       <c r="C61">
-        <v>0</v>
+        <v>17418.88</v>
       </c>
       <c r="D61">
-        <v>0</v>
+        <v>10907.25</v>
       </c>
       <c r="E61">
-        <v>-0.01</v>
+        <v>25305.28</v>
       </c>
       <c r="F61">
-        <v>0</v>
+        <v>18026.83</v>
       </c>
       <c r="G61">
-        <v>-0.01</v>
+        <v>15780.23</v>
       </c>
       <c r="H61">
-        <v>-0.02</v>
+        <v>87438.47</v>
+      </c>
+      <c r="I61" t="str">
+        <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62">
+        <v>99</v>
+      </c>
+      <c r="B62" t="str">
+        <v>both</v>
+      </c>
+      <c r="C62">
+        <v>185207.49</v>
+      </c>
+      <c r="D62">
+        <v>256748.52</v>
+      </c>
+      <c r="E62">
+        <v>277688</v>
+      </c>
+      <c r="F62">
+        <v>276576.2</v>
+      </c>
+      <c r="G62">
+        <v>296519.86</v>
+      </c>
+      <c r="H62">
+        <v>1292740.07</v>
+      </c>
+      <c r="I62" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>123623963915635</v>
+      </c>
+      <c r="B63" t="str">
+        <v>spark only</v>
+      </c>
+      <c r="C63">
+        <v>0</v>
+      </c>
+      <c r="D63">
+        <v>0</v>
+      </c>
+      <c r="E63">
+        <v>-0.01</v>
+      </c>
+      <c r="F63">
+        <v>0</v>
+      </c>
+      <c r="G63">
+        <v>-0.01</v>
+      </c>
+      <c r="H63">
+        <v>-0.02</v>
+      </c>
+      <c r="I63" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
         <v>90000000000000000000</v>
       </c>
-      <c r="B62" t="str">
+      <c r="B64" t="str">
         <v>spark only</v>
       </c>
-      <c r="C62">
+      <c r="C64">
         <v>-0.06</v>
       </c>
-      <c r="D62">
+      <c r="D64">
         <v>-0.01</v>
       </c>
-      <c r="E62">
-        <v>0</v>
-      </c>
-      <c r="F62">
-        <v>0</v>
-      </c>
-      <c r="G62">
-        <v>0</v>
-      </c>
-      <c r="H62">
+      <c r="E64">
+        <v>0</v>
+      </c>
+      <c r="F64">
+        <v>0</v>
+      </c>
+      <c r="G64">
+        <v>0</v>
+      </c>
+      <c r="H64">
         <v>-0.07</v>
+      </c>
+      <c r="I64" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H62"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I64"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F58"/>
+  <dimension ref="A1:G60"/>
   <cols>
-    <col min="1" max="1" width="14.83203125" customWidth="1"/>
+    <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
     <col min="3" max="3" width="13.83203125" customWidth="1"/>
     <col min="4" max="4" width="13.83203125" customWidth="1"/>
     <col min="5" max="5" width="13.83203125" customWidth="1"/>
     <col min="6" max="6" width="13.83203125" customWidth="1"/>
+    <col min="7" max="7" width="55.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5510,6 +5882,9 @@
       <c r="F1" t="str">
         <v>total_diff</v>
       </c>
+      <c r="G1" t="str">
+        <v>notes</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -5529,6 +5904,9 @@
       </c>
       <c r="F2">
         <v>219094.81</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Diff vs Spark = Chronicle farm (USDS-CLE) only. Spark does not track this farm.</v>
       </c>
     </row>
     <row r="3">
@@ -5550,6 +5928,9 @@
       <c r="F3">
         <v>347334.42</v>
       </c>
+      <c r="G3" t="str">
+        <v>Diff vs Spark = Chronicle farm (USDS-CLE) only. Spark does not track this farm.</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4">
@@ -5570,6 +5951,9 @@
       <c r="F4">
         <v>0</v>
       </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5">
@@ -5590,6 +5974,9 @@
       <c r="F5">
         <v>0</v>
       </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6">
@@ -5610,6 +5997,9 @@
       <c r="F6">
         <v>0</v>
       </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7">
@@ -5630,6 +6020,9 @@
       <c r="F7">
         <v>-45362.23</v>
       </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8">
@@ -5650,6 +6043,9 @@
       <c r="F8">
         <v>-737923.58</v>
       </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9">
@@ -5670,6 +6066,9 @@
       <c r="F9">
         <v>-2.18</v>
       </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10">
@@ -5690,6 +6089,9 @@
       <c r="F10">
         <v>0</v>
       </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11">
@@ -5710,6 +6112,9 @@
       <c r="F11">
         <v>0</v>
       </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12">
@@ -5730,6 +6135,9 @@
       <c r="F12">
         <v>0.03</v>
       </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13">
@@ -5750,6 +6158,9 @@
       <c r="F13">
         <v>1.27</v>
       </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14">
@@ -5770,6 +6181,9 @@
       <c r="F14">
         <v>-3330</v>
       </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15">
@@ -5790,6 +6204,9 @@
       <c r="F15">
         <v>-10434.71</v>
       </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16">
@@ -5810,6 +6227,9 @@
       <c r="F16">
         <v>-28087.56</v>
       </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17">
@@ -5830,6 +6250,9 @@
       <c r="F17">
         <v>-22460.06</v>
       </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18">
@@ -5850,6 +6273,9 @@
       <c r="F18">
         <v>-87916.08</v>
       </c>
+      <c r="G18" t="str">
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19">
@@ -5870,6 +6296,9 @@
       <c r="F19">
         <v>-8.43</v>
       </c>
+      <c r="G19" t="str">
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20">
@@ -5890,6 +6319,9 @@
       <c r="F20">
         <v>-7889.26</v>
       </c>
+      <c r="G20" t="str">
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21">
@@ -5910,6 +6342,9 @@
       <c r="F21">
         <v>-0.3</v>
       </c>
+      <c r="G21" t="str">
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22">
@@ -5930,6 +6365,9 @@
       <c r="F22">
         <v>-52262.69</v>
       </c>
+      <c r="G22" t="str">
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23">
@@ -5950,6 +6388,9 @@
       <c r="F23">
         <v>0.06</v>
       </c>
+      <c r="G23" t="str">
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24">
@@ -5970,6 +6411,9 @@
       <c r="F24">
         <v>-11.2</v>
       </c>
+      <c r="G24" t="str">
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25">
@@ -5990,6 +6434,9 @@
       <c r="F25">
         <v>-139.81</v>
       </c>
+      <c r="G25" t="str">
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26">
@@ -6010,6 +6457,9 @@
       <c r="F26">
         <v>-27.08</v>
       </c>
+      <c r="G26" t="str">
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27">
@@ -6030,6 +6480,9 @@
       <c r="F27">
         <v>-0.28</v>
       </c>
+      <c r="G27" t="str">
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28">
@@ -6050,6 +6503,9 @@
       <c r="F28">
         <v>0</v>
       </c>
+      <c r="G28" t="str">
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29">
@@ -6070,6 +6526,9 @@
       <c r="F29">
         <v>0</v>
       </c>
+      <c r="G29" t="str">
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30">
@@ -6090,6 +6549,9 @@
       <c r="F30">
         <v>-129.73</v>
       </c>
+      <c r="G30" t="str">
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31">
@@ -6110,6 +6572,9 @@
       <c r="F31">
         <v>0</v>
       </c>
+      <c r="G31" t="str">
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32">
@@ -6130,6 +6595,9 @@
       <c r="F32">
         <v>0</v>
       </c>
+      <c r="G32" t="str">
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33">
@@ -6150,6 +6618,9 @@
       <c r="F33">
         <v>0</v>
       </c>
+      <c r="G33" t="str">
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34">
@@ -6170,6 +6641,9 @@
       <c r="F34">
         <v>0</v>
       </c>
+      <c r="G34" t="str">
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35">
@@ -6190,6 +6664,9 @@
       <c r="F35">
         <v>0</v>
       </c>
+      <c r="G35" t="str">
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36">
@@ -6210,6 +6687,9 @@
       <c r="F36">
         <v>3256.73</v>
       </c>
+      <c r="G36" t="str">
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37">
@@ -6230,6 +6710,9 @@
       <c r="F37">
         <v>14.25</v>
       </c>
+      <c r="G37" t="str">
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38">
@@ -6250,6 +6733,9 @@
       <c r="F38">
         <v>-178305.2</v>
       </c>
+      <c r="G38" t="str">
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39">
@@ -6270,6 +6756,9 @@
       <c r="F39">
         <v>-1024.58</v>
       </c>
+      <c r="G39" t="str">
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40">
@@ -6290,6 +6779,9 @@
       <c r="F40">
         <v>5.5</v>
       </c>
+      <c r="G40" t="str">
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41">
@@ -6310,6 +6802,9 @@
       <c r="F41">
         <v>0</v>
       </c>
+      <c r="G41" t="str">
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42">
@@ -6330,6 +6825,9 @@
       <c r="F42">
         <v>-11298.53</v>
       </c>
+      <c r="G42" t="str">
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43">
@@ -6350,6 +6848,9 @@
       <c r="F43">
         <v>-752.11</v>
       </c>
+      <c r="G43" t="str">
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="A44">
@@ -6370,6 +6871,9 @@
       <c r="F44">
         <v>0</v>
       </c>
+      <c r="G44" t="str">
+        <v/>
+      </c>
     </row>
     <row r="45">
       <c r="A45">
@@ -6390,6 +6894,9 @@
       <c r="F45">
         <v>0</v>
       </c>
+      <c r="G45" t="str">
+        <v/>
+      </c>
     </row>
     <row r="46">
       <c r="A46">
@@ -6410,6 +6917,9 @@
       <c r="F46">
         <v>61.28</v>
       </c>
+      <c r="G46" t="str">
+        <v/>
+      </c>
     </row>
     <row r="47">
       <c r="A47">
@@ -6430,6 +6940,9 @@
       <c r="F47">
         <v>0</v>
       </c>
+      <c r="G47" t="str">
+        <v/>
+      </c>
     </row>
     <row r="48">
       <c r="A48">
@@ -6450,6 +6963,9 @@
       <c r="F48">
         <v>15.07</v>
       </c>
+      <c r="G48" t="str">
+        <v/>
+      </c>
     </row>
     <row r="49">
       <c r="A49">
@@ -6470,6 +6986,9 @@
       <c r="F49">
         <v>0</v>
       </c>
+      <c r="G49" t="str">
+        <v/>
+      </c>
     </row>
     <row r="50">
       <c r="A50">
@@ -6490,6 +7009,9 @@
       <c r="F50">
         <v>0</v>
       </c>
+      <c r="G50" t="str">
+        <v/>
+      </c>
     </row>
     <row r="51">
       <c r="A51">
@@ -6510,6 +7032,9 @@
       <c r="F51">
         <v>0</v>
       </c>
+      <c r="G51" t="str">
+        <v/>
+      </c>
     </row>
     <row r="52">
       <c r="A52">
@@ -6530,6 +7055,9 @@
       <c r="F52">
         <v>0</v>
       </c>
+      <c r="G52" t="str">
+        <v/>
+      </c>
     </row>
     <row r="53">
       <c r="A53">
@@ -6550,6 +7078,9 @@
       <c r="F53">
         <v>1.6</v>
       </c>
+      <c r="G53" t="str">
+        <v/>
+      </c>
     </row>
     <row r="54">
       <c r="A54">
@@ -6570,6 +7101,9 @@
       <c r="F54">
         <v>0</v>
       </c>
+      <c r="G54" t="str">
+        <v/>
+      </c>
     </row>
     <row r="55">
       <c r="A55">
@@ -6590,6 +7124,9 @@
       <c r="F55">
         <v>0</v>
       </c>
+      <c r="G55" t="str">
+        <v/>
+      </c>
     </row>
     <row r="56">
       <c r="A56">
@@ -6610,6 +7147,9 @@
       <c r="F56">
         <v>0</v>
       </c>
+      <c r="G56" t="str">
+        <v/>
+      </c>
     </row>
     <row r="57">
       <c r="A57">
@@ -6630,44 +7170,97 @@
       <c r="F57">
         <v>2490.99</v>
       </c>
+      <c r="G57" t="str">
+        <v/>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
+        <v/>
+      </c>
+      <c r="B58" t="str">
+        <v/>
+      </c>
+      <c r="C58" t="str">
+        <v/>
+      </c>
+      <c r="D58" t="str">
+        <v/>
+      </c>
+      <c r="E58" t="str">
+        <v/>
+      </c>
+      <c r="F58" t="str">
+        <v/>
+      </c>
+      <c r="G58" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>── untagged ──</v>
+      </c>
+      <c r="B59" t="str">
+        <v/>
+      </c>
+      <c r="C59" t="str">
+        <v/>
+      </c>
+      <c r="D59" t="str">
+        <v/>
+      </c>
+      <c r="E59" t="str">
+        <v/>
+      </c>
+      <c r="F59" t="str">
+        <v/>
+      </c>
+      <c r="G59" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
         <v>untagged</v>
       </c>
-      <c r="B58" t="str">
-        <v>both</v>
-      </c>
-      <c r="C58">
+      <c r="B60" t="str">
+        <v>both</v>
+      </c>
+      <c r="C60">
         <v>61884.66</v>
       </c>
-      <c r="D58">
+      <c r="D60">
         <v>43197.23</v>
       </c>
-      <c r="E58">
+      <c r="E60">
         <v>70821.38</v>
       </c>
-      <c r="F58">
+      <c r="F60">
         <v>175903.27</v>
+      </c>
+      <c r="G60" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F58"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G60"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F60"/>
+  <dimension ref="A1:G62"/>
   <cols>
-    <col min="1" max="1" width="14.83203125" customWidth="1"/>
+    <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
     <col min="3" max="3" width="13.83203125" customWidth="1"/>
     <col min="4" max="4" width="13.83203125" customWidth="1"/>
     <col min="5" max="5" width="13.83203125" customWidth="1"/>
     <col min="6" max="6" width="13.83203125" customWidth="1"/>
+    <col min="7" max="7" width="55.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6689,6 +7282,9 @@
       <c r="F1" t="str">
         <v>total_diff</v>
       </c>
+      <c r="G1" t="str">
+        <v>notes</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -6708,6 +7304,9 @@
       </c>
       <c r="F2">
         <v>218770.23</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Diff vs Spark = Chronicle farm (USDS-CLE) only. Spark does not track this farm.</v>
       </c>
     </row>
     <row r="3">
@@ -6729,6 +7328,9 @@
       <c r="F3">
         <v>331741.07</v>
       </c>
+      <c r="G3" t="str">
+        <v>Diff vs Spark = Chronicle farm (USDS-CLE) only. Spark does not track this farm.</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4">
@@ -6749,6 +7351,9 @@
       <c r="F4">
         <v>0</v>
       </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5">
@@ -6769,6 +7374,9 @@
       <c r="F5">
         <v>343867.32</v>
       </c>
+      <c r="G5" t="str">
+        <v>Subproxy holdings, no DR applied. Handled in Supply Side MSC.</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6">
@@ -6789,6 +7397,9 @@
       <c r="F6">
         <v>-44356.89</v>
       </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7">
@@ -6809,6 +7420,9 @@
       <c r="F7">
         <v>-745247.75</v>
       </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8">
@@ -6829,6 +7443,9 @@
       <c r="F8">
         <v>-2.18</v>
       </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9">
@@ -6849,6 +7466,9 @@
       <c r="F9">
         <v>4221.34</v>
       </c>
+      <c r="G9" t="str">
+        <v>Found in Spark datasets only, no onchain events.</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10">
@@ -6869,6 +7489,9 @@
       <c r="F10">
         <v>0</v>
       </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11">
@@ -6889,6 +7512,9 @@
       <c r="F11">
         <v>0</v>
       </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12">
@@ -6909,6 +7535,9 @@
       <c r="F12">
         <v>0.03</v>
       </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13">
@@ -6929,6 +7558,9 @@
       <c r="F13">
         <v>1.27</v>
       </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14">
@@ -6949,6 +7581,9 @@
       <c r="F14">
         <v>-3330</v>
       </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15">
@@ -6969,6 +7604,9 @@
       <c r="F15">
         <v>-7979.33</v>
       </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16">
@@ -6989,6 +7627,9 @@
       <c r="F16">
         <v>-28087.56</v>
       </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17">
@@ -7009,6 +7650,9 @@
       <c r="F17">
         <v>-22460.06</v>
       </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18">
@@ -7029,6 +7673,9 @@
       <c r="F18">
         <v>-87916.08</v>
       </c>
+      <c r="G18" t="str">
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19">
@@ -7049,6 +7696,9 @@
       <c r="F19">
         <v>-8.43</v>
       </c>
+      <c r="G19" t="str">
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20">
@@ -7069,6 +7719,9 @@
       <c r="F20">
         <v>-7889.26</v>
       </c>
+      <c r="G20" t="str">
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21">
@@ -7089,6 +7742,9 @@
       <c r="F21">
         <v>-0.3</v>
       </c>
+      <c r="G21" t="str">
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22">
@@ -7109,6 +7765,9 @@
       <c r="F22">
         <v>-52262.69</v>
       </c>
+      <c r="G22" t="str">
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23">
@@ -7129,6 +7788,9 @@
       <c r="F23">
         <v>0.06</v>
       </c>
+      <c r="G23" t="str">
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24">
@@ -7149,6 +7811,9 @@
       <c r="F24">
         <v>-11.2</v>
       </c>
+      <c r="G24" t="str">
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25">
@@ -7169,6 +7834,9 @@
       <c r="F25">
         <v>-139.81</v>
       </c>
+      <c r="G25" t="str">
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26">
@@ -7189,6 +7857,9 @@
       <c r="F26">
         <v>-27.08</v>
       </c>
+      <c r="G26" t="str">
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27">
@@ -7209,6 +7880,9 @@
       <c r="F27">
         <v>-0.28</v>
       </c>
+      <c r="G27" t="str">
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28">
@@ -7229,6 +7903,9 @@
       <c r="F28">
         <v>0</v>
       </c>
+      <c r="G28" t="str">
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29">
@@ -7249,6 +7926,9 @@
       <c r="F29">
         <v>0</v>
       </c>
+      <c r="G29" t="str">
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30">
@@ -7269,6 +7949,9 @@
       <c r="F30">
         <v>-129.73</v>
       </c>
+      <c r="G30" t="str">
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31">
@@ -7289,6 +7972,9 @@
       <c r="F31">
         <v>0</v>
       </c>
+      <c r="G31" t="str">
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32">
@@ -7309,6 +7995,9 @@
       <c r="F32">
         <v>0</v>
       </c>
+      <c r="G32" t="str">
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33">
@@ -7329,6 +8018,9 @@
       <c r="F33">
         <v>0</v>
       </c>
+      <c r="G33" t="str">
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34">
@@ -7349,6 +8041,9 @@
       <c r="F34">
         <v>0</v>
       </c>
+      <c r="G34" t="str">
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35">
@@ -7369,6 +8064,9 @@
       <c r="F35">
         <v>0</v>
       </c>
+      <c r="G35" t="str">
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36">
@@ -7389,6 +8087,9 @@
       <c r="F36">
         <v>3089.33</v>
       </c>
+      <c r="G36" t="str">
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37">
@@ -7409,6 +8110,9 @@
       <c r="F37">
         <v>12.16</v>
       </c>
+      <c r="G37" t="str">
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38">
@@ -7429,6 +8133,9 @@
       <c r="F38">
         <v>-178305.2</v>
       </c>
+      <c r="G38" t="str">
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39">
@@ -7449,6 +8156,9 @@
       <c r="F39">
         <v>-1024.58</v>
       </c>
+      <c r="G39" t="str">
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40">
@@ -7469,6 +8179,9 @@
       <c r="F40">
         <v>5.5</v>
       </c>
+      <c r="G40" t="str">
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41">
@@ -7489,6 +8202,9 @@
       <c r="F41">
         <v>0</v>
       </c>
+      <c r="G41" t="str">
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42">
@@ -7509,6 +8225,9 @@
       <c r="F42">
         <v>-11298.53</v>
       </c>
+      <c r="G42" t="str">
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43">
@@ -7529,6 +8248,9 @@
       <c r="F43">
         <v>-752.11</v>
       </c>
+      <c r="G43" t="str">
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="A44">
@@ -7549,6 +8271,9 @@
       <c r="F44">
         <v>0</v>
       </c>
+      <c r="G44" t="str">
+        <v/>
+      </c>
     </row>
     <row r="45">
       <c r="A45">
@@ -7569,6 +8294,9 @@
       <c r="F45">
         <v>0</v>
       </c>
+      <c r="G45" t="str">
+        <v/>
+      </c>
     </row>
     <row r="46">
       <c r="A46">
@@ -7589,6 +8317,9 @@
       <c r="F46">
         <v>61.28</v>
       </c>
+      <c r="G46" t="str">
+        <v/>
+      </c>
     </row>
     <row r="47">
       <c r="A47">
@@ -7609,6 +8340,9 @@
       <c r="F47">
         <v>0</v>
       </c>
+      <c r="G47" t="str">
+        <v/>
+      </c>
     </row>
     <row r="48">
       <c r="A48">
@@ -7629,6 +8363,9 @@
       <c r="F48">
         <v>15.07</v>
       </c>
+      <c r="G48" t="str">
+        <v/>
+      </c>
     </row>
     <row r="49">
       <c r="A49">
@@ -7649,6 +8386,9 @@
       <c r="F49">
         <v>0</v>
       </c>
+      <c r="G49" t="str">
+        <v/>
+      </c>
     </row>
     <row r="50">
       <c r="A50">
@@ -7669,6 +8409,9 @@
       <c r="F50">
         <v>0</v>
       </c>
+      <c r="G50" t="str">
+        <v/>
+      </c>
     </row>
     <row r="51">
       <c r="A51">
@@ -7689,6 +8432,9 @@
       <c r="F51">
         <v>0</v>
       </c>
+      <c r="G51" t="str">
+        <v/>
+      </c>
     </row>
     <row r="52">
       <c r="A52">
@@ -7709,6 +8455,9 @@
       <c r="F52">
         <v>0</v>
       </c>
+      <c r="G52" t="str">
+        <v/>
+      </c>
     </row>
     <row r="53">
       <c r="A53">
@@ -7729,6 +8478,9 @@
       <c r="F53">
         <v>1.6</v>
       </c>
+      <c r="G53" t="str">
+        <v/>
+      </c>
     </row>
     <row r="54">
       <c r="A54">
@@ -7749,6 +8501,9 @@
       <c r="F54">
         <v>0</v>
       </c>
+      <c r="G54" t="str">
+        <v/>
+      </c>
     </row>
     <row r="55">
       <c r="A55">
@@ -7769,6 +8524,9 @@
       <c r="F55">
         <v>0</v>
       </c>
+      <c r="G55" t="str">
+        <v/>
+      </c>
     </row>
     <row r="56">
       <c r="A56">
@@ -7789,6 +8547,9 @@
       <c r="F56">
         <v>0</v>
       </c>
+      <c r="G56" t="str">
+        <v/>
+      </c>
     </row>
     <row r="57">
       <c r="A57">
@@ -7809,70 +8570,128 @@
       <c r="F57">
         <v>2490.99</v>
       </c>
+      <c r="G57" t="str">
+        <v/>
+      </c>
     </row>
     <row r="58">
-      <c r="A58">
+      <c r="A58" t="str">
+        <v/>
+      </c>
+      <c r="B58" t="str">
+        <v/>
+      </c>
+      <c r="C58" t="str">
+        <v/>
+      </c>
+      <c r="D58" t="str">
+        <v/>
+      </c>
+      <c r="E58" t="str">
+        <v/>
+      </c>
+      <c r="F58" t="str">
+        <v/>
+      </c>
+      <c r="G58" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>── untagged ──</v>
+      </c>
+      <c r="B59" t="str">
+        <v/>
+      </c>
+      <c r="C59" t="str">
+        <v/>
+      </c>
+      <c r="D59" t="str">
+        <v/>
+      </c>
+      <c r="E59" t="str">
+        <v/>
+      </c>
+      <c r="F59" t="str">
+        <v/>
+      </c>
+      <c r="G59" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
         <v>123623963915635</v>
       </c>
-      <c r="B58" t="str">
+      <c r="B60" t="str">
         <v>spark only</v>
       </c>
-      <c r="C58">
-        <v>0</v>
-      </c>
-      <c r="D58">
-        <v>0</v>
-      </c>
-      <c r="E58">
+      <c r="C60">
+        <v>0</v>
+      </c>
+      <c r="D60">
+        <v>0</v>
+      </c>
+      <c r="E60">
         <v>0.01</v>
       </c>
-      <c r="F58">
+      <c r="F60">
         <v>0.01</v>
       </c>
-    </row>
-    <row r="59">
-      <c r="A59">
+      <c r="G60" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
         <v>90000000000000000000</v>
       </c>
-      <c r="B59" t="str">
+      <c r="B61" t="str">
         <v>spark only</v>
       </c>
-      <c r="C59">
+      <c r="C61">
         <v>0.06</v>
       </c>
-      <c r="D59">
+      <c r="D61">
         <v>0.01</v>
       </c>
-      <c r="E59">
-        <v>0</v>
-      </c>
-      <c r="F59">
+      <c r="E61">
+        <v>0</v>
+      </c>
+      <c r="F61">
         <v>0.07</v>
       </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="str">
+      <c r="G61" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
         <v>untagged</v>
       </c>
-      <c r="B60" t="str">
-        <v>both</v>
-      </c>
-      <c r="C60">
+      <c r="B62" t="str">
+        <v>both</v>
+      </c>
+      <c r="C62">
         <v>-140741.72</v>
       </c>
-      <c r="D60">
+      <c r="D62">
         <v>-224458.55</v>
       </c>
-      <c r="E60">
+      <c r="E62">
         <v>-232171.91</v>
       </c>
-      <c r="F60">
+      <c r="F62">
         <v>-597372.18</v>
+      </c>
+      <c r="G62" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F60"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G62"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/dune-results/dr_comparison_2026.xlsx
+++ b/dune-results/dr_comparison_2026.xlsx
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G60"/>
+  <dimension ref="A1:G70"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="13.83203125" customWidth="1"/>
@@ -437,951 +437,951 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>0</v>
-      </c>
-      <c r="B2">
-        <v>79854.22</v>
-      </c>
-      <c r="C2">
-        <v>65755.52</v>
-      </c>
-      <c r="D2">
-        <v>73485.07</v>
+      <c r="A2" t="str">
+        <v>0 (spUSDC)</v>
+      </c>
+      <c r="B2" t="str">
+        <v/>
+      </c>
+      <c r="C2" t="str">
+        <v/>
+      </c>
+      <c r="D2" t="str">
+        <v/>
       </c>
       <c r="E2">
-        <v>75538.34</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>75621.85</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>370255</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>1</v>
+      <c r="A3" t="str">
+        <v>0 (stUSDS)</v>
       </c>
       <c r="B3">
-        <v>129628.4</v>
+        <v>0</v>
       </c>
       <c r="C3">
-        <v>96894.31</v>
+        <v>0</v>
       </c>
       <c r="D3">
-        <v>120811.71</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>116182.88</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>129037.41</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>592554.71</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>2</v>
+      <c r="A4" t="str">
+        <v>0 (sUSDC)</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>12.77</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>13.93</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>11.94</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>9.51</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>62.45</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>10</v>
-      </c>
-      <c r="B5" t="str">
-        <v/>
-      </c>
-      <c r="C5" t="str">
-        <v/>
-      </c>
-      <c r="D5" t="str">
-        <v/>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
+      <c r="A5" t="str">
+        <v>0 (sUSDS)</v>
+      </c>
+      <c r="B5">
+        <v>79746.04</v>
+      </c>
+      <c r="C5">
+        <v>65657.97</v>
+      </c>
+      <c r="D5">
+        <v>72961.66</v>
+      </c>
+      <c r="E5">
+        <v>74224.92</v>
+      </c>
+      <c r="F5">
+        <v>75156.16</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>367746.75</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>100</v>
-      </c>
-      <c r="B6" t="str">
-        <v/>
-      </c>
-      <c r="C6" t="str">
-        <v/>
-      </c>
-      <c r="D6" t="str">
-        <v/>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
+      <c r="A6" t="str">
+        <v>0 (USDS-CLE)</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>324.57</v>
+      </c>
+      <c r="E6">
+        <v>1121.44</v>
+      </c>
+      <c r="F6">
+        <v>340.38</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>1786.39</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>127</v>
+      <c r="A7" t="str">
+        <v>0 (USDS-SKY)</v>
       </c>
       <c r="B7">
-        <v>3037.15</v>
+        <v>93.87</v>
       </c>
       <c r="C7">
-        <v>2639.18</v>
+        <v>84.78</v>
       </c>
       <c r="D7">
-        <v>2167.44</v>
+        <v>4.31</v>
       </c>
       <c r="E7">
-        <v>1447.5</v>
+        <v>0.21</v>
       </c>
       <c r="F7">
-        <v>730.93</v>
+        <v>0.22</v>
       </c>
       <c r="G7">
-        <v>10022.2</v>
+        <v>183.39</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>128</v>
+      <c r="A8" t="str">
+        <v>0 (USDS-SPK)</v>
       </c>
       <c r="B8">
-        <v>826847.7</v>
+        <v>0</v>
       </c>
       <c r="C8">
-        <v>837591.56</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>1199709.46</v>
+        <v>180.6</v>
       </c>
       <c r="E8">
-        <v>1321957.96</v>
+        <v>179.83</v>
       </c>
       <c r="F8">
-        <v>1461137.84</v>
+        <v>115.58</v>
       </c>
       <c r="G8">
-        <v>5647244.52</v>
+        <v>476.01</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>129</v>
+      <c r="A9" t="str">
+        <v>1 (stUSDS)</v>
       </c>
       <c r="B9">
-        <v>1.03</v>
+        <v>1800.55</v>
       </c>
       <c r="C9">
-        <v>0.52</v>
+        <v>3037.92</v>
       </c>
       <c r="D9">
-        <v>0.67</v>
+        <v>2945.79</v>
       </c>
       <c r="E9">
-        <v>0.77</v>
+        <v>3010.98</v>
       </c>
       <c r="F9">
-        <v>1.13</v>
+        <v>3711.55</v>
       </c>
       <c r="G9">
-        <v>4.12</v>
+        <v>14506.79</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>170</v>
+      <c r="A10" t="str">
+        <v>1 (sUSDS)</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>81433.39</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>66656.73</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>97033.4</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>94312.71</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>104095.73</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>443531.96</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>171</v>
+      <c r="A11" t="str">
+        <v>1 (USDS-CLE)</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>5139.57</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>4193.83</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>6259.94</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>5552.85</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>8195.2</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>29341.39</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>182</v>
+      <c r="A12" t="str">
+        <v>1 (USDS-SKY)</v>
       </c>
       <c r="B12">
-        <v>0.01</v>
+        <v>26939.34</v>
       </c>
       <c r="C12">
-        <v>0.01</v>
+        <v>5782.4</v>
       </c>
       <c r="D12">
-        <v>0.01</v>
+        <v>2741.32</v>
       </c>
       <c r="E12">
-        <v>0.01</v>
+        <v>1747.61</v>
       </c>
       <c r="F12">
-        <v>0.01</v>
+        <v>1012.75</v>
       </c>
       <c r="G12">
-        <v>0.05</v>
+        <v>38223.42</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>183</v>
+      <c r="A13" t="str">
+        <v>1 (USDS-SPK)</v>
       </c>
       <c r="B13">
-        <v>21333.38</v>
+        <v>14315.55</v>
       </c>
       <c r="C13">
-        <v>13278.93</v>
+        <v>17223.43</v>
       </c>
       <c r="D13">
-        <v>11113.76</v>
+        <v>11831.25</v>
       </c>
       <c r="E13">
-        <v>9912.97</v>
+        <v>11558.72</v>
       </c>
       <c r="F13">
-        <v>11847.6</v>
+        <v>12022.19</v>
       </c>
       <c r="G13">
-        <v>67486.64</v>
+        <v>66951.14</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>186</v>
+        <v>2</v>
       </c>
       <c r="B14">
-        <v>467.21</v>
+        <v>0</v>
       </c>
       <c r="C14">
-        <v>638.59</v>
+        <v>0</v>
       </c>
       <c r="D14">
-        <v>1188.8</v>
+        <v>0</v>
       </c>
       <c r="E14">
-        <v>1386.57</v>
+        <v>0</v>
       </c>
       <c r="F14">
-        <v>1241.16</v>
+        <v>0</v>
       </c>
       <c r="G14">
-        <v>4922.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>188</v>
-      </c>
-      <c r="B15">
-        <v>475.33</v>
-      </c>
-      <c r="C15">
-        <v>108.27</v>
-      </c>
-      <c r="D15">
-        <v>7201.39</v>
-      </c>
-      <c r="E15">
-        <v>14582.19</v>
-      </c>
-      <c r="F15">
-        <v>11608.11</v>
+        <v>10</v>
+      </c>
+      <c r="B15" t="str">
+        <v/>
+      </c>
+      <c r="C15" t="str">
+        <v/>
+      </c>
+      <c r="D15" t="str">
+        <v/>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
       </c>
       <c r="G15">
-        <v>33975.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>190</v>
-      </c>
-      <c r="B16">
-        <v>10427.71</v>
-      </c>
-      <c r="C16">
-        <v>5314.13</v>
-      </c>
-      <c r="D16">
-        <v>4209.1</v>
-      </c>
-      <c r="E16">
-        <v>2912.07</v>
-      </c>
-      <c r="F16">
-        <v>2740.89</v>
+        <v>100</v>
+      </c>
+      <c r="B16" t="str">
+        <v/>
+      </c>
+      <c r="C16" t="str">
+        <v/>
+      </c>
+      <c r="D16" t="str">
+        <v/>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v/>
       </c>
       <c r="G16">
-        <v>25603.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>191</v>
+        <v>127</v>
       </c>
       <c r="B17">
-        <v>3326.25</v>
+        <v>3037.15</v>
       </c>
       <c r="C17">
-        <v>5352.96</v>
+        <v>2639.18</v>
       </c>
       <c r="D17">
-        <v>8218.73</v>
+        <v>2167.44</v>
       </c>
       <c r="E17">
-        <v>12123.38</v>
+        <v>1447.5</v>
       </c>
       <c r="F17">
-        <v>23241.91</v>
+        <v>730.93</v>
       </c>
       <c r="G17">
-        <v>52263.23</v>
+        <v>10022.2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>192</v>
+        <v>128</v>
       </c>
       <c r="B18">
-        <v>22700.54</v>
+        <v>826847.7</v>
       </c>
       <c r="C18">
-        <v>16725.41</v>
+        <v>837591.56</v>
       </c>
       <c r="D18">
-        <v>19342.47</v>
+        <v>1199709.46</v>
       </c>
       <c r="E18">
-        <v>15097.77</v>
+        <v>1321957.96</v>
       </c>
       <c r="F18">
-        <v>10576.24</v>
+        <v>1461137.84</v>
       </c>
       <c r="G18">
-        <v>84442.43</v>
+        <v>5647244.52</v>
       </c>
     </row>
     <row r="19">
       <c r="A19">
-        <v>194</v>
+        <v>129</v>
       </c>
       <c r="B19">
-        <v>1.99</v>
+        <v>1.03</v>
       </c>
       <c r="C19">
-        <v>1.7</v>
+        <v>0.52</v>
       </c>
       <c r="D19">
-        <v>1.88</v>
+        <v>0.67</v>
       </c>
       <c r="E19">
-        <v>1.72</v>
+        <v>0.77</v>
       </c>
       <c r="F19">
-        <v>1.75</v>
+        <v>1.13</v>
       </c>
       <c r="G19">
-        <v>9.04</v>
+        <v>4.12</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>195</v>
+        <v>170</v>
       </c>
       <c r="B20">
-        <v>1554.29</v>
+        <v>0</v>
       </c>
       <c r="C20">
-        <v>669.49</v>
+        <v>0</v>
       </c>
       <c r="D20">
-        <v>3049.96</v>
+        <v>0</v>
       </c>
       <c r="E20">
-        <v>1990.3</v>
+        <v>0</v>
       </c>
       <c r="F20">
-        <v>1235.01</v>
+        <v>0</v>
       </c>
       <c r="G20">
-        <v>8499.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <v>196</v>
+        <v>171</v>
       </c>
       <c r="B21">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="C21">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="D21">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E21">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="F21">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G21">
-        <v>0.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>197</v>
+        <v>182</v>
       </c>
       <c r="B22">
-        <v>6824.99</v>
+        <v>0.01</v>
       </c>
       <c r="C22">
-        <v>6314.15</v>
+        <v>0.01</v>
       </c>
       <c r="D22">
-        <v>5576.07</v>
+        <v>0.01</v>
       </c>
       <c r="E22">
-        <v>8508.93</v>
+        <v>0.01</v>
       </c>
       <c r="F22">
-        <v>10729.88</v>
+        <v>0.01</v>
       </c>
       <c r="G22">
-        <v>37954.02</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>198</v>
+        <v>183</v>
       </c>
       <c r="B23">
-        <v>0.02</v>
+        <v>21333.38</v>
       </c>
       <c r="C23">
-        <v>0.02</v>
+        <v>13278.93</v>
       </c>
       <c r="D23">
-        <v>0.02</v>
+        <v>11113.76</v>
       </c>
       <c r="E23">
-        <v>0.02</v>
+        <v>9912.97</v>
       </c>
       <c r="F23">
-        <v>0.02</v>
+        <v>11847.6</v>
       </c>
       <c r="G23">
-        <v>0.1</v>
+        <v>67486.64</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>200</v>
+        <v>186</v>
       </c>
       <c r="B24">
-        <v>1.96</v>
+        <v>467.21</v>
       </c>
       <c r="C24">
-        <v>0.65</v>
+        <v>638.59</v>
       </c>
       <c r="D24">
-        <v>5.79</v>
+        <v>1188.8</v>
       </c>
       <c r="E24">
-        <v>32.59</v>
+        <v>1386.57</v>
       </c>
       <c r="F24">
-        <v>91.6</v>
+        <v>1241.16</v>
       </c>
       <c r="G24">
-        <v>132.59</v>
+        <v>4922.33</v>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <v>202</v>
+        <v>188</v>
       </c>
       <c r="B25">
-        <v>28.54</v>
+        <v>475.33</v>
       </c>
       <c r="C25">
-        <v>32.89</v>
+        <v>108.27</v>
       </c>
       <c r="D25">
-        <v>42.56</v>
+        <v>7201.39</v>
       </c>
       <c r="E25">
-        <v>39.75</v>
+        <v>14582.19</v>
       </c>
       <c r="F25">
-        <v>33.27</v>
+        <v>11608.11</v>
       </c>
       <c r="G25">
-        <v>177.01</v>
+        <v>33975.29</v>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <v>204</v>
-      </c>
-      <c r="B26" t="str">
-        <v/>
+        <v>190</v>
+      </c>
+      <c r="B26">
+        <v>10427.71</v>
       </c>
       <c r="C26">
-        <v>1.61</v>
+        <v>5314.13</v>
       </c>
       <c r="D26">
-        <v>16.91</v>
+        <v>4209.1</v>
       </c>
       <c r="E26">
-        <v>34.05</v>
+        <v>2912.07</v>
       </c>
       <c r="F26">
-        <v>30.45</v>
+        <v>2740.89</v>
       </c>
       <c r="G26">
-        <v>83.02</v>
+        <v>25603.9</v>
       </c>
     </row>
     <row r="27">
       <c r="A27">
-        <v>205</v>
+        <v>191</v>
       </c>
       <c r="B27">
-        <v>0</v>
+        <v>3326.25</v>
       </c>
       <c r="C27">
-        <v>0.02</v>
+        <v>5352.96</v>
       </c>
       <c r="D27">
-        <v>0.2</v>
+        <v>8218.73</v>
       </c>
       <c r="E27">
-        <v>0.21</v>
+        <v>12123.38</v>
       </c>
       <c r="F27">
-        <v>0.21</v>
+        <v>23241.91</v>
       </c>
       <c r="G27">
-        <v>0.64</v>
+        <v>52263.23</v>
       </c>
     </row>
     <row r="28">
       <c r="A28">
-        <v>206</v>
-      </c>
-      <c r="B28" t="str">
-        <v/>
-      </c>
-      <c r="C28" t="str">
-        <v/>
-      </c>
-      <c r="D28" t="str">
-        <v/>
-      </c>
-      <c r="E28" t="str">
-        <v/>
+        <v>192</v>
+      </c>
+      <c r="B28">
+        <v>22700.54</v>
+      </c>
+      <c r="C28">
+        <v>16725.41</v>
+      </c>
+      <c r="D28">
+        <v>19342.47</v>
+      </c>
+      <c r="E28">
+        <v>15097.77</v>
       </c>
       <c r="F28">
-        <v>0</v>
+        <v>10576.24</v>
       </c>
       <c r="G28">
-        <v>0</v>
+        <v>84442.43</v>
       </c>
     </row>
     <row r="29">
       <c r="A29">
-        <v>214</v>
-      </c>
-      <c r="B29" t="str">
-        <v/>
-      </c>
-      <c r="C29" t="str">
-        <v/>
-      </c>
-      <c r="D29" t="str">
-        <v/>
-      </c>
-      <c r="E29" t="str">
-        <v/>
+        <v>194</v>
+      </c>
+      <c r="B29">
+        <v>1.99</v>
+      </c>
+      <c r="C29">
+        <v>1.7</v>
+      </c>
+      <c r="D29">
+        <v>1.88</v>
+      </c>
+      <c r="E29">
+        <v>1.72</v>
       </c>
       <c r="F29">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="G29">
-        <v>0</v>
+        <v>9.04</v>
       </c>
     </row>
     <row r="30">
       <c r="A30">
-        <v>216</v>
-      </c>
-      <c r="B30" t="str">
-        <v/>
-      </c>
-      <c r="C30" t="str">
-        <v/>
+        <v>195</v>
+      </c>
+      <c r="B30">
+        <v>1554.29</v>
+      </c>
+      <c r="C30">
+        <v>669.49</v>
       </c>
       <c r="D30">
-        <v>86.77</v>
+        <v>3049.96</v>
       </c>
       <c r="E30">
-        <v>151.21</v>
+        <v>1990.3</v>
       </c>
       <c r="F30">
-        <v>189.04</v>
+        <v>1235.01</v>
       </c>
       <c r="G30">
-        <v>427.02</v>
+        <v>8499.05</v>
       </c>
     </row>
     <row r="31">
       <c r="A31">
-        <v>219</v>
-      </c>
-      <c r="B31" t="str">
-        <v/>
-      </c>
-      <c r="C31" t="str">
-        <v/>
-      </c>
-      <c r="D31" t="str">
-        <v/>
+        <v>196</v>
+      </c>
+      <c r="B31">
+        <v>0.01</v>
+      </c>
+      <c r="C31">
+        <v>0.09</v>
+      </c>
+      <c r="D31">
+        <v>0.1</v>
       </c>
       <c r="E31">
-        <v>14.26</v>
-      </c>
-      <c r="F31" t="str">
-        <v/>
+        <v>0.1</v>
+      </c>
+      <c r="F31">
+        <v>0.1</v>
       </c>
       <c r="G31">
-        <v>14.26</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="32">
       <c r="A32">
-        <v>223</v>
-      </c>
-      <c r="B32" t="str">
-        <v/>
-      </c>
-      <c r="C32" t="str">
-        <v/>
-      </c>
-      <c r="D32" t="str">
-        <v/>
-      </c>
-      <c r="E32" t="str">
-        <v/>
+        <v>197</v>
+      </c>
+      <c r="B32">
+        <v>6824.99</v>
+      </c>
+      <c r="C32">
+        <v>6314.15</v>
+      </c>
+      <c r="D32">
+        <v>5576.07</v>
+      </c>
+      <c r="E32">
+        <v>8508.93</v>
       </c>
       <c r="F32">
-        <v>0</v>
+        <v>10729.88</v>
       </c>
       <c r="G32">
-        <v>0</v>
+        <v>37954.02</v>
       </c>
     </row>
     <row r="33">
       <c r="A33">
-        <v>224</v>
-      </c>
-      <c r="B33" t="str">
-        <v/>
-      </c>
-      <c r="C33" t="str">
-        <v/>
-      </c>
-      <c r="D33" t="str">
-        <v/>
-      </c>
-      <c r="E33" t="str">
-        <v/>
+        <v>198</v>
+      </c>
+      <c r="B33">
+        <v>0.02</v>
+      </c>
+      <c r="C33">
+        <v>0.02</v>
+      </c>
+      <c r="D33">
+        <v>0.02</v>
+      </c>
+      <c r="E33">
+        <v>0.02</v>
       </c>
       <c r="F33">
-        <v>4582.17</v>
+        <v>0.02</v>
       </c>
       <c r="G33">
-        <v>4582.17</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34">
-        <v>303</v>
+        <v>200</v>
       </c>
       <c r="B34">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="C34">
-        <v>0</v>
+        <v>0.65</v>
       </c>
       <c r="D34">
-        <v>0</v>
+        <v>5.79</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>32.59</v>
       </c>
       <c r="F34">
-        <v>0</v>
+        <v>91.6</v>
       </c>
       <c r="G34">
-        <v>0</v>
+        <v>132.59</v>
       </c>
     </row>
     <row r="35">
       <c r="A35">
-        <v>555</v>
+        <v>202</v>
       </c>
       <c r="B35">
-        <v>0</v>
+        <v>28.54</v>
       </c>
       <c r="C35">
-        <v>0</v>
+        <v>32.89</v>
       </c>
       <c r="D35">
-        <v>0</v>
+        <v>42.56</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>39.75</v>
       </c>
       <c r="F35">
-        <v>0</v>
+        <v>33.27</v>
       </c>
       <c r="G35">
-        <v>0</v>
+        <v>177.01</v>
       </c>
     </row>
     <row r="36">
       <c r="A36">
-        <v>1001</v>
-      </c>
-      <c r="B36">
-        <v>2254.8</v>
+        <v>204</v>
+      </c>
+      <c r="B36" t="str">
+        <v/>
       </c>
       <c r="C36">
-        <v>1601.44</v>
+        <v>1.61</v>
       </c>
       <c r="D36">
-        <v>1655.49</v>
+        <v>16.91</v>
       </c>
       <c r="E36">
-        <v>1433.94</v>
+        <v>34.05</v>
       </c>
       <c r="F36">
-        <v>912.57</v>
+        <v>30.45</v>
       </c>
       <c r="G36">
-        <v>7858.24</v>
+        <v>83.02</v>
       </c>
     </row>
     <row r="37">
       <c r="A37">
-        <v>1002</v>
+        <v>205</v>
       </c>
       <c r="B37">
-        <v>1969.51</v>
+        <v>0</v>
       </c>
       <c r="C37">
-        <v>2970.51</v>
+        <v>0.02</v>
       </c>
       <c r="D37">
-        <v>29195.53</v>
+        <v>0.2</v>
       </c>
       <c r="E37">
-        <v>28955.22</v>
+        <v>0.21</v>
       </c>
       <c r="F37">
-        <v>33175.15</v>
+        <v>0.21</v>
       </c>
       <c r="G37">
-        <v>96265.92</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="38">
       <c r="A38">
-        <v>1004</v>
-      </c>
-      <c r="B38">
-        <v>0.01</v>
-      </c>
-      <c r="C38">
-        <v>0</v>
-      </c>
-      <c r="D38">
-        <v>0.01</v>
-      </c>
-      <c r="E38">
-        <v>0.01</v>
+        <v>206</v>
+      </c>
+      <c r="B38" t="str">
+        <v/>
+      </c>
+      <c r="C38" t="str">
+        <v/>
+      </c>
+      <c r="D38" t="str">
+        <v/>
+      </c>
+      <c r="E38" t="str">
+        <v/>
       </c>
       <c r="F38">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="G38">
-        <v>0.04</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39">
-        <v>1007</v>
-      </c>
-      <c r="B39">
-        <v>10082.51</v>
-      </c>
-      <c r="C39">
-        <v>13745.06</v>
-      </c>
-      <c r="D39">
-        <v>15859.43</v>
-      </c>
-      <c r="E39">
-        <v>14112.17</v>
+        <v>214</v>
+      </c>
+      <c r="B39" t="str">
+        <v/>
+      </c>
+      <c r="C39" t="str">
+        <v/>
+      </c>
+      <c r="D39" t="str">
+        <v/>
+      </c>
+      <c r="E39" t="str">
+        <v/>
       </c>
       <c r="F39">
-        <v>10762.39</v>
+        <v>0</v>
       </c>
       <c r="G39">
-        <v>64561.56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40">
-        <v>1015</v>
-      </c>
-      <c r="B40">
-        <v>0</v>
-      </c>
-      <c r="C40">
-        <v>0</v>
+        <v>216</v>
+      </c>
+      <c r="B40" t="str">
+        <v/>
+      </c>
+      <c r="C40" t="str">
+        <v/>
       </c>
       <c r="D40">
-        <v>0</v>
+        <v>86.77</v>
       </c>
       <c r="E40">
-        <v>0</v>
+        <v>151.21</v>
       </c>
       <c r="F40">
-        <v>0</v>
+        <v>189.04</v>
       </c>
       <c r="G40">
-        <v>0</v>
+        <v>427.02</v>
       </c>
     </row>
     <row r="41">
       <c r="A41">
-        <v>1016</v>
-      </c>
-      <c r="B41">
-        <v>1201.05</v>
-      </c>
-      <c r="C41">
-        <v>167.54</v>
-      </c>
-      <c r="D41">
-        <v>8.98</v>
+        <v>219</v>
+      </c>
+      <c r="B41" t="str">
+        <v/>
+      </c>
+      <c r="C41" t="str">
+        <v/>
+      </c>
+      <c r="D41" t="str">
+        <v/>
       </c>
       <c r="E41">
-        <v>0.59</v>
+        <v>14.26</v>
       </c>
       <c r="F41" t="str">
         <v/>
       </c>
       <c r="G41">
-        <v>1378.16</v>
+        <v>14.26</v>
       </c>
     </row>
     <row r="42">
       <c r="A42">
-        <v>1017</v>
-      </c>
-      <c r="B42">
-        <v>215.45</v>
-      </c>
-      <c r="C42">
-        <v>140.34</v>
-      </c>
-      <c r="D42">
-        <v>148.1</v>
-      </c>
-      <c r="E42">
-        <v>85.99</v>
+        <v>223</v>
+      </c>
+      <c r="B42" t="str">
+        <v/>
+      </c>
+      <c r="C42" t="str">
+        <v/>
+      </c>
+      <c r="D42" t="str">
+        <v/>
+      </c>
+      <c r="E42" t="str">
+        <v/>
       </c>
       <c r="F42">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="G42">
-        <v>593.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43">
-        <v>2000</v>
+        <v>224</v>
       </c>
       <c r="B43" t="str">
         <v/>
@@ -1392,22 +1392,22 @@
       <c r="D43" t="str">
         <v/>
       </c>
-      <c r="E43">
-        <v>0</v>
+      <c r="E43" t="str">
+        <v/>
       </c>
       <c r="F43">
-        <v>0</v>
+        <v>4582.17</v>
       </c>
       <c r="G43">
-        <v>0</v>
+        <v>4582.17</v>
       </c>
     </row>
     <row r="44">
       <c r="A44">
-        <v>2001</v>
-      </c>
-      <c r="B44" t="str">
-        <v/>
+        <v>303</v>
+      </c>
+      <c r="B44">
+        <v>0</v>
       </c>
       <c r="C44">
         <v>0</v>
@@ -1416,142 +1416,142 @@
         <v>0</v>
       </c>
       <c r="E44">
-        <v>82.24</v>
+        <v>0</v>
       </c>
       <c r="F44">
-        <v>8467.99</v>
+        <v>0</v>
       </c>
       <c r="G44">
-        <v>8550.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45">
-        <v>2002</v>
-      </c>
-      <c r="B45" t="str">
-        <v/>
-      </c>
-      <c r="C45" t="str">
-        <v/>
+        <v>555</v>
+      </c>
+      <c r="B45">
+        <v>0</v>
+      </c>
+      <c r="C45">
+        <v>0</v>
       </c>
       <c r="D45">
-        <v>174574.28</v>
+        <v>0</v>
       </c>
       <c r="E45">
-        <v>116737.37</v>
+        <v>0</v>
       </c>
       <c r="F45">
         <v>0</v>
       </c>
       <c r="G45">
-        <v>291311.65</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46">
-        <v>2003</v>
-      </c>
-      <c r="B46" t="str">
-        <v/>
-      </c>
-      <c r="C46" t="str">
-        <v/>
-      </c>
-      <c r="D46" t="str">
-        <v/>
+        <v>1001</v>
+      </c>
+      <c r="B46">
+        <v>2254.8</v>
+      </c>
+      <c r="C46">
+        <v>1601.44</v>
+      </c>
+      <c r="D46">
+        <v>1655.49</v>
       </c>
       <c r="E46">
-        <v>0</v>
+        <v>1433.94</v>
       </c>
       <c r="F46">
-        <v>0</v>
+        <v>912.57</v>
       </c>
       <c r="G46">
-        <v>0</v>
+        <v>7858.24</v>
       </c>
     </row>
     <row r="47">
       <c r="A47">
-        <v>2005</v>
-      </c>
-      <c r="B47" t="str">
-        <v/>
-      </c>
-      <c r="C47" t="str">
-        <v/>
+        <v>1002</v>
+      </c>
+      <c r="B47">
+        <v>1969.51</v>
+      </c>
+      <c r="C47">
+        <v>2970.51</v>
       </c>
       <c r="D47">
-        <v>17144.97</v>
+        <v>29195.53</v>
       </c>
       <c r="E47">
-        <v>8259.88</v>
-      </c>
-      <c r="F47" t="str">
-        <v/>
+        <v>28955.22</v>
+      </c>
+      <c r="F47">
+        <v>33175.15</v>
       </c>
       <c r="G47">
-        <v>25404.85</v>
+        <v>96265.92</v>
       </c>
     </row>
     <row r="48">
       <c r="A48">
-        <v>2008</v>
-      </c>
-      <c r="B48" t="str">
-        <v/>
-      </c>
-      <c r="C48" t="str">
-        <v/>
-      </c>
-      <c r="D48" t="str">
-        <v/>
-      </c>
-      <c r="E48" t="str">
-        <v/>
+        <v>1004</v>
+      </c>
+      <c r="B48">
+        <v>0.01</v>
+      </c>
+      <c r="C48">
+        <v>0</v>
+      </c>
+      <c r="D48">
+        <v>0.01</v>
+      </c>
+      <c r="E48">
+        <v>0.01</v>
       </c>
       <c r="F48">
-        <v>12035.78</v>
+        <v>0.01</v>
       </c>
       <c r="G48">
-        <v>12035.78</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="49">
       <c r="A49">
-        <v>2222</v>
-      </c>
-      <c r="B49" t="str">
-        <v/>
-      </c>
-      <c r="C49" t="str">
-        <v/>
-      </c>
-      <c r="D49" t="str">
-        <v/>
+        <v>1007</v>
+      </c>
+      <c r="B49">
+        <v>10082.51</v>
+      </c>
+      <c r="C49">
+        <v>13745.06</v>
+      </c>
+      <c r="D49">
+        <v>15859.43</v>
       </c>
       <c r="E49">
-        <v>10.68</v>
+        <v>14112.17</v>
       </c>
       <c r="F49">
-        <v>14.75</v>
+        <v>10762.39</v>
       </c>
       <c r="G49">
-        <v>25.43</v>
+        <v>64561.56</v>
       </c>
     </row>
     <row r="50">
       <c r="A50">
-        <v>3000</v>
-      </c>
-      <c r="B50" t="str">
-        <v/>
-      </c>
-      <c r="C50" t="str">
-        <v/>
-      </c>
-      <c r="D50" t="str">
-        <v/>
+        <v>1015</v>
+      </c>
+      <c r="B50">
+        <v>0</v>
+      </c>
+      <c r="C50">
+        <v>0</v>
+      </c>
+      <c r="D50">
+        <v>0</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -1565,53 +1565,53 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>3001</v>
-      </c>
-      <c r="B51" t="str">
-        <v/>
-      </c>
-      <c r="C51" t="str">
-        <v/>
-      </c>
-      <c r="D51" t="str">
-        <v/>
-      </c>
-      <c r="E51" t="str">
-        <v/>
-      </c>
-      <c r="F51">
-        <v>0</v>
+        <v>1016</v>
+      </c>
+      <c r="B51">
+        <v>1201.05</v>
+      </c>
+      <c r="C51">
+        <v>167.54</v>
+      </c>
+      <c r="D51">
+        <v>8.98</v>
+      </c>
+      <c r="E51">
+        <v>0.59</v>
+      </c>
+      <c r="F51" t="str">
+        <v/>
       </c>
       <c r="G51">
-        <v>0</v>
+        <v>1378.16</v>
       </c>
     </row>
     <row r="52">
       <c r="A52">
-        <v>3333</v>
+        <v>1017</v>
       </c>
       <c r="B52">
-        <v>0.71</v>
+        <v>215.45</v>
       </c>
       <c r="C52">
-        <v>0.41</v>
+        <v>140.34</v>
       </c>
       <c r="D52">
-        <v>0.48</v>
+        <v>148.1</v>
       </c>
       <c r="E52">
-        <v>0.49</v>
+        <v>85.99</v>
       </c>
       <c r="F52">
-        <v>0.48</v>
+        <v>3.52</v>
       </c>
       <c r="G52">
-        <v>2.57</v>
+        <v>593.4</v>
       </c>
     </row>
     <row r="53">
       <c r="A53">
-        <v>4011</v>
+        <v>2000</v>
       </c>
       <c r="B53" t="str">
         <v/>
@@ -1622,88 +1622,88 @@
       <c r="D53" t="str">
         <v/>
       </c>
-      <c r="E53" t="str">
-        <v/>
+      <c r="E53">
+        <v>0</v>
       </c>
       <c r="F53">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="G53">
-        <v>0.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54">
-        <v>4012</v>
+        <v>2001</v>
       </c>
       <c r="B54" t="str">
         <v/>
       </c>
-      <c r="C54" t="str">
-        <v/>
-      </c>
-      <c r="D54" t="str">
-        <v/>
-      </c>
-      <c r="E54" t="str">
-        <v/>
+      <c r="C54">
+        <v>0</v>
+      </c>
+      <c r="D54">
+        <v>0</v>
+      </c>
+      <c r="E54">
+        <v>82.24</v>
       </c>
       <c r="F54">
-        <v>0</v>
+        <v>8467.99</v>
       </c>
       <c r="G54">
-        <v>0</v>
+        <v>8550.23</v>
       </c>
     </row>
     <row r="55">
       <c r="A55">
-        <v>9998</v>
-      </c>
-      <c r="B55">
-        <v>0</v>
-      </c>
-      <c r="C55">
-        <v>0</v>
+        <v>2002</v>
+      </c>
+      <c r="B55" t="str">
+        <v/>
+      </c>
+      <c r="C55" t="str">
+        <v/>
       </c>
       <c r="D55">
-        <v>0</v>
+        <v>174574.28</v>
       </c>
       <c r="E55">
-        <v>0</v>
+        <v>116737.37</v>
       </c>
       <c r="F55">
         <v>0</v>
       </c>
       <c r="G55">
-        <v>0</v>
+        <v>291311.65</v>
       </c>
     </row>
     <row r="56">
       <c r="A56">
-        <v>13425</v>
-      </c>
-      <c r="B56">
-        <v>858.01</v>
-      </c>
-      <c r="C56">
-        <v>774.97</v>
-      </c>
-      <c r="D56">
-        <v>858.01</v>
+        <v>2003</v>
+      </c>
+      <c r="B56" t="str">
+        <v/>
+      </c>
+      <c r="C56" t="str">
+        <v/>
+      </c>
+      <c r="D56" t="str">
+        <v/>
       </c>
       <c r="E56">
-        <v>641.16</v>
+        <v>0</v>
       </c>
       <c r="F56">
-        <v>9.67</v>
+        <v>0</v>
       </c>
       <c r="G56">
-        <v>3141.82</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="str">
-        <v/>
+      <c r="A57">
+        <v>2005</v>
       </c>
       <c r="B57" t="str">
         <v/>
@@ -1711,22 +1711,22 @@
       <c r="C57" t="str">
         <v/>
       </c>
-      <c r="D57" t="str">
-        <v/>
-      </c>
-      <c r="E57" t="str">
-        <v/>
+      <c r="D57">
+        <v>17144.97</v>
+      </c>
+      <c r="E57">
+        <v>8259.88</v>
       </c>
       <c r="F57" t="str">
         <v/>
       </c>
-      <c r="G57" t="str">
-        <v/>
+      <c r="G57">
+        <v>25404.85</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="str">
-        <v>── untagged ──</v>
+      <c r="A58">
+        <v>2008</v>
       </c>
       <c r="B58" t="str">
         <v/>
@@ -1740,69 +1740,299 @@
       <c r="E58" t="str">
         <v/>
       </c>
-      <c r="F58" t="str">
-        <v/>
-      </c>
-      <c r="G58" t="str">
-        <v/>
+      <c r="F58">
+        <v>12035.78</v>
+      </c>
+      <c r="G58">
+        <v>12035.78</v>
       </c>
     </row>
     <row r="59">
       <c r="A59">
-        <v>-999999</v>
-      </c>
-      <c r="B59">
-        <v>17418.88</v>
-      </c>
-      <c r="C59">
-        <v>10907.25</v>
-      </c>
-      <c r="D59">
-        <v>25305.28</v>
+        <v>2222</v>
+      </c>
+      <c r="B59" t="str">
+        <v/>
+      </c>
+      <c r="C59" t="str">
+        <v/>
+      </c>
+      <c r="D59" t="str">
+        <v/>
       </c>
       <c r="E59">
-        <v>18026.83</v>
+        <v>10.68</v>
       </c>
       <c r="F59">
-        <v>15780.23</v>
+        <v>14.75</v>
       </c>
       <c r="G59">
-        <v>87438.47</v>
+        <v>25.43</v>
       </c>
     </row>
     <row r="60">
       <c r="A60">
+        <v>3000</v>
+      </c>
+      <c r="B60" t="str">
+        <v/>
+      </c>
+      <c r="C60" t="str">
+        <v/>
+      </c>
+      <c r="D60" t="str">
+        <v/>
+      </c>
+      <c r="E60">
+        <v>0</v>
+      </c>
+      <c r="F60">
+        <v>0</v>
+      </c>
+      <c r="G60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>3001</v>
+      </c>
+      <c r="B61" t="str">
+        <v/>
+      </c>
+      <c r="C61" t="str">
+        <v/>
+      </c>
+      <c r="D61" t="str">
+        <v/>
+      </c>
+      <c r="E61" t="str">
+        <v/>
+      </c>
+      <c r="F61">
+        <v>0</v>
+      </c>
+      <c r="G61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>3333</v>
+      </c>
+      <c r="B62">
+        <v>0.71</v>
+      </c>
+      <c r="C62">
+        <v>0.41</v>
+      </c>
+      <c r="D62">
+        <v>0.48</v>
+      </c>
+      <c r="E62">
+        <v>0.49</v>
+      </c>
+      <c r="F62">
+        <v>0.48</v>
+      </c>
+      <c r="G62">
+        <v>2.57</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>4011</v>
+      </c>
+      <c r="B63" t="str">
+        <v/>
+      </c>
+      <c r="C63" t="str">
+        <v/>
+      </c>
+      <c r="D63" t="str">
+        <v/>
+      </c>
+      <c r="E63" t="str">
+        <v/>
+      </c>
+      <c r="F63">
+        <v>0.01</v>
+      </c>
+      <c r="G63">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>4012</v>
+      </c>
+      <c r="B64" t="str">
+        <v/>
+      </c>
+      <c r="C64" t="str">
+        <v/>
+      </c>
+      <c r="D64" t="str">
+        <v/>
+      </c>
+      <c r="E64" t="str">
+        <v/>
+      </c>
+      <c r="F64">
+        <v>0</v>
+      </c>
+      <c r="G64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>9998</v>
+      </c>
+      <c r="B65">
+        <v>0</v>
+      </c>
+      <c r="C65">
+        <v>0</v>
+      </c>
+      <c r="D65">
+        <v>0</v>
+      </c>
+      <c r="E65">
+        <v>0</v>
+      </c>
+      <c r="F65">
+        <v>0</v>
+      </c>
+      <c r="G65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>13425</v>
+      </c>
+      <c r="B66">
+        <v>858.01</v>
+      </c>
+      <c r="C66">
+        <v>774.97</v>
+      </c>
+      <c r="D66">
+        <v>858.01</v>
+      </c>
+      <c r="E66">
+        <v>641.16</v>
+      </c>
+      <c r="F66">
+        <v>9.67</v>
+      </c>
+      <c r="G66">
+        <v>3141.82</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v/>
+      </c>
+      <c r="B67" t="str">
+        <v/>
+      </c>
+      <c r="C67" t="str">
+        <v/>
+      </c>
+      <c r="D67" t="str">
+        <v/>
+      </c>
+      <c r="E67" t="str">
+        <v/>
+      </c>
+      <c r="F67" t="str">
+        <v/>
+      </c>
+      <c r="G67" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>── untagged ──</v>
+      </c>
+      <c r="B68" t="str">
+        <v/>
+      </c>
+      <c r="C68" t="str">
+        <v/>
+      </c>
+      <c r="D68" t="str">
+        <v/>
+      </c>
+      <c r="E68" t="str">
+        <v/>
+      </c>
+      <c r="F68" t="str">
+        <v/>
+      </c>
+      <c r="G68" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>-999999</v>
+      </c>
+      <c r="B69">
+        <v>17418.88</v>
+      </c>
+      <c r="C69">
+        <v>10907.25</v>
+      </c>
+      <c r="D69">
+        <v>25305.28</v>
+      </c>
+      <c r="E69">
+        <v>18026.83</v>
+      </c>
+      <c r="F69">
+        <v>15780.23</v>
+      </c>
+      <c r="G69">
+        <v>87438.47</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
         <v>99</v>
       </c>
-      <c r="B60">
+      <c r="B70">
         <v>1602756.97</v>
       </c>
-      <c r="C60">
+      <c r="C70">
         <v>1541979.87</v>
       </c>
-      <c r="D60">
+      <c r="D70">
         <v>1790892.59</v>
       </c>
-      <c r="E60">
+      <c r="E70">
         <v>1722310.47</v>
       </c>
-      <c r="F60">
+      <c r="F70">
         <v>1895178.54</v>
       </c>
-      <c r="G60">
+      <c r="G70">
         <v>8553118.44</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G60"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G70"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G61"/>
+  <dimension ref="A1:G69"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="13.83203125" customWidth="1"/>
@@ -1837,894 +2067,894 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>0</v>
-      </c>
-      <c r="B2">
-        <v>79854.22</v>
-      </c>
-      <c r="C2">
-        <v>65755.52</v>
-      </c>
-      <c r="D2">
-        <v>73160.49</v>
+      <c r="A2" t="str">
+        <v>0 (spUSDC)</v>
+      </c>
+      <c r="B2" t="str">
+        <v/>
+      </c>
+      <c r="C2" t="str">
+        <v/>
+      </c>
+      <c r="D2" t="str">
+        <v/>
       </c>
       <c r="E2">
-        <v>74416.9</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>75281.45</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>368468.58</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>1</v>
+      <c r="A3" t="str">
+        <v>0 (stUSDS)</v>
       </c>
       <c r="B3">
-        <v>124488.83</v>
+        <v>0</v>
       </c>
       <c r="C3">
-        <v>92700.48</v>
+        <v>0</v>
       </c>
       <c r="D3">
-        <v>114551.76</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>110630.03</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>120842.22</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>563213.32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>2</v>
+      <c r="A4" t="str">
+        <v>0 (sUSDC)</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>12.77</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>13.93</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>11.94</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>9.51</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>62.45</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>126</v>
+      <c r="A5" t="str">
+        <v>0 (sUSDS)</v>
       </c>
       <c r="B5">
-        <v>106392.55</v>
+        <v>79746.04</v>
       </c>
       <c r="C5">
-        <v>114516.89</v>
+        <v>65657.97</v>
       </c>
       <c r="D5">
-        <v>122957.88</v>
+        <v>72961.66</v>
       </c>
       <c r="E5">
-        <v>115359.51</v>
+        <v>74224.91</v>
       </c>
       <c r="F5">
-        <v>118567.8</v>
+        <v>75156.15</v>
       </c>
       <c r="G5">
-        <v>577794.63</v>
+        <v>367746.73</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>127</v>
+      <c r="A6" t="str">
+        <v>0 (USDS-SKY)</v>
       </c>
       <c r="B6">
-        <v>3482.42</v>
+        <v>93.87</v>
       </c>
       <c r="C6">
-        <v>2847.77</v>
+        <v>84.78</v>
       </c>
       <c r="D6">
-        <v>2518.92</v>
+        <v>4.31</v>
       </c>
       <c r="E6">
-        <v>1845.23</v>
+        <v>0.21</v>
       </c>
       <c r="F6">
-        <v>903.41</v>
+        <v>0.22</v>
       </c>
       <c r="G6">
-        <v>11597.75</v>
+        <v>183.39</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>128</v>
+      <c r="A7" t="str">
+        <v>0 (USDS-SPK)</v>
       </c>
       <c r="B7">
-        <v>822783.59</v>
+        <v>0</v>
       </c>
       <c r="C7">
-        <v>833426.1</v>
+        <v>0</v>
       </c>
       <c r="D7">
-        <v>1200614.86</v>
+        <v>180.6</v>
       </c>
       <c r="E7">
-        <v>1323989.36</v>
+        <v>179.83</v>
       </c>
       <c r="F7">
-        <v>1462735.31</v>
+        <v>115.58</v>
       </c>
       <c r="G7">
-        <v>5643549.22</v>
+        <v>476.01</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>129</v>
+      <c r="A8" t="str">
+        <v>1 (stUSDS)</v>
       </c>
       <c r="B8">
-        <v>1.03</v>
+        <v>1800.55</v>
       </c>
       <c r="C8">
-        <v>0.52</v>
+        <v>3037.92</v>
       </c>
       <c r="D8">
-        <v>0.67</v>
+        <v>2945.79</v>
       </c>
       <c r="E8">
-        <v>0.77</v>
+        <v>3010.98</v>
       </c>
       <c r="F8">
-        <v>1.13</v>
+        <v>3711.55</v>
       </c>
       <c r="G8">
-        <v>4.12</v>
+        <v>14506.79</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>130</v>
+      <c r="A9" t="str">
+        <v>1 (sUSDS)</v>
       </c>
       <c r="B9">
-        <v>266.96</v>
+        <v>81433.39</v>
       </c>
       <c r="C9">
-        <v>252.94</v>
+        <v>66656.73</v>
       </c>
       <c r="D9">
-        <v>3701.44</v>
+        <v>97033.4</v>
       </c>
       <c r="E9">
-        <v>4353.38</v>
+        <v>94312.71</v>
       </c>
       <c r="F9">
-        <v>3885.67</v>
+        <v>104095.73</v>
       </c>
       <c r="G9">
-        <v>12460.39</v>
+        <v>443531.96</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>170</v>
+      <c r="A10" t="str">
+        <v>1 (USDS-SKY)</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>26939.34</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>5782.4</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>2741.32</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>1747.61</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>1012.75</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>38223.42</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>171</v>
+      <c r="A11" t="str">
+        <v>1 (USDS-SPK)</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>14315.55</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>17223.43</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>11831.25</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>11558.72</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>12022.19</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>66951.14</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>182</v>
+        <v>2</v>
       </c>
       <c r="B12">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="C12">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="D12">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="E12">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="F12">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="G12">
-        <v>0.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>183</v>
+        <v>126</v>
       </c>
       <c r="B13">
-        <v>21333.38</v>
+        <v>106392.55</v>
       </c>
       <c r="C13">
-        <v>13278.93</v>
+        <v>114516.89</v>
       </c>
       <c r="D13">
-        <v>11113.76</v>
+        <v>122957.88</v>
       </c>
       <c r="E13">
-        <v>9912.97</v>
+        <v>115359.51</v>
       </c>
       <c r="F13">
-        <v>11847.6</v>
+        <v>118567.8</v>
       </c>
       <c r="G13">
-        <v>67486.64</v>
+        <v>577794.63</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>186</v>
+        <v>127</v>
       </c>
       <c r="B14">
-        <v>467.21</v>
+        <v>3482.42</v>
       </c>
       <c r="C14">
-        <v>638.59</v>
+        <v>2847.77</v>
       </c>
       <c r="D14">
-        <v>1188.8</v>
+        <v>2518.92</v>
       </c>
       <c r="E14">
-        <v>1386.57</v>
+        <v>1845.23</v>
       </c>
       <c r="F14">
-        <v>1241.16</v>
+        <v>903.41</v>
       </c>
       <c r="G14">
-        <v>4922.33</v>
+        <v>11597.75</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>188</v>
+        <v>128</v>
       </c>
       <c r="B15">
-        <v>475.32</v>
+        <v>822783.59</v>
       </c>
       <c r="C15">
-        <v>108.26</v>
+        <v>833426.1</v>
       </c>
       <c r="D15">
-        <v>9656.79</v>
+        <v>1200614.86</v>
       </c>
       <c r="E15">
-        <v>14909.91</v>
+        <v>1323989.36</v>
       </c>
       <c r="F15">
-        <v>11718.71</v>
+        <v>1462735.31</v>
       </c>
       <c r="G15">
-        <v>36868.99</v>
+        <v>5643549.22</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>190</v>
+        <v>129</v>
       </c>
       <c r="B16">
-        <v>10427.71</v>
+        <v>1.03</v>
       </c>
       <c r="C16">
-        <v>5314.13</v>
+        <v>0.52</v>
       </c>
       <c r="D16">
-        <v>4209.1</v>
+        <v>0.67</v>
       </c>
       <c r="E16">
-        <v>2912.07</v>
+        <v>0.77</v>
       </c>
       <c r="F16">
-        <v>2740.89</v>
+        <v>1.13</v>
       </c>
       <c r="G16">
-        <v>25603.9</v>
+        <v>4.12</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>191</v>
+        <v>130</v>
       </c>
       <c r="B17">
-        <v>3326.25</v>
+        <v>266.96</v>
       </c>
       <c r="C17">
-        <v>5352.96</v>
+        <v>252.94</v>
       </c>
       <c r="D17">
-        <v>8218.73</v>
+        <v>3701.44</v>
       </c>
       <c r="E17">
-        <v>12123.38</v>
+        <v>4353.38</v>
       </c>
       <c r="F17">
-        <v>23241.91</v>
+        <v>3885.67</v>
       </c>
       <c r="G17">
-        <v>52263.23</v>
+        <v>12460.39</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>192</v>
+        <v>170</v>
       </c>
       <c r="B18">
-        <v>22700.54</v>
+        <v>0</v>
       </c>
       <c r="C18">
-        <v>16725.41</v>
+        <v>0</v>
       </c>
       <c r="D18">
-        <v>19342.47</v>
+        <v>0</v>
       </c>
       <c r="E18">
-        <v>15097.77</v>
+        <v>0</v>
       </c>
       <c r="F18">
-        <v>10576.24</v>
+        <v>0</v>
       </c>
       <c r="G18">
-        <v>84442.43</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19">
-        <v>194</v>
+        <v>171</v>
       </c>
       <c r="B19">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="C19">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="D19">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="E19">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="F19">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="G19">
-        <v>9.04</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="B20">
-        <v>1554.29</v>
+        <v>0.01</v>
       </c>
       <c r="C20">
-        <v>669.49</v>
+        <v>0.01</v>
       </c>
       <c r="D20">
-        <v>3049.96</v>
+        <v>0.01</v>
       </c>
       <c r="E20">
-        <v>1990.3</v>
+        <v>0.01</v>
       </c>
       <c r="F20">
-        <v>1235.01</v>
+        <v>0.01</v>
       </c>
       <c r="G20">
-        <v>8499.05</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="B21">
-        <v>0.01</v>
+        <v>21333.38</v>
       </c>
       <c r="C21">
-        <v>0.09</v>
+        <v>13278.93</v>
       </c>
       <c r="D21">
-        <v>0.1</v>
+        <v>11113.76</v>
       </c>
       <c r="E21">
-        <v>0.1</v>
+        <v>9912.97</v>
       </c>
       <c r="F21">
-        <v>0.1</v>
+        <v>11847.6</v>
       </c>
       <c r="G21">
-        <v>0.4</v>
+        <v>67486.64</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="B22">
-        <v>6824.99</v>
+        <v>467.21</v>
       </c>
       <c r="C22">
-        <v>6314.15</v>
+        <v>638.59</v>
       </c>
       <c r="D22">
-        <v>5576.07</v>
+        <v>1188.8</v>
       </c>
       <c r="E22">
-        <v>8508.93</v>
+        <v>1386.57</v>
       </c>
       <c r="F22">
-        <v>10729.88</v>
+        <v>1241.16</v>
       </c>
       <c r="G22">
-        <v>37954.02</v>
+        <v>4922.33</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="B23">
-        <v>0.02</v>
+        <v>475.32</v>
       </c>
       <c r="C23">
-        <v>0.02</v>
+        <v>108.26</v>
       </c>
       <c r="D23">
-        <v>0.02</v>
+        <v>9656.79</v>
       </c>
       <c r="E23">
-        <v>0.02</v>
+        <v>14909.91</v>
       </c>
       <c r="F23">
-        <v>0.02</v>
+        <v>11718.71</v>
       </c>
       <c r="G23">
-        <v>0.1</v>
+        <v>36868.99</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="B24">
-        <v>1.96</v>
+        <v>10427.71</v>
       </c>
       <c r="C24">
-        <v>0.65</v>
+        <v>5314.13</v>
       </c>
       <c r="D24">
-        <v>5.79</v>
+        <v>4209.1</v>
       </c>
       <c r="E24">
-        <v>32.59</v>
+        <v>2912.07</v>
       </c>
       <c r="F24">
-        <v>91.6</v>
+        <v>2740.89</v>
       </c>
       <c r="G24">
-        <v>132.59</v>
+        <v>25603.9</v>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="B25">
-        <v>28.54</v>
+        <v>3326.25</v>
       </c>
       <c r="C25">
-        <v>32.89</v>
+        <v>5352.96</v>
       </c>
       <c r="D25">
-        <v>42.56</v>
+        <v>8218.73</v>
       </c>
       <c r="E25">
-        <v>39.75</v>
+        <v>12123.38</v>
       </c>
       <c r="F25">
-        <v>33.27</v>
+        <v>23241.91</v>
       </c>
       <c r="G25">
-        <v>177.01</v>
+        <v>52263.23</v>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <v>204</v>
-      </c>
-      <c r="B26" t="str">
-        <v/>
+        <v>192</v>
+      </c>
+      <c r="B26">
+        <v>22700.54</v>
       </c>
       <c r="C26">
-        <v>1.61</v>
+        <v>16725.41</v>
       </c>
       <c r="D26">
-        <v>16.91</v>
+        <v>19342.47</v>
       </c>
       <c r="E26">
-        <v>34.05</v>
+        <v>15097.77</v>
       </c>
       <c r="F26">
-        <v>30.45</v>
+        <v>10576.24</v>
       </c>
       <c r="G26">
-        <v>83.02</v>
+        <v>84442.43</v>
       </c>
     </row>
     <row r="27">
       <c r="A27">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="B27">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="C27">
-        <v>0.02</v>
+        <v>1.7</v>
       </c>
       <c r="D27">
-        <v>0.2</v>
+        <v>1.88</v>
       </c>
       <c r="E27">
-        <v>0.21</v>
+        <v>1.72</v>
       </c>
       <c r="F27">
-        <v>0.21</v>
+        <v>1.75</v>
       </c>
       <c r="G27">
-        <v>0.64</v>
+        <v>9.04</v>
       </c>
     </row>
     <row r="28">
       <c r="A28">
-        <v>206</v>
-      </c>
-      <c r="B28" t="str">
-        <v/>
-      </c>
-      <c r="C28" t="str">
-        <v/>
-      </c>
-      <c r="D28" t="str">
-        <v/>
-      </c>
-      <c r="E28" t="str">
-        <v/>
+        <v>195</v>
+      </c>
+      <c r="B28">
+        <v>1554.29</v>
+      </c>
+      <c r="C28">
+        <v>669.49</v>
+      </c>
+      <c r="D28">
+        <v>3049.96</v>
+      </c>
+      <c r="E28">
+        <v>1990.3</v>
       </c>
       <c r="F28">
-        <v>0</v>
+        <v>1235.01</v>
       </c>
       <c r="G28">
-        <v>0</v>
+        <v>8499.05</v>
       </c>
     </row>
     <row r="29">
       <c r="A29">
-        <v>214</v>
-      </c>
-      <c r="B29" t="str">
-        <v/>
-      </c>
-      <c r="C29" t="str">
-        <v/>
-      </c>
-      <c r="D29" t="str">
-        <v/>
-      </c>
-      <c r="E29" t="str">
-        <v/>
+        <v>196</v>
+      </c>
+      <c r="B29">
+        <v>0.01</v>
+      </c>
+      <c r="C29">
+        <v>0.09</v>
+      </c>
+      <c r="D29">
+        <v>0.1</v>
+      </c>
+      <c r="E29">
+        <v>0.1</v>
       </c>
       <c r="F29">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G29">
-        <v>0</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="30">
       <c r="A30">
-        <v>216</v>
-      </c>
-      <c r="B30" t="str">
-        <v/>
-      </c>
-      <c r="C30" t="str">
-        <v/>
+        <v>197</v>
+      </c>
+      <c r="B30">
+        <v>6824.99</v>
+      </c>
+      <c r="C30">
+        <v>6314.15</v>
       </c>
       <c r="D30">
-        <v>86.77</v>
+        <v>5576.07</v>
       </c>
       <c r="E30">
-        <v>151.21</v>
+        <v>8508.93</v>
       </c>
       <c r="F30">
-        <v>189.04</v>
+        <v>10729.88</v>
       </c>
       <c r="G30">
-        <v>427.02</v>
+        <v>37954.02</v>
       </c>
     </row>
     <row r="31">
       <c r="A31">
-        <v>219</v>
-      </c>
-      <c r="B31" t="str">
-        <v/>
-      </c>
-      <c r="C31" t="str">
-        <v/>
-      </c>
-      <c r="D31" t="str">
-        <v/>
+        <v>198</v>
+      </c>
+      <c r="B31">
+        <v>0.02</v>
+      </c>
+      <c r="C31">
+        <v>0.02</v>
+      </c>
+      <c r="D31">
+        <v>0.02</v>
       </c>
       <c r="E31">
-        <v>14.26</v>
-      </c>
-      <c r="F31" t="str">
-        <v/>
+        <v>0.02</v>
+      </c>
+      <c r="F31">
+        <v>0.02</v>
       </c>
       <c r="G31">
-        <v>14.26</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32">
-        <v>223</v>
-      </c>
-      <c r="B32" t="str">
-        <v/>
-      </c>
-      <c r="C32" t="str">
-        <v/>
-      </c>
-      <c r="D32" t="str">
-        <v/>
-      </c>
-      <c r="E32" t="str">
-        <v/>
+        <v>200</v>
+      </c>
+      <c r="B32">
+        <v>1.96</v>
+      </c>
+      <c r="C32">
+        <v>0.65</v>
+      </c>
+      <c r="D32">
+        <v>5.79</v>
+      </c>
+      <c r="E32">
+        <v>32.59</v>
       </c>
       <c r="F32">
-        <v>0</v>
+        <v>91.6</v>
       </c>
       <c r="G32">
-        <v>0</v>
+        <v>132.59</v>
       </c>
     </row>
     <row r="33">
       <c r="A33">
-        <v>224</v>
-      </c>
-      <c r="B33" t="str">
-        <v/>
-      </c>
-      <c r="C33" t="str">
-        <v/>
-      </c>
-      <c r="D33" t="str">
-        <v/>
-      </c>
-      <c r="E33" t="str">
-        <v/>
+        <v>202</v>
+      </c>
+      <c r="B33">
+        <v>28.54</v>
+      </c>
+      <c r="C33">
+        <v>32.89</v>
+      </c>
+      <c r="D33">
+        <v>42.56</v>
+      </c>
+      <c r="E33">
+        <v>39.75</v>
       </c>
       <c r="F33">
-        <v>4582.17</v>
+        <v>33.27</v>
       </c>
       <c r="G33">
-        <v>4582.17</v>
+        <v>177.01</v>
       </c>
     </row>
     <row r="34">
       <c r="A34">
-        <v>303</v>
-      </c>
-      <c r="B34">
-        <v>0</v>
+        <v>204</v>
+      </c>
+      <c r="B34" t="str">
+        <v/>
       </c>
       <c r="C34">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="D34">
-        <v>0</v>
+        <v>16.91</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>34.05</v>
       </c>
       <c r="F34">
-        <v>0</v>
+        <v>30.45</v>
       </c>
       <c r="G34">
-        <v>0</v>
+        <v>83.02</v>
       </c>
     </row>
     <row r="35">
       <c r="A35">
-        <v>555</v>
+        <v>205</v>
       </c>
       <c r="B35">
         <v>0</v>
       </c>
       <c r="C35">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="D35">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="F35">
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="G35">
-        <v>0</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="36">
       <c r="A36">
-        <v>1001</v>
-      </c>
-      <c r="B36">
-        <v>2171.72</v>
-      </c>
-      <c r="C36">
-        <v>1561.38</v>
-      </c>
-      <c r="D36">
-        <v>1611.23</v>
-      </c>
-      <c r="E36">
-        <v>1391.66</v>
+        <v>206</v>
+      </c>
+      <c r="B36" t="str">
+        <v/>
+      </c>
+      <c r="C36" t="str">
+        <v/>
+      </c>
+      <c r="D36" t="str">
+        <v/>
+      </c>
+      <c r="E36" t="str">
+        <v/>
       </c>
       <c r="F36">
-        <v>868.97</v>
+        <v>0</v>
       </c>
       <c r="G36">
-        <v>7604.96</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37">
-        <v>1002</v>
-      </c>
-      <c r="B37">
-        <v>1968.87</v>
-      </c>
-      <c r="C37">
-        <v>2969.94</v>
-      </c>
-      <c r="D37">
-        <v>29194.65</v>
-      </c>
-      <c r="E37">
-        <v>28954.6</v>
+        <v>214</v>
+      </c>
+      <c r="B37" t="str">
+        <v/>
+      </c>
+      <c r="C37" t="str">
+        <v/>
+      </c>
+      <c r="D37" t="str">
+        <v/>
+      </c>
+      <c r="E37" t="str">
+        <v/>
       </c>
       <c r="F37">
-        <v>33174.52</v>
+        <v>0</v>
       </c>
       <c r="G37">
-        <v>96262.58</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38">
-        <v>1004</v>
-      </c>
-      <c r="B38">
-        <v>0.01</v>
-      </c>
-      <c r="C38">
-        <v>0</v>
+        <v>216</v>
+      </c>
+      <c r="B38" t="str">
+        <v/>
+      </c>
+      <c r="C38" t="str">
+        <v/>
       </c>
       <c r="D38">
-        <v>0.01</v>
+        <v>86.77</v>
       </c>
       <c r="E38">
-        <v>0.01</v>
+        <v>151.21</v>
       </c>
       <c r="F38">
-        <v>0.01</v>
+        <v>189.04</v>
       </c>
       <c r="G38">
-        <v>0.04</v>
+        <v>427.02</v>
       </c>
     </row>
     <row r="39">
       <c r="A39">
-        <v>1007</v>
-      </c>
-      <c r="B39">
-        <v>10082.51</v>
-      </c>
-      <c r="C39">
-        <v>13745.06</v>
-      </c>
-      <c r="D39">
-        <v>15859.43</v>
+        <v>219</v>
+      </c>
+      <c r="B39" t="str">
+        <v/>
+      </c>
+      <c r="C39" t="str">
+        <v/>
+      </c>
+      <c r="D39" t="str">
+        <v/>
       </c>
       <c r="E39">
-        <v>14112.17</v>
-      </c>
-      <c r="F39">
-        <v>10762.39</v>
+        <v>14.26</v>
+      </c>
+      <c r="F39" t="str">
+        <v/>
       </c>
       <c r="G39">
-        <v>64561.56</v>
+        <v>14.26</v>
       </c>
     </row>
     <row r="40">
       <c r="A40">
-        <v>1015</v>
-      </c>
-      <c r="B40">
-        <v>0</v>
-      </c>
-      <c r="C40">
-        <v>0</v>
-      </c>
-      <c r="D40">
-        <v>0</v>
-      </c>
-      <c r="E40">
-        <v>0</v>
+        <v>223</v>
+      </c>
+      <c r="B40" t="str">
+        <v/>
+      </c>
+      <c r="C40" t="str">
+        <v/>
+      </c>
+      <c r="D40" t="str">
+        <v/>
+      </c>
+      <c r="E40" t="str">
+        <v/>
       </c>
       <c r="F40">
         <v>0</v>
@@ -2735,62 +2965,62 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>1016</v>
-      </c>
-      <c r="B41">
-        <v>1201.05</v>
-      </c>
-      <c r="C41">
-        <v>167.54</v>
-      </c>
-      <c r="D41">
-        <v>8.98</v>
-      </c>
-      <c r="E41">
-        <v>0.59</v>
+        <v>224</v>
+      </c>
+      <c r="B41" t="str">
+        <v/>
+      </c>
+      <c r="C41" t="str">
+        <v/>
+      </c>
+      <c r="D41" t="str">
+        <v/>
+      </c>
+      <c r="E41" t="str">
+        <v/>
       </c>
       <c r="F41">
-        <v>0</v>
+        <v>4582.17</v>
       </c>
       <c r="G41">
-        <v>1378.16</v>
+        <v>4582.17</v>
       </c>
     </row>
     <row r="42">
       <c r="A42">
-        <v>1017</v>
+        <v>303</v>
       </c>
       <c r="B42">
-        <v>215.45</v>
+        <v>0</v>
       </c>
       <c r="C42">
-        <v>140.34</v>
+        <v>0</v>
       </c>
       <c r="D42">
-        <v>148.1</v>
+        <v>0</v>
       </c>
       <c r="E42">
-        <v>85.99</v>
+        <v>0</v>
       </c>
       <c r="F42">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="G42">
-        <v>593.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43">
-        <v>2000</v>
-      </c>
-      <c r="B43" t="str">
-        <v/>
-      </c>
-      <c r="C43" t="str">
-        <v/>
-      </c>
-      <c r="D43" t="str">
-        <v/>
+        <v>555</v>
+      </c>
+      <c r="B43">
+        <v>0</v>
+      </c>
+      <c r="C43">
+        <v>0</v>
+      </c>
+      <c r="D43">
+        <v>0</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -2804,168 +3034,168 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>2001</v>
-      </c>
-      <c r="B44" t="str">
-        <v/>
+        <v>1001</v>
+      </c>
+      <c r="B44">
+        <v>2171.72</v>
       </c>
       <c r="C44">
-        <v>0</v>
+        <v>1561.38</v>
       </c>
       <c r="D44">
-        <v>0</v>
+        <v>1611.23</v>
       </c>
       <c r="E44">
-        <v>82.24</v>
+        <v>1391.66</v>
       </c>
       <c r="F44">
-        <v>8467.99</v>
+        <v>868.97</v>
       </c>
       <c r="G44">
-        <v>8550.23</v>
+        <v>7604.96</v>
       </c>
     </row>
     <row r="45">
       <c r="A45">
-        <v>2002</v>
-      </c>
-      <c r="B45" t="str">
-        <v/>
-      </c>
-      <c r="C45" t="str">
-        <v/>
+        <v>1002</v>
+      </c>
+      <c r="B45">
+        <v>1968.87</v>
+      </c>
+      <c r="C45">
+        <v>2969.94</v>
       </c>
       <c r="D45">
-        <v>174574.28</v>
+        <v>29194.65</v>
       </c>
       <c r="E45">
-        <v>116737.37</v>
+        <v>28954.6</v>
       </c>
       <c r="F45">
-        <v>0</v>
+        <v>33174.52</v>
       </c>
       <c r="G45">
-        <v>291311.65</v>
+        <v>96262.58</v>
       </c>
     </row>
     <row r="46">
       <c r="A46">
-        <v>2003</v>
-      </c>
-      <c r="B46" t="str">
-        <v/>
-      </c>
-      <c r="C46" t="str">
-        <v/>
-      </c>
-      <c r="D46" t="str">
-        <v/>
+        <v>1004</v>
+      </c>
+      <c r="B46">
+        <v>0.01</v>
+      </c>
+      <c r="C46">
+        <v>0</v>
+      </c>
+      <c r="D46">
+        <v>0.01</v>
       </c>
       <c r="E46">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="F46">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="G46">
-        <v>0</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="47">
       <c r="A47">
-        <v>2005</v>
-      </c>
-      <c r="B47" t="str">
-        <v/>
-      </c>
-      <c r="C47" t="str">
-        <v/>
+        <v>1007</v>
+      </c>
+      <c r="B47">
+        <v>10082.51</v>
+      </c>
+      <c r="C47">
+        <v>13745.06</v>
       </c>
       <c r="D47">
-        <v>17144.97</v>
+        <v>15859.43</v>
       </c>
       <c r="E47">
-        <v>8259.88</v>
-      </c>
-      <c r="F47" t="str">
-        <v/>
+        <v>14112.17</v>
+      </c>
+      <c r="F47">
+        <v>10762.39</v>
       </c>
       <c r="G47">
-        <v>25404.85</v>
+        <v>64561.56</v>
       </c>
     </row>
     <row r="48">
       <c r="A48">
-        <v>2008</v>
-      </c>
-      <c r="B48" t="str">
-        <v/>
-      </c>
-      <c r="C48" t="str">
-        <v/>
-      </c>
-      <c r="D48" t="str">
-        <v/>
-      </c>
-      <c r="E48" t="str">
-        <v/>
+        <v>1015</v>
+      </c>
+      <c r="B48">
+        <v>0</v>
+      </c>
+      <c r="C48">
+        <v>0</v>
+      </c>
+      <c r="D48">
+        <v>0</v>
+      </c>
+      <c r="E48">
+        <v>0</v>
       </c>
       <c r="F48">
-        <v>12035.78</v>
+        <v>0</v>
       </c>
       <c r="G48">
-        <v>12035.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49">
-        <v>2222</v>
-      </c>
-      <c r="B49" t="str">
-        <v/>
-      </c>
-      <c r="C49" t="str">
-        <v/>
-      </c>
-      <c r="D49" t="str">
-        <v/>
+        <v>1016</v>
+      </c>
+      <c r="B49">
+        <v>1201.05</v>
+      </c>
+      <c r="C49">
+        <v>167.54</v>
+      </c>
+      <c r="D49">
+        <v>8.98</v>
       </c>
       <c r="E49">
-        <v>10.68</v>
+        <v>0.59</v>
       </c>
       <c r="F49">
-        <v>14.75</v>
+        <v>0</v>
       </c>
       <c r="G49">
-        <v>25.43</v>
+        <v>1378.16</v>
       </c>
     </row>
     <row r="50">
       <c r="A50">
-        <v>3000</v>
-      </c>
-      <c r="B50" t="str">
-        <v/>
-      </c>
-      <c r="C50" t="str">
-        <v/>
-      </c>
-      <c r="D50" t="str">
-        <v/>
+        <v>1017</v>
+      </c>
+      <c r="B50">
+        <v>215.45</v>
+      </c>
+      <c r="C50">
+        <v>140.34</v>
+      </c>
+      <c r="D50">
+        <v>148.1</v>
       </c>
       <c r="E50">
-        <v>0</v>
+        <v>85.99</v>
       </c>
       <c r="F50">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="G50">
-        <v>0</v>
+        <v>593.4</v>
       </c>
     </row>
     <row r="51">
       <c r="A51">
-        <v>3001</v>
+        <v>2000</v>
       </c>
       <c r="B51" t="str">
         <v/>
@@ -2976,8 +3206,8 @@
       <c r="D51" t="str">
         <v/>
       </c>
-      <c r="E51" t="str">
-        <v/>
+      <c r="E51">
+        <v>0</v>
       </c>
       <c r="F51">
         <v>0</v>
@@ -2988,30 +3218,30 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>3333</v>
-      </c>
-      <c r="B52">
-        <v>0.71</v>
+        <v>2001</v>
+      </c>
+      <c r="B52" t="str">
+        <v/>
       </c>
       <c r="C52">
-        <v>0.41</v>
+        <v>0</v>
       </c>
       <c r="D52">
-        <v>0.48</v>
+        <v>0</v>
       </c>
       <c r="E52">
-        <v>0.49</v>
+        <v>82.24</v>
       </c>
       <c r="F52">
-        <v>0.48</v>
+        <v>8467.99</v>
       </c>
       <c r="G52">
-        <v>2.57</v>
+        <v>8550.23</v>
       </c>
     </row>
     <row r="53">
       <c r="A53">
-        <v>4011</v>
+        <v>2002</v>
       </c>
       <c r="B53" t="str">
         <v/>
@@ -3019,22 +3249,22 @@
       <c r="C53" t="str">
         <v/>
       </c>
-      <c r="D53" t="str">
-        <v/>
-      </c>
-      <c r="E53" t="str">
-        <v/>
+      <c r="D53">
+        <v>174574.28</v>
+      </c>
+      <c r="E53">
+        <v>116737.37</v>
       </c>
       <c r="F53">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="G53">
-        <v>0.01</v>
+        <v>291311.65</v>
       </c>
     </row>
     <row r="54">
       <c r="A54">
-        <v>4012</v>
+        <v>2003</v>
       </c>
       <c r="B54" t="str">
         <v/>
@@ -3045,8 +3275,8 @@
       <c r="D54" t="str">
         <v/>
       </c>
-      <c r="E54" t="str">
-        <v/>
+      <c r="E54">
+        <v>0</v>
       </c>
       <c r="F54">
         <v>0</v>
@@ -3057,53 +3287,53 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>9998</v>
-      </c>
-      <c r="B55">
-        <v>0</v>
-      </c>
-      <c r="C55">
-        <v>0</v>
+        <v>2005</v>
+      </c>
+      <c r="B55" t="str">
+        <v/>
+      </c>
+      <c r="C55" t="str">
+        <v/>
       </c>
       <c r="D55">
-        <v>0</v>
+        <v>17144.97</v>
       </c>
       <c r="E55">
-        <v>0</v>
-      </c>
-      <c r="F55">
-        <v>0</v>
+        <v>8259.88</v>
+      </c>
+      <c r="F55" t="str">
+        <v/>
       </c>
       <c r="G55">
-        <v>0</v>
+        <v>25404.85</v>
       </c>
     </row>
     <row r="56">
       <c r="A56">
-        <v>13425</v>
-      </c>
-      <c r="B56">
-        <v>858.01</v>
-      </c>
-      <c r="C56">
-        <v>774.97</v>
-      </c>
-      <c r="D56">
-        <v>858.01</v>
-      </c>
-      <c r="E56">
-        <v>641.16</v>
+        <v>2008</v>
+      </c>
+      <c r="B56" t="str">
+        <v/>
+      </c>
+      <c r="C56" t="str">
+        <v/>
+      </c>
+      <c r="D56" t="str">
+        <v/>
+      </c>
+      <c r="E56" t="str">
+        <v/>
       </c>
       <c r="F56">
-        <v>9.67</v>
+        <v>12035.78</v>
       </c>
       <c r="G56">
-        <v>3141.82</v>
+        <v>12035.78</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="str">
-        <v/>
+      <c r="A57">
+        <v>2222</v>
       </c>
       <c r="B57" t="str">
         <v/>
@@ -3114,19 +3344,19 @@
       <c r="D57" t="str">
         <v/>
       </c>
-      <c r="E57" t="str">
-        <v/>
-      </c>
-      <c r="F57" t="str">
-        <v/>
-      </c>
-      <c r="G57" t="str">
-        <v/>
+      <c r="E57">
+        <v>10.68</v>
+      </c>
+      <c r="F57">
+        <v>14.75</v>
+      </c>
+      <c r="G57">
+        <v>25.43</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="str">
-        <v>── untagged ──</v>
+      <c r="A58">
+        <v>3000</v>
       </c>
       <c r="B58" t="str">
         <v/>
@@ -3137,88 +3367,272 @@
       <c r="D58" t="str">
         <v/>
       </c>
-      <c r="E58" t="str">
-        <v/>
-      </c>
-      <c r="F58" t="str">
-        <v/>
-      </c>
-      <c r="G58" t="str">
-        <v/>
+      <c r="E58">
+        <v>0</v>
+      </c>
+      <c r="F58">
+        <v>0</v>
+      </c>
+      <c r="G58">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59">
-        <v>99</v>
-      </c>
-      <c r="B59">
-        <v>1417549.48</v>
-      </c>
-      <c r="C59">
-        <v>1285231.35</v>
-      </c>
-      <c r="D59">
-        <v>1513204.59</v>
-      </c>
-      <c r="E59">
-        <v>1445734.27</v>
+        <v>3001</v>
+      </c>
+      <c r="B59" t="str">
+        <v/>
+      </c>
+      <c r="C59" t="str">
+        <v/>
+      </c>
+      <c r="D59" t="str">
+        <v/>
+      </c>
+      <c r="E59" t="str">
+        <v/>
       </c>
       <c r="F59">
-        <v>1598658.68</v>
+        <v>0</v>
       </c>
       <c r="G59">
-        <v>7260378.37</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60">
-        <v>123623963915635</v>
+        <v>3333</v>
       </c>
       <c r="B60">
-        <v>0</v>
+        <v>0.71</v>
       </c>
       <c r="C60">
-        <v>0</v>
+        <v>0.41</v>
       </c>
       <c r="D60">
-        <v>0.01</v>
+        <v>0.48</v>
       </c>
       <c r="E60">
-        <v>0</v>
+        <v>0.49</v>
       </c>
       <c r="F60">
-        <v>0.01</v>
+        <v>0.48</v>
       </c>
       <c r="G60">
-        <v>0.02</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="61">
       <c r="A61">
+        <v>4011</v>
+      </c>
+      <c r="B61" t="str">
+        <v/>
+      </c>
+      <c r="C61" t="str">
+        <v/>
+      </c>
+      <c r="D61" t="str">
+        <v/>
+      </c>
+      <c r="E61" t="str">
+        <v/>
+      </c>
+      <c r="F61">
+        <v>0.01</v>
+      </c>
+      <c r="G61">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>4012</v>
+      </c>
+      <c r="B62" t="str">
+        <v/>
+      </c>
+      <c r="C62" t="str">
+        <v/>
+      </c>
+      <c r="D62" t="str">
+        <v/>
+      </c>
+      <c r="E62" t="str">
+        <v/>
+      </c>
+      <c r="F62">
+        <v>0</v>
+      </c>
+      <c r="G62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>9998</v>
+      </c>
+      <c r="B63">
+        <v>0</v>
+      </c>
+      <c r="C63">
+        <v>0</v>
+      </c>
+      <c r="D63">
+        <v>0</v>
+      </c>
+      <c r="E63">
+        <v>0</v>
+      </c>
+      <c r="F63">
+        <v>0</v>
+      </c>
+      <c r="G63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>13425</v>
+      </c>
+      <c r="B64">
+        <v>858.01</v>
+      </c>
+      <c r="C64">
+        <v>774.97</v>
+      </c>
+      <c r="D64">
+        <v>858.01</v>
+      </c>
+      <c r="E64">
+        <v>641.16</v>
+      </c>
+      <c r="F64">
+        <v>9.67</v>
+      </c>
+      <c r="G64">
+        <v>3141.82</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v/>
+      </c>
+      <c r="B65" t="str">
+        <v/>
+      </c>
+      <c r="C65" t="str">
+        <v/>
+      </c>
+      <c r="D65" t="str">
+        <v/>
+      </c>
+      <c r="E65" t="str">
+        <v/>
+      </c>
+      <c r="F65" t="str">
+        <v/>
+      </c>
+      <c r="G65" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>── untagged ──</v>
+      </c>
+      <c r="B66" t="str">
+        <v/>
+      </c>
+      <c r="C66" t="str">
+        <v/>
+      </c>
+      <c r="D66" t="str">
+        <v/>
+      </c>
+      <c r="E66" t="str">
+        <v/>
+      </c>
+      <c r="F66" t="str">
+        <v/>
+      </c>
+      <c r="G66" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>99</v>
+      </c>
+      <c r="B67">
+        <v>1417549.48</v>
+      </c>
+      <c r="C67">
+        <v>1285231.35</v>
+      </c>
+      <c r="D67">
+        <v>1513204.59</v>
+      </c>
+      <c r="E67">
+        <v>1445734.27</v>
+      </c>
+      <c r="F67">
+        <v>1598658.68</v>
+      </c>
+      <c r="G67">
+        <v>7260378.37</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>123623963915635</v>
+      </c>
+      <c r="B68">
+        <v>0</v>
+      </c>
+      <c r="C68">
+        <v>0</v>
+      </c>
+      <c r="D68">
+        <v>0.01</v>
+      </c>
+      <c r="E68">
+        <v>0</v>
+      </c>
+      <c r="F68">
+        <v>0.01</v>
+      </c>
+      <c r="G68">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
         <v>90000000000000000000</v>
       </c>
-      <c r="B61">
+      <c r="B69">
         <v>0.06</v>
       </c>
-      <c r="C61">
+      <c r="C69">
         <v>0.01</v>
       </c>
-      <c r="D61">
-        <v>0</v>
-      </c>
-      <c r="E61">
-        <v>0</v>
-      </c>
-      <c r="F61">
-        <v>0</v>
-      </c>
-      <c r="G61">
+      <c r="D69">
+        <v>0</v>
+      </c>
+      <c r="E69">
+        <v>0</v>
+      </c>
+      <c r="F69">
+        <v>0</v>
+      </c>
+      <c r="G69">
         <v>0.07</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G61"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G69"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3974,7 +4388,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I64"/>
+  <dimension ref="A1:I74"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
@@ -4017,8 +4431,8 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>0</v>
+      <c r="A2" t="str">
+        <v>0 (spUSDC)</v>
       </c>
       <c r="B2" t="str">
         <v>both</v>
@@ -4030,53 +4444,53 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>324.58</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>1121.44</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>340.4</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>1786.42</v>
+        <v>0</v>
       </c>
       <c r="I2" t="str">
-        <v>Diff vs Spark = Chronicle farm (USDS-CLE) only. Spark does not track this farm.</v>
+        <v/>
       </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>1</v>
+      <c r="A3" t="str">
+        <v>0 (stUSDS)</v>
       </c>
       <c r="B3" t="str">
         <v>both</v>
       </c>
       <c r="C3">
-        <v>5139.57</v>
+        <v>0</v>
       </c>
       <c r="D3">
-        <v>4193.83</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>6259.94</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>5552.85</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>8195.2</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>29341.39</v>
+        <v>0</v>
       </c>
       <c r="I3" t="str">
-        <v>Diff vs Spark = Chronicle farm (USDS-CLE) only. Spark does not track this farm.</v>
+        <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>2</v>
+      <c r="A4" t="str">
+        <v>0 (sUSDC)</v>
       </c>
       <c r="B4" t="str">
         <v>both</v>
@@ -4104,11 +4518,11 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>10</v>
+      <c r="A5" t="str">
+        <v>0 (sUSDS)</v>
       </c>
       <c r="B5" t="str">
-        <v>ours only</v>
+        <v>both</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -4117,24 +4531,24 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="I5" t="str">
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>100</v>
+      <c r="A6" t="str">
+        <v>0 (USDS-CLE)</v>
       </c>
       <c r="B6" t="str">
         <v>ours only</v>
@@ -4146,111 +4560,111 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>324.57</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>1121.44</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>340.38</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>1786.39</v>
       </c>
       <c r="I6" t="str">
-        <v/>
+        <v>Chronicle farm — not tracked by Spark.</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>126</v>
+      <c r="A7" t="str">
+        <v>0 (USDS-SKY)</v>
       </c>
       <c r="B7" t="str">
-        <v>spark only</v>
+        <v>both</v>
       </c>
       <c r="C7">
-        <v>-106392.55</v>
+        <v>0</v>
       </c>
       <c r="D7">
-        <v>-114516.89</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>-122957.88</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>-115359.51</v>
+        <v>0</v>
       </c>
       <c r="G7">
-        <v>-118567.8</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>-577794.63</v>
+        <v>0</v>
       </c>
       <c r="I7" t="str">
-        <v>Subproxy holdings, no DR applied. Handled in Supply Side MSC.</v>
+        <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>127</v>
+      <c r="A8" t="str">
+        <v>0 (USDS-SPK)</v>
       </c>
       <c r="B8" t="str">
         <v>both</v>
       </c>
       <c r="C8">
-        <v>-445.27</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>-208.59</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>-351.49</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>-397.73</v>
+        <v>0</v>
       </c>
       <c r="G8">
-        <v>-172.48</v>
+        <v>0</v>
       </c>
       <c r="H8">
-        <v>-1575.56</v>
+        <v>0</v>
       </c>
       <c r="I8" t="str">
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>128</v>
+      <c r="A9" t="str">
+        <v>1 (stUSDS)</v>
       </c>
       <c r="B9" t="str">
         <v>both</v>
       </c>
       <c r="C9">
-        <v>4064.11</v>
+        <v>0</v>
       </c>
       <c r="D9">
-        <v>4165.46</v>
+        <v>0</v>
       </c>
       <c r="E9">
-        <v>-905.41</v>
+        <v>0</v>
       </c>
       <c r="F9">
-        <v>-2031.4</v>
+        <v>0</v>
       </c>
       <c r="G9">
-        <v>-1597.47</v>
+        <v>0</v>
       </c>
       <c r="H9">
-        <v>3695.29</v>
+        <v>0</v>
       </c>
       <c r="I9" t="str">
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>129</v>
+      <c r="A10" t="str">
+        <v>1 (sUSDS)</v>
       </c>
       <c r="B10" t="str">
         <v>both</v>
@@ -4278,37 +4692,37 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>130</v>
+      <c r="A11" t="str">
+        <v>1 (USDS-CLE)</v>
       </c>
       <c r="B11" t="str">
-        <v>spark only</v>
+        <v>ours only</v>
       </c>
       <c r="C11">
-        <v>-266.96</v>
+        <v>5139.57</v>
       </c>
       <c r="D11">
-        <v>-252.94</v>
+        <v>4193.83</v>
       </c>
       <c r="E11">
-        <v>-3701.44</v>
+        <v>6259.94</v>
       </c>
       <c r="F11">
-        <v>-4353.38</v>
+        <v>5552.85</v>
       </c>
       <c r="G11">
-        <v>-3885.67</v>
+        <v>8195.2</v>
       </c>
       <c r="H11">
-        <v>-12460.39</v>
+        <v>29341.39</v>
       </c>
       <c r="I11" t="str">
-        <v>Found in Spark datasets only, no onchain events.</v>
+        <v>Chronicle farm — not tracked by Spark.</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>170</v>
+      <c r="A12" t="str">
+        <v>1 (USDS-SKY)</v>
       </c>
       <c r="B12" t="str">
         <v>both</v>
@@ -4336,8 +4750,8 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>171</v>
+      <c r="A13" t="str">
+        <v>1 (USDS-SPK)</v>
       </c>
       <c r="B13" t="str">
         <v>both</v>
@@ -4366,7 +4780,7 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>182</v>
+        <v>2</v>
       </c>
       <c r="B14" t="str">
         <v>both</v>
@@ -4395,10 +4809,10 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>183</v>
+        <v>10</v>
       </c>
       <c r="B15" t="str">
-        <v>both</v>
+        <v>ours only</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -4424,10 +4838,10 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>186</v>
+        <v>100</v>
       </c>
       <c r="B16" t="str">
-        <v>both</v>
+        <v>ours only</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -4453,57 +4867,57 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>188</v>
+        <v>126</v>
       </c>
       <c r="B17" t="str">
-        <v>both</v>
+        <v>spark only</v>
       </c>
       <c r="C17">
-        <v>0.01</v>
+        <v>-106392.55</v>
       </c>
       <c r="D17">
-        <v>0.01</v>
+        <v>-114516.89</v>
       </c>
       <c r="E17">
-        <v>-2455.39</v>
+        <v>-122957.88</v>
       </c>
       <c r="F17">
-        <v>-327.72</v>
+        <v>-115359.51</v>
       </c>
       <c r="G17">
-        <v>-110.6</v>
+        <v>-118567.8</v>
       </c>
       <c r="H17">
-        <v>-2893.69</v>
+        <v>-577794.63</v>
       </c>
       <c r="I17" t="str">
-        <v/>
+        <v>Subproxy holdings, no DR applied. Handled in Supply Side MSC.</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>190</v>
+        <v>127</v>
       </c>
       <c r="B18" t="str">
         <v>both</v>
       </c>
       <c r="C18">
-        <v>0</v>
+        <v>-445.27</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>-208.59</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>-351.49</v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <v>-397.73</v>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>-172.48</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>-1575.56</v>
       </c>
       <c r="I18" t="str">
         <v/>
@@ -4511,28 +4925,28 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>191</v>
+        <v>128</v>
       </c>
       <c r="B19" t="str">
         <v>both</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>4064.11</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>4165.46</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>-905.41</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>-2031.4</v>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>-1597.47</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>3695.29</v>
       </c>
       <c r="I19" t="str">
         <v/>
@@ -4540,7 +4954,7 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>192</v>
+        <v>129</v>
       </c>
       <c r="B20" t="str">
         <v>both</v>
@@ -4569,36 +4983,36 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>194</v>
+        <v>130</v>
       </c>
       <c r="B21" t="str">
-        <v>both</v>
+        <v>spark only</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>-266.96</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>-252.94</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>-3701.44</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>-4353.38</v>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>-3885.67</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>-12460.39</v>
       </c>
       <c r="I21" t="str">
-        <v/>
+        <v>Found in Spark datasets only, no onchain events.</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>195</v>
+        <v>170</v>
       </c>
       <c r="B22" t="str">
         <v>both</v>
@@ -4627,7 +5041,7 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>196</v>
+        <v>171</v>
       </c>
       <c r="B23" t="str">
         <v>both</v>
@@ -4656,7 +5070,7 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>197</v>
+        <v>182</v>
       </c>
       <c r="B24" t="str">
         <v>both</v>
@@ -4685,7 +5099,7 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>198</v>
+        <v>183</v>
       </c>
       <c r="B25" t="str">
         <v>both</v>
@@ -4714,7 +5128,7 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>200</v>
+        <v>186</v>
       </c>
       <c r="B26" t="str">
         <v>both</v>
@@ -4743,28 +5157,28 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>202</v>
+        <v>188</v>
       </c>
       <c r="B27" t="str">
         <v>both</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>-2455.39</v>
       </c>
       <c r="F27">
-        <v>0</v>
+        <v>-327.72</v>
       </c>
       <c r="G27">
-        <v>0</v>
+        <v>-110.6</v>
       </c>
       <c r="H27">
-        <v>0</v>
+        <v>-2893.69</v>
       </c>
       <c r="I27" t="str">
         <v/>
@@ -4772,7 +5186,7 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="B28" t="str">
         <v>both</v>
@@ -4801,7 +5215,7 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>205</v>
+        <v>191</v>
       </c>
       <c r="B29" t="str">
         <v>both</v>
@@ -4830,7 +5244,7 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="B30" t="str">
         <v>both</v>
@@ -4859,7 +5273,7 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>214</v>
+        <v>194</v>
       </c>
       <c r="B31" t="str">
         <v>both</v>
@@ -4888,7 +5302,7 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>216</v>
+        <v>195</v>
       </c>
       <c r="B32" t="str">
         <v>both</v>
@@ -4917,7 +5331,7 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>219</v>
+        <v>196</v>
       </c>
       <c r="B33" t="str">
         <v>both</v>
@@ -4946,7 +5360,7 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>223</v>
+        <v>197</v>
       </c>
       <c r="B34" t="str">
         <v>both</v>
@@ -4975,7 +5389,7 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>224</v>
+        <v>198</v>
       </c>
       <c r="B35" t="str">
         <v>both</v>
@@ -5004,7 +5418,7 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>303</v>
+        <v>200</v>
       </c>
       <c r="B36" t="str">
         <v>both</v>
@@ -5033,7 +5447,7 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>555</v>
+        <v>202</v>
       </c>
       <c r="B37" t="str">
         <v>both</v>
@@ -5062,28 +5476,28 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>1001</v>
+        <v>204</v>
       </c>
       <c r="B38" t="str">
         <v>both</v>
       </c>
       <c r="C38">
-        <v>83.09</v>
+        <v>0</v>
       </c>
       <c r="D38">
-        <v>40.06</v>
+        <v>0</v>
       </c>
       <c r="E38">
-        <v>44.25</v>
+        <v>0</v>
       </c>
       <c r="F38">
-        <v>42.28</v>
+        <v>0</v>
       </c>
       <c r="G38">
-        <v>43.6</v>
+        <v>0</v>
       </c>
       <c r="H38">
-        <v>253.28</v>
+        <v>0</v>
       </c>
       <c r="I38" t="str">
         <v/>
@@ -5091,28 +5505,28 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>1002</v>
+        <v>205</v>
       </c>
       <c r="B39" t="str">
         <v>both</v>
       </c>
       <c r="C39">
-        <v>0.64</v>
+        <v>0</v>
       </c>
       <c r="D39">
-        <v>0.57</v>
+        <v>0</v>
       </c>
       <c r="E39">
-        <v>0.88</v>
+        <v>0</v>
       </c>
       <c r="F39">
-        <v>0.62</v>
+        <v>0</v>
       </c>
       <c r="G39">
-        <v>0.64</v>
+        <v>0</v>
       </c>
       <c r="H39">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="I39" t="str">
         <v/>
@@ -5120,7 +5534,7 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>1004</v>
+        <v>206</v>
       </c>
       <c r="B40" t="str">
         <v>both</v>
@@ -5149,7 +5563,7 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>1007</v>
+        <v>214</v>
       </c>
       <c r="B41" t="str">
         <v>both</v>
@@ -5178,7 +5592,7 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>1015</v>
+        <v>216</v>
       </c>
       <c r="B42" t="str">
         <v>both</v>
@@ -5207,7 +5621,7 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>1016</v>
+        <v>219</v>
       </c>
       <c r="B43" t="str">
         <v>both</v>
@@ -5236,7 +5650,7 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>1017</v>
+        <v>223</v>
       </c>
       <c r="B44" t="str">
         <v>both</v>
@@ -5265,7 +5679,7 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>2000</v>
+        <v>224</v>
       </c>
       <c r="B45" t="str">
         <v>both</v>
@@ -5294,7 +5708,7 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>2001</v>
+        <v>303</v>
       </c>
       <c r="B46" t="str">
         <v>both</v>
@@ -5323,7 +5737,7 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>2002</v>
+        <v>555</v>
       </c>
       <c r="B47" t="str">
         <v>both</v>
@@ -5352,28 +5766,28 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>2003</v>
+        <v>1001</v>
       </c>
       <c r="B48" t="str">
         <v>both</v>
       </c>
       <c r="C48">
-        <v>0</v>
+        <v>83.09</v>
       </c>
       <c r="D48">
-        <v>0</v>
+        <v>40.06</v>
       </c>
       <c r="E48">
-        <v>0</v>
+        <v>44.25</v>
       </c>
       <c r="F48">
-        <v>0</v>
+        <v>42.28</v>
       </c>
       <c r="G48">
-        <v>0</v>
+        <v>43.6</v>
       </c>
       <c r="H48">
-        <v>0</v>
+        <v>253.28</v>
       </c>
       <c r="I48" t="str">
         <v/>
@@ -5381,28 +5795,28 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>2005</v>
+        <v>1002</v>
       </c>
       <c r="B49" t="str">
         <v>both</v>
       </c>
       <c r="C49">
-        <v>0</v>
+        <v>0.64</v>
       </c>
       <c r="D49">
-        <v>0</v>
+        <v>0.57</v>
       </c>
       <c r="E49">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="F49">
-        <v>0</v>
+        <v>0.62</v>
       </c>
       <c r="G49">
-        <v>0</v>
+        <v>0.64</v>
       </c>
       <c r="H49">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="I49" t="str">
         <v/>
@@ -5410,7 +5824,7 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>2008</v>
+        <v>1004</v>
       </c>
       <c r="B50" t="str">
         <v>both</v>
@@ -5439,7 +5853,7 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>2222</v>
+        <v>1007</v>
       </c>
       <c r="B51" t="str">
         <v>both</v>
@@ -5468,7 +5882,7 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>3000</v>
+        <v>1015</v>
       </c>
       <c r="B52" t="str">
         <v>both</v>
@@ -5497,7 +5911,7 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>3001</v>
+        <v>1016</v>
       </c>
       <c r="B53" t="str">
         <v>both</v>
@@ -5526,7 +5940,7 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>3333</v>
+        <v>1017</v>
       </c>
       <c r="B54" t="str">
         <v>both</v>
@@ -5555,7 +5969,7 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>4011</v>
+        <v>2000</v>
       </c>
       <c r="B55" t="str">
         <v>both</v>
@@ -5584,7 +5998,7 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>4012</v>
+        <v>2001</v>
       </c>
       <c r="B56" t="str">
         <v>both</v>
@@ -5613,7 +6027,7 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>9998</v>
+        <v>2002</v>
       </c>
       <c r="B57" t="str">
         <v>both</v>
@@ -5642,7 +6056,7 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>13425</v>
+        <v>2003</v>
       </c>
       <c r="B58" t="str">
         <v>both</v>
@@ -5670,58 +6084,58 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="str">
-        <v/>
+      <c r="A59">
+        <v>2005</v>
       </c>
       <c r="B59" t="str">
-        <v/>
-      </c>
-      <c r="C59" t="str">
-        <v/>
-      </c>
-      <c r="D59" t="str">
-        <v/>
-      </c>
-      <c r="E59" t="str">
-        <v/>
-      </c>
-      <c r="F59" t="str">
-        <v/>
-      </c>
-      <c r="G59" t="str">
-        <v/>
-      </c>
-      <c r="H59" t="str">
-        <v/>
+        <v>both</v>
+      </c>
+      <c r="C59">
+        <v>0</v>
+      </c>
+      <c r="D59">
+        <v>0</v>
+      </c>
+      <c r="E59">
+        <v>0</v>
+      </c>
+      <c r="F59">
+        <v>0</v>
+      </c>
+      <c r="G59">
+        <v>0</v>
+      </c>
+      <c r="H59">
+        <v>0</v>
       </c>
       <c r="I59" t="str">
         <v/>
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="str">
-        <v>── untagged ──</v>
+      <c r="A60">
+        <v>2008</v>
       </c>
       <c r="B60" t="str">
-        <v/>
-      </c>
-      <c r="C60" t="str">
-        <v/>
-      </c>
-      <c r="D60" t="str">
-        <v/>
-      </c>
-      <c r="E60" t="str">
-        <v/>
-      </c>
-      <c r="F60" t="str">
-        <v/>
-      </c>
-      <c r="G60" t="str">
-        <v/>
-      </c>
-      <c r="H60" t="str">
-        <v/>
+        <v>both</v>
+      </c>
+      <c r="C60">
+        <v>0</v>
+      </c>
+      <c r="D60">
+        <v>0</v>
+      </c>
+      <c r="E60">
+        <v>0</v>
+      </c>
+      <c r="F60">
+        <v>0</v>
+      </c>
+      <c r="G60">
+        <v>0</v>
+      </c>
+      <c r="H60">
+        <v>0</v>
       </c>
       <c r="I60" t="str">
         <v/>
@@ -5729,28 +6143,28 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>-999999</v>
+        <v>2222</v>
       </c>
       <c r="B61" t="str">
-        <v>ours only</v>
+        <v>both</v>
       </c>
       <c r="C61">
-        <v>17418.88</v>
+        <v>0</v>
       </c>
       <c r="D61">
-        <v>10907.25</v>
+        <v>0</v>
       </c>
       <c r="E61">
-        <v>25305.28</v>
+        <v>0</v>
       </c>
       <c r="F61">
-        <v>18026.83</v>
+        <v>0</v>
       </c>
       <c r="G61">
-        <v>15780.23</v>
+        <v>0</v>
       </c>
       <c r="H61">
-        <v>87438.47</v>
+        <v>0</v>
       </c>
       <c r="I61" t="str">
         <v/>
@@ -5758,28 +6172,28 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>99</v>
+        <v>3000</v>
       </c>
       <c r="B62" t="str">
         <v>both</v>
       </c>
       <c r="C62">
-        <v>185207.49</v>
+        <v>0</v>
       </c>
       <c r="D62">
-        <v>256748.52</v>
+        <v>0</v>
       </c>
       <c r="E62">
-        <v>277688</v>
+        <v>0</v>
       </c>
       <c r="F62">
-        <v>276576.2</v>
+        <v>0</v>
       </c>
       <c r="G62">
-        <v>296519.86</v>
+        <v>0</v>
       </c>
       <c r="H62">
-        <v>1292740.07</v>
+        <v>0</v>
       </c>
       <c r="I62" t="str">
         <v/>
@@ -5787,10 +6201,10 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>123623963915635</v>
+        <v>3001</v>
       </c>
       <c r="B63" t="str">
-        <v>spark only</v>
+        <v>both</v>
       </c>
       <c r="C63">
         <v>0</v>
@@ -5799,16 +6213,16 @@
         <v>0</v>
       </c>
       <c r="E63">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="F63">
         <v>0</v>
       </c>
       <c r="G63">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="H63">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="I63" t="str">
         <v/>
@@ -5816,43 +6230,333 @@
     </row>
     <row r="64">
       <c r="A64">
+        <v>3333</v>
+      </c>
+      <c r="B64" t="str">
+        <v>both</v>
+      </c>
+      <c r="C64">
+        <v>0</v>
+      </c>
+      <c r="D64">
+        <v>0</v>
+      </c>
+      <c r="E64">
+        <v>0</v>
+      </c>
+      <c r="F64">
+        <v>0</v>
+      </c>
+      <c r="G64">
+        <v>0</v>
+      </c>
+      <c r="H64">
+        <v>0</v>
+      </c>
+      <c r="I64" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>4011</v>
+      </c>
+      <c r="B65" t="str">
+        <v>both</v>
+      </c>
+      <c r="C65">
+        <v>0</v>
+      </c>
+      <c r="D65">
+        <v>0</v>
+      </c>
+      <c r="E65">
+        <v>0</v>
+      </c>
+      <c r="F65">
+        <v>0</v>
+      </c>
+      <c r="G65">
+        <v>0</v>
+      </c>
+      <c r="H65">
+        <v>0</v>
+      </c>
+      <c r="I65" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>4012</v>
+      </c>
+      <c r="B66" t="str">
+        <v>both</v>
+      </c>
+      <c r="C66">
+        <v>0</v>
+      </c>
+      <c r="D66">
+        <v>0</v>
+      </c>
+      <c r="E66">
+        <v>0</v>
+      </c>
+      <c r="F66">
+        <v>0</v>
+      </c>
+      <c r="G66">
+        <v>0</v>
+      </c>
+      <c r="H66">
+        <v>0</v>
+      </c>
+      <c r="I66" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>9998</v>
+      </c>
+      <c r="B67" t="str">
+        <v>both</v>
+      </c>
+      <c r="C67">
+        <v>0</v>
+      </c>
+      <c r="D67">
+        <v>0</v>
+      </c>
+      <c r="E67">
+        <v>0</v>
+      </c>
+      <c r="F67">
+        <v>0</v>
+      </c>
+      <c r="G67">
+        <v>0</v>
+      </c>
+      <c r="H67">
+        <v>0</v>
+      </c>
+      <c r="I67" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>13425</v>
+      </c>
+      <c r="B68" t="str">
+        <v>both</v>
+      </c>
+      <c r="C68">
+        <v>0</v>
+      </c>
+      <c r="D68">
+        <v>0</v>
+      </c>
+      <c r="E68">
+        <v>0</v>
+      </c>
+      <c r="F68">
+        <v>0</v>
+      </c>
+      <c r="G68">
+        <v>0</v>
+      </c>
+      <c r="H68">
+        <v>0</v>
+      </c>
+      <c r="I68" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v/>
+      </c>
+      <c r="B69" t="str">
+        <v/>
+      </c>
+      <c r="C69" t="str">
+        <v/>
+      </c>
+      <c r="D69" t="str">
+        <v/>
+      </c>
+      <c r="E69" t="str">
+        <v/>
+      </c>
+      <c r="F69" t="str">
+        <v/>
+      </c>
+      <c r="G69" t="str">
+        <v/>
+      </c>
+      <c r="H69" t="str">
+        <v/>
+      </c>
+      <c r="I69" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>── untagged ──</v>
+      </c>
+      <c r="B70" t="str">
+        <v/>
+      </c>
+      <c r="C70" t="str">
+        <v/>
+      </c>
+      <c r="D70" t="str">
+        <v/>
+      </c>
+      <c r="E70" t="str">
+        <v/>
+      </c>
+      <c r="F70" t="str">
+        <v/>
+      </c>
+      <c r="G70" t="str">
+        <v/>
+      </c>
+      <c r="H70" t="str">
+        <v/>
+      </c>
+      <c r="I70" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>-999999</v>
+      </c>
+      <c r="B71" t="str">
+        <v>ours only</v>
+      </c>
+      <c r="C71">
+        <v>17418.88</v>
+      </c>
+      <c r="D71">
+        <v>10907.25</v>
+      </c>
+      <c r="E71">
+        <v>25305.28</v>
+      </c>
+      <c r="F71">
+        <v>18026.83</v>
+      </c>
+      <c r="G71">
+        <v>15780.23</v>
+      </c>
+      <c r="H71">
+        <v>87438.47</v>
+      </c>
+      <c r="I71" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>99</v>
+      </c>
+      <c r="B72" t="str">
+        <v>both</v>
+      </c>
+      <c r="C72">
+        <v>185207.49</v>
+      </c>
+      <c r="D72">
+        <v>256748.52</v>
+      </c>
+      <c r="E72">
+        <v>277688</v>
+      </c>
+      <c r="F72">
+        <v>276576.2</v>
+      </c>
+      <c r="G72">
+        <v>296519.86</v>
+      </c>
+      <c r="H72">
+        <v>1292740.07</v>
+      </c>
+      <c r="I72" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>123623963915635</v>
+      </c>
+      <c r="B73" t="str">
+        <v>spark only</v>
+      </c>
+      <c r="C73">
+        <v>0</v>
+      </c>
+      <c r="D73">
+        <v>0</v>
+      </c>
+      <c r="E73">
+        <v>-0.01</v>
+      </c>
+      <c r="F73">
+        <v>0</v>
+      </c>
+      <c r="G73">
+        <v>-0.01</v>
+      </c>
+      <c r="H73">
+        <v>-0.02</v>
+      </c>
+      <c r="I73" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
         <v>90000000000000000000</v>
       </c>
-      <c r="B64" t="str">
+      <c r="B74" t="str">
         <v>spark only</v>
       </c>
-      <c r="C64">
+      <c r="C74">
         <v>-0.06</v>
       </c>
-      <c r="D64">
+      <c r="D74">
         <v>-0.01</v>
       </c>
-      <c r="E64">
-        <v>0</v>
-      </c>
-      <c r="F64">
-        <v>0</v>
-      </c>
-      <c r="G64">
-        <v>0</v>
-      </c>
-      <c r="H64">
+      <c r="E74">
+        <v>0</v>
+      </c>
+      <c r="F74">
+        <v>0</v>
+      </c>
+      <c r="G74">
+        <v>0</v>
+      </c>
+      <c r="H74">
         <v>-0.07</v>
       </c>
-      <c r="I64" t="str">
+      <c r="I74" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I64"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I74"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G60"/>
+  <dimension ref="A1:G70"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
@@ -5887,100 +6591,100 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>0</v>
+      <c r="A2" t="str">
+        <v>0 (spUSDC)</v>
       </c>
       <c r="B2" t="str">
         <v>ours only</v>
       </c>
       <c r="C2">
-        <v>79854.22</v>
+        <v>0</v>
       </c>
       <c r="D2">
-        <v>65755.52</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>73485.07</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>219094.81</v>
+        <v>0</v>
       </c>
       <c r="G2" t="str">
-        <v>Diff vs Spark = Chronicle farm (USDS-CLE) only. Spark does not track this farm.</v>
+        <v/>
       </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>1</v>
+      <c r="A3" t="str">
+        <v>0 (stUSDS)</v>
       </c>
       <c r="B3" t="str">
         <v>ours only</v>
       </c>
       <c r="C3">
-        <v>129628.4</v>
+        <v>0</v>
       </c>
       <c r="D3">
-        <v>96894.31</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>120811.71</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>347334.42</v>
+        <v>0</v>
       </c>
       <c r="G3" t="str">
-        <v>Diff vs Spark = Chronicle farm (USDS-CLE) only. Spark does not track this farm.</v>
+        <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>2</v>
+      <c r="A4" t="str">
+        <v>0 (sUSDC)</v>
       </c>
       <c r="B4" t="str">
         <v>ours only</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>12.77</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>13.93</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="G4" t="str">
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>10</v>
+      <c r="A5" t="str">
+        <v>0 (sUSDS)</v>
       </c>
       <c r="B5" t="str">
         <v>ours only</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>79746.04</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>65657.97</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>72961.66</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>218365.67</v>
       </c>
       <c r="G5" t="str">
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>100</v>
+      <c r="A6" t="str">
+        <v>0 (USDS-CLE)</v>
       </c>
       <c r="B6" t="str">
         <v>ours only</v>
@@ -5992,171 +6696,171 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>324.57</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>324.57</v>
       </c>
       <c r="G6" t="str">
-        <v/>
+        <v>Chronicle farm — not tracked by Spark.</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>127</v>
+      <c r="A7" t="str">
+        <v>0 (USDS-SKY)</v>
       </c>
       <c r="B7" t="str">
-        <v>both</v>
+        <v>ours only</v>
       </c>
       <c r="C7">
-        <v>-11305.25</v>
+        <v>93.87</v>
       </c>
       <c r="D7">
-        <v>-6522.52</v>
+        <v>84.78</v>
       </c>
       <c r="E7">
-        <v>-27534.46</v>
+        <v>4.31</v>
       </c>
       <c r="F7">
-        <v>-45362.23</v>
+        <v>182.96</v>
       </c>
       <c r="G7" t="str">
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>128</v>
+      <c r="A8" t="str">
+        <v>0 (USDS-SPK)</v>
       </c>
       <c r="B8" t="str">
-        <v>both</v>
+        <v>ours only</v>
       </c>
       <c r="C8">
-        <v>-292339.2</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>-191733.24</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>-253851.14</v>
+        <v>180.6</v>
       </c>
       <c r="F8">
-        <v>-737923.58</v>
+        <v>180.6</v>
       </c>
       <c r="G8" t="str">
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>129</v>
+      <c r="A9" t="str">
+        <v>1 (stUSDS)</v>
       </c>
       <c r="B9" t="str">
-        <v>both</v>
+        <v>ours only</v>
       </c>
       <c r="C9">
-        <v>-1.57</v>
+        <v>1800.55</v>
       </c>
       <c r="D9">
-        <v>-0.38</v>
+        <v>3037.92</v>
       </c>
       <c r="E9">
-        <v>-0.23</v>
+        <v>2945.79</v>
       </c>
       <c r="F9">
-        <v>-2.18</v>
+        <v>7784.26</v>
       </c>
       <c r="G9" t="str">
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>170</v>
+      <c r="A10" t="str">
+        <v>1 (sUSDS)</v>
       </c>
       <c r="B10" t="str">
-        <v>both</v>
+        <v>ours only</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>81433.39</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>66656.73</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>97033.4</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>245123.52</v>
       </c>
       <c r="G10" t="str">
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>171</v>
+      <c r="A11" t="str">
+        <v>1 (USDS-CLE)</v>
       </c>
       <c r="B11" t="str">
-        <v>both</v>
+        <v>ours only</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>5139.57</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>4193.83</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>6259.94</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>15593.34</v>
       </c>
       <c r="G11" t="str">
-        <v/>
+        <v>Chronicle farm — not tracked by Spark.</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>182</v>
+      <c r="A12" t="str">
+        <v>1 (USDS-SKY)</v>
       </c>
       <c r="B12" t="str">
-        <v>both</v>
+        <v>ours only</v>
       </c>
       <c r="C12">
-        <v>0.01</v>
+        <v>26939.34</v>
       </c>
       <c r="D12">
-        <v>0.01</v>
+        <v>5782.4</v>
       </c>
       <c r="E12">
-        <v>0.01</v>
+        <v>2741.32</v>
       </c>
       <c r="F12">
-        <v>0.03</v>
+        <v>35463.06</v>
       </c>
       <c r="G12" t="str">
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>183</v>
+      <c r="A13" t="str">
+        <v>1 (USDS-SPK)</v>
       </c>
       <c r="B13" t="str">
-        <v>both</v>
+        <v>ours only</v>
       </c>
       <c r="C13">
-        <v>-5.92</v>
+        <v>14315.55</v>
       </c>
       <c r="D13">
-        <v>2.63</v>
+        <v>17223.43</v>
       </c>
       <c r="E13">
-        <v>4.56</v>
+        <v>11831.25</v>
       </c>
       <c r="F13">
-        <v>1.27</v>
+        <v>43370.23</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -6164,22 +6868,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>186</v>
+        <v>2</v>
       </c>
       <c r="B14" t="str">
-        <v>both</v>
+        <v>ours only</v>
       </c>
       <c r="C14">
-        <v>-684.59</v>
+        <v>0</v>
       </c>
       <c r="D14">
-        <v>-918.21</v>
+        <v>0</v>
       </c>
       <c r="E14">
-        <v>-1727.2</v>
+        <v>0</v>
       </c>
       <c r="F14">
-        <v>-3330</v>
+        <v>0</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -6187,22 +6891,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>188</v>
+        <v>10</v>
       </c>
       <c r="B15" t="str">
-        <v>both</v>
+        <v>ours only</v>
       </c>
       <c r="C15">
-        <v>-711.57</v>
+        <v>0</v>
       </c>
       <c r="D15">
-        <v>-161.83</v>
+        <v>0</v>
       </c>
       <c r="E15">
-        <v>-9561.31</v>
+        <v>0</v>
       </c>
       <c r="F15">
-        <v>-10434.71</v>
+        <v>0</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -6210,22 +6914,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>190</v>
+        <v>100</v>
       </c>
       <c r="B16" t="str">
-        <v>both</v>
+        <v>ours only</v>
       </c>
       <c r="C16">
-        <v>-14421.49</v>
+        <v>0</v>
       </c>
       <c r="D16">
-        <v>-7690.97</v>
+        <v>0</v>
       </c>
       <c r="E16">
-        <v>-5975.1</v>
+        <v>0</v>
       </c>
       <c r="F16">
-        <v>-28087.56</v>
+        <v>0</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -6233,22 +6937,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>191</v>
+        <v>127</v>
       </c>
       <c r="B17" t="str">
         <v>both</v>
       </c>
       <c r="C17">
-        <v>-4608.45</v>
+        <v>-11305.25</v>
       </c>
       <c r="D17">
-        <v>-7101.14</v>
+        <v>-6522.52</v>
       </c>
       <c r="E17">
-        <v>-10750.47</v>
+        <v>-27534.46</v>
       </c>
       <c r="F17">
-        <v>-22460.06</v>
+        <v>-45362.23</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -6256,22 +6960,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>192</v>
+        <v>128</v>
       </c>
       <c r="B18" t="str">
         <v>both</v>
       </c>
       <c r="C18">
-        <v>-33983.76</v>
+        <v>-292339.2</v>
       </c>
       <c r="D18">
-        <v>-25010.79</v>
+        <v>-191733.24</v>
       </c>
       <c r="E18">
-        <v>-28921.53</v>
+        <v>-253851.14</v>
       </c>
       <c r="F18">
-        <v>-87916.08</v>
+        <v>-737923.58</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -6279,22 +6983,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>194</v>
+        <v>129</v>
       </c>
       <c r="B19" t="str">
         <v>both</v>
       </c>
       <c r="C19">
-        <v>-3.01</v>
+        <v>-1.57</v>
       </c>
       <c r="D19">
-        <v>-2.6</v>
+        <v>-0.38</v>
       </c>
       <c r="E19">
-        <v>-2.82</v>
+        <v>-0.23</v>
       </c>
       <c r="F19">
-        <v>-8.43</v>
+        <v>-2.18</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -6302,22 +7006,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>195</v>
+        <v>170</v>
       </c>
       <c r="B20" t="str">
         <v>both</v>
       </c>
       <c r="C20">
-        <v>-2327.51</v>
+        <v>0</v>
       </c>
       <c r="D20">
-        <v>-1000.51</v>
+        <v>0</v>
       </c>
       <c r="E20">
-        <v>-4561.24</v>
+        <v>0</v>
       </c>
       <c r="F20">
-        <v>-7889.26</v>
+        <v>0</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -6325,22 +7029,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>196</v>
+        <v>171</v>
       </c>
       <c r="B21" t="str">
         <v>both</v>
       </c>
       <c r="C21">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="D21">
-        <v>-0.11</v>
+        <v>0</v>
       </c>
       <c r="E21">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="F21">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -6348,22 +7052,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>197</v>
+        <v>182</v>
       </c>
       <c r="B22" t="str">
         <v>both</v>
       </c>
       <c r="C22">
-        <v>-27119.81</v>
+        <v>0.01</v>
       </c>
       <c r="D22">
-        <v>-25149.75</v>
+        <v>0.01</v>
       </c>
       <c r="E22">
-        <v>6.87</v>
+        <v>0.01</v>
       </c>
       <c r="F22">
-        <v>-52262.69</v>
+        <v>0.03</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -6371,22 +7075,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>198</v>
+        <v>183</v>
       </c>
       <c r="B23" t="str">
         <v>both</v>
       </c>
       <c r="C23">
-        <v>0.02</v>
+        <v>-5.92</v>
       </c>
       <c r="D23">
-        <v>0.02</v>
+        <v>2.63</v>
       </c>
       <c r="E23">
-        <v>0.02</v>
+        <v>4.56</v>
       </c>
       <c r="F23">
-        <v>0.06</v>
+        <v>1.27</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -6394,22 +7098,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>200</v>
+        <v>186</v>
       </c>
       <c r="B24" t="str">
         <v>both</v>
       </c>
       <c r="C24">
-        <v>-2.74</v>
+        <v>-684.59</v>
       </c>
       <c r="D24">
-        <v>-0.85</v>
+        <v>-918.21</v>
       </c>
       <c r="E24">
-        <v>-7.61</v>
+        <v>-1727.2</v>
       </c>
       <c r="F24">
-        <v>-11.2</v>
+        <v>-3330</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -6417,22 +7121,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>202</v>
+        <v>188</v>
       </c>
       <c r="B25" t="str">
         <v>both</v>
       </c>
       <c r="C25">
-        <v>-39.86</v>
+        <v>-711.57</v>
       </c>
       <c r="D25">
-        <v>-44.41</v>
+        <v>-161.83</v>
       </c>
       <c r="E25">
-        <v>-55.54</v>
+        <v>-9561.31</v>
       </c>
       <c r="F25">
-        <v>-139.81</v>
+        <v>-10434.71</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -6440,22 +7144,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="B26" t="str">
         <v>both</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>-14421.49</v>
       </c>
       <c r="D26">
-        <v>-2.39</v>
+        <v>-7690.97</v>
       </c>
       <c r="E26">
-        <v>-24.69</v>
+        <v>-5975.1</v>
       </c>
       <c r="F26">
-        <v>-27.08</v>
+        <v>-28087.56</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -6463,22 +7167,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>205</v>
+        <v>191</v>
       </c>
       <c r="B27" t="str">
         <v>both</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>-4608.45</v>
       </c>
       <c r="D27">
-        <v>0.02</v>
+        <v>-7101.14</v>
       </c>
       <c r="E27">
-        <v>-0.3</v>
+        <v>-10750.47</v>
       </c>
       <c r="F27">
-        <v>-0.28</v>
+        <v>-22460.06</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -6486,22 +7190,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="B28" t="str">
-        <v>ours only</v>
+        <v>both</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>-33983.76</v>
       </c>
       <c r="D28">
-        <v>0</v>
+        <v>-25010.79</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>-28921.53</v>
       </c>
       <c r="F28">
-        <v>0</v>
+        <v>-87916.08</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -6509,22 +7213,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>214</v>
+        <v>194</v>
       </c>
       <c r="B29" t="str">
-        <v>ours only</v>
+        <v>both</v>
       </c>
       <c r="C29">
-        <v>0</v>
+        <v>-3.01</v>
       </c>
       <c r="D29">
-        <v>0</v>
+        <v>-2.6</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>-2.82</v>
       </c>
       <c r="F29">
-        <v>0</v>
+        <v>-8.43</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -6532,22 +7236,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>216</v>
+        <v>195</v>
       </c>
       <c r="B30" t="str">
         <v>both</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>-2327.51</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>-1000.51</v>
       </c>
       <c r="E30">
-        <v>-129.73</v>
+        <v>-4561.24</v>
       </c>
       <c r="F30">
-        <v>-129.73</v>
+        <v>-7889.26</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -6555,22 +7259,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>219</v>
+        <v>196</v>
       </c>
       <c r="B31" t="str">
         <v>both</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="D31">
-        <v>0</v>
+        <v>-0.11</v>
       </c>
       <c r="E31">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="F31">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -6578,22 +7282,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>223</v>
+        <v>197</v>
       </c>
       <c r="B32" t="str">
-        <v>ours only</v>
+        <v>both</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>-27119.81</v>
       </c>
       <c r="D32">
-        <v>0</v>
+        <v>-25149.75</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>6.87</v>
       </c>
       <c r="F32">
-        <v>0</v>
+        <v>-52262.69</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -6601,22 +7305,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>224</v>
+        <v>198</v>
       </c>
       <c r="B33" t="str">
-        <v>ours only</v>
+        <v>both</v>
       </c>
       <c r="C33">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="F33">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -6624,22 +7328,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>303</v>
+        <v>200</v>
       </c>
       <c r="B34" t="str">
         <v>both</v>
       </c>
       <c r="C34">
-        <v>0</v>
+        <v>-2.74</v>
       </c>
       <c r="D34">
-        <v>0</v>
+        <v>-0.85</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>-7.61</v>
       </c>
       <c r="F34">
-        <v>0</v>
+        <v>-11.2</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -6647,22 +7351,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>555</v>
+        <v>202</v>
       </c>
       <c r="B35" t="str">
         <v>both</v>
       </c>
       <c r="C35">
-        <v>0</v>
+        <v>-39.86</v>
       </c>
       <c r="D35">
-        <v>0</v>
+        <v>-44.41</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>-55.54</v>
       </c>
       <c r="F35">
-        <v>0</v>
+        <v>-139.81</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -6670,22 +7374,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>1001</v>
+        <v>204</v>
       </c>
       <c r="B36" t="str">
         <v>both</v>
       </c>
       <c r="C36">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="D36">
-        <v>1601.44</v>
+        <v>-2.39</v>
       </c>
       <c r="E36">
-        <v>1655.49</v>
+        <v>-24.69</v>
       </c>
       <c r="F36">
-        <v>3256.73</v>
+        <v>-27.08</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -6693,22 +7397,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>1002</v>
+        <v>205</v>
       </c>
       <c r="B37" t="str">
         <v>both</v>
       </c>
       <c r="C37">
-        <v>-0.49</v>
+        <v>0</v>
       </c>
       <c r="D37">
-        <v>2.21</v>
+        <v>0.02</v>
       </c>
       <c r="E37">
-        <v>12.53</v>
+        <v>-0.3</v>
       </c>
       <c r="F37">
-        <v>14.25</v>
+        <v>-0.28</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -6716,22 +7420,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>1003</v>
+        <v>206</v>
       </c>
       <c r="B38" t="str">
-        <v>amatsu only</v>
+        <v>ours only</v>
       </c>
       <c r="C38">
-        <v>-67207.7</v>
+        <v>0</v>
       </c>
       <c r="D38">
-        <v>-52633.8</v>
+        <v>0</v>
       </c>
       <c r="E38">
-        <v>-58463.7</v>
+        <v>0</v>
       </c>
       <c r="F38">
-        <v>-178305.2</v>
+        <v>0</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -6739,22 +7443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>1004</v>
+        <v>214</v>
       </c>
       <c r="B39" t="str">
-        <v>both</v>
+        <v>ours only</v>
       </c>
       <c r="C39">
-        <v>-228.59</v>
+        <v>0</v>
       </c>
       <c r="D39">
-        <v>-266.4</v>
+        <v>0</v>
       </c>
       <c r="E39">
-        <v>-529.59</v>
+        <v>0</v>
       </c>
       <c r="F39">
-        <v>-1024.58</v>
+        <v>0</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -6762,22 +7466,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>1007</v>
+        <v>216</v>
       </c>
       <c r="B40" t="str">
         <v>both</v>
       </c>
       <c r="C40">
-        <v>-0.29</v>
+        <v>0</v>
       </c>
       <c r="D40">
-        <v>-1.54</v>
+        <v>0</v>
       </c>
       <c r="E40">
-        <v>7.33</v>
+        <v>-129.73</v>
       </c>
       <c r="F40">
-        <v>5.5</v>
+        <v>-129.73</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -6785,7 +7489,7 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>1015</v>
+        <v>219</v>
       </c>
       <c r="B41" t="str">
         <v>both</v>
@@ -6808,22 +7512,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>1016</v>
+        <v>223</v>
       </c>
       <c r="B42" t="str">
-        <v>both</v>
+        <v>ours only</v>
       </c>
       <c r="C42">
-        <v>-3596.75</v>
+        <v>0</v>
       </c>
       <c r="D42">
-        <v>-3197.86</v>
+        <v>0</v>
       </c>
       <c r="E42">
-        <v>-4503.92</v>
+        <v>0</v>
       </c>
       <c r="F42">
-        <v>-11298.53</v>
+        <v>0</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -6831,22 +7535,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>1017</v>
+        <v>224</v>
       </c>
       <c r="B43" t="str">
-        <v>both</v>
+        <v>ours only</v>
       </c>
       <c r="C43">
-        <v>-320.85</v>
+        <v>0</v>
       </c>
       <c r="D43">
-        <v>-209.86</v>
+        <v>0</v>
       </c>
       <c r="E43">
-        <v>-221.4</v>
+        <v>0</v>
       </c>
       <c r="F43">
-        <v>-752.11</v>
+        <v>0</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -6854,7 +7558,7 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>2000</v>
+        <v>303</v>
       </c>
       <c r="B44" t="str">
         <v>both</v>
@@ -6877,7 +7581,7 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>2001</v>
+        <v>555</v>
       </c>
       <c r="B45" t="str">
         <v>both</v>
@@ -6900,22 +7604,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>2002</v>
+        <v>1001</v>
       </c>
       <c r="B46" t="str">
         <v>both</v>
       </c>
       <c r="C46">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="D46">
-        <v>0</v>
+        <v>1601.44</v>
       </c>
       <c r="E46">
-        <v>61.28</v>
+        <v>1655.49</v>
       </c>
       <c r="F46">
-        <v>61.28</v>
+        <v>3256.73</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -6923,22 +7627,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>2003</v>
+        <v>1002</v>
       </c>
       <c r="B47" t="str">
         <v>both</v>
       </c>
       <c r="C47">
-        <v>0</v>
+        <v>-0.49</v>
       </c>
       <c r="D47">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="E47">
-        <v>0</v>
+        <v>12.53</v>
       </c>
       <c r="F47">
-        <v>0</v>
+        <v>14.25</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -6946,22 +7650,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>2005</v>
+        <v>1003</v>
       </c>
       <c r="B48" t="str">
-        <v>both</v>
+        <v>amatsu only</v>
       </c>
       <c r="C48">
-        <v>0</v>
+        <v>-67207.7</v>
       </c>
       <c r="D48">
-        <v>0</v>
+        <v>-52633.8</v>
       </c>
       <c r="E48">
-        <v>15.07</v>
+        <v>-58463.7</v>
       </c>
       <c r="F48">
-        <v>15.07</v>
+        <v>-178305.2</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -6969,22 +7673,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>2008</v>
+        <v>1004</v>
       </c>
       <c r="B49" t="str">
-        <v>ours only</v>
+        <v>both</v>
       </c>
       <c r="C49">
-        <v>0</v>
+        <v>-228.59</v>
       </c>
       <c r="D49">
-        <v>0</v>
+        <v>-266.4</v>
       </c>
       <c r="E49">
-        <v>0</v>
+        <v>-529.59</v>
       </c>
       <c r="F49">
-        <v>0</v>
+        <v>-1024.58</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -6992,22 +7696,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>2222</v>
+        <v>1007</v>
       </c>
       <c r="B50" t="str">
         <v>both</v>
       </c>
       <c r="C50">
-        <v>0</v>
+        <v>-0.29</v>
       </c>
       <c r="D50">
-        <v>0</v>
+        <v>-1.54</v>
       </c>
       <c r="E50">
-        <v>0</v>
+        <v>7.33</v>
       </c>
       <c r="F50">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -7015,10 +7719,10 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>3000</v>
+        <v>1015</v>
       </c>
       <c r="B51" t="str">
-        <v>ours only</v>
+        <v>both</v>
       </c>
       <c r="C51">
         <v>0</v>
@@ -7038,22 +7742,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>3001</v>
+        <v>1016</v>
       </c>
       <c r="B52" t="str">
-        <v>ours only</v>
+        <v>both</v>
       </c>
       <c r="C52">
-        <v>0</v>
+        <v>-3596.75</v>
       </c>
       <c r="D52">
-        <v>0</v>
+        <v>-3197.86</v>
       </c>
       <c r="E52">
-        <v>0</v>
+        <v>-4503.92</v>
       </c>
       <c r="F52">
-        <v>0</v>
+        <v>-11298.53</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -7061,22 +7765,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>3333</v>
+        <v>1017</v>
       </c>
       <c r="B53" t="str">
-        <v>ours only</v>
+        <v>both</v>
       </c>
       <c r="C53">
-        <v>0.71</v>
+        <v>-320.85</v>
       </c>
       <c r="D53">
-        <v>0.41</v>
+        <v>-209.86</v>
       </c>
       <c r="E53">
-        <v>0.48</v>
+        <v>-221.4</v>
       </c>
       <c r="F53">
-        <v>1.6</v>
+        <v>-752.11</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -7084,10 +7788,10 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>4011</v>
+        <v>2000</v>
       </c>
       <c r="B54" t="str">
-        <v>ours only</v>
+        <v>both</v>
       </c>
       <c r="C54">
         <v>0</v>
@@ -7107,10 +7811,10 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>4012</v>
+        <v>2001</v>
       </c>
       <c r="B55" t="str">
-        <v>ours only</v>
+        <v>both</v>
       </c>
       <c r="C55">
         <v>0</v>
@@ -7130,10 +7834,10 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>9998</v>
+        <v>2002</v>
       </c>
       <c r="B56" t="str">
-        <v>ours only</v>
+        <v>both</v>
       </c>
       <c r="C56">
         <v>0</v>
@@ -7142,10 +7846,10 @@
         <v>0</v>
       </c>
       <c r="E56">
-        <v>0</v>
+        <v>61.28</v>
       </c>
       <c r="F56">
-        <v>0</v>
+        <v>61.28</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -7153,106 +7857,336 @@
     </row>
     <row r="57">
       <c r="A57">
+        <v>2003</v>
+      </c>
+      <c r="B57" t="str">
+        <v>both</v>
+      </c>
+      <c r="C57">
+        <v>0</v>
+      </c>
+      <c r="D57">
+        <v>0</v>
+      </c>
+      <c r="E57">
+        <v>0</v>
+      </c>
+      <c r="F57">
+        <v>0</v>
+      </c>
+      <c r="G57" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>2005</v>
+      </c>
+      <c r="B58" t="str">
+        <v>both</v>
+      </c>
+      <c r="C58">
+        <v>0</v>
+      </c>
+      <c r="D58">
+        <v>0</v>
+      </c>
+      <c r="E58">
+        <v>15.07</v>
+      </c>
+      <c r="F58">
+        <v>15.07</v>
+      </c>
+      <c r="G58" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>2008</v>
+      </c>
+      <c r="B59" t="str">
+        <v>ours only</v>
+      </c>
+      <c r="C59">
+        <v>0</v>
+      </c>
+      <c r="D59">
+        <v>0</v>
+      </c>
+      <c r="E59">
+        <v>0</v>
+      </c>
+      <c r="F59">
+        <v>0</v>
+      </c>
+      <c r="G59" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>2222</v>
+      </c>
+      <c r="B60" t="str">
+        <v>both</v>
+      </c>
+      <c r="C60">
+        <v>0</v>
+      </c>
+      <c r="D60">
+        <v>0</v>
+      </c>
+      <c r="E60">
+        <v>0</v>
+      </c>
+      <c r="F60">
+        <v>0</v>
+      </c>
+      <c r="G60" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>3000</v>
+      </c>
+      <c r="B61" t="str">
+        <v>ours only</v>
+      </c>
+      <c r="C61">
+        <v>0</v>
+      </c>
+      <c r="D61">
+        <v>0</v>
+      </c>
+      <c r="E61">
+        <v>0</v>
+      </c>
+      <c r="F61">
+        <v>0</v>
+      </c>
+      <c r="G61" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>3001</v>
+      </c>
+      <c r="B62" t="str">
+        <v>ours only</v>
+      </c>
+      <c r="C62">
+        <v>0</v>
+      </c>
+      <c r="D62">
+        <v>0</v>
+      </c>
+      <c r="E62">
+        <v>0</v>
+      </c>
+      <c r="F62">
+        <v>0</v>
+      </c>
+      <c r="G62" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>3333</v>
+      </c>
+      <c r="B63" t="str">
+        <v>ours only</v>
+      </c>
+      <c r="C63">
+        <v>0.71</v>
+      </c>
+      <c r="D63">
+        <v>0.41</v>
+      </c>
+      <c r="E63">
+        <v>0.48</v>
+      </c>
+      <c r="F63">
+        <v>1.6</v>
+      </c>
+      <c r="G63" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>4011</v>
+      </c>
+      <c r="B64" t="str">
+        <v>ours only</v>
+      </c>
+      <c r="C64">
+        <v>0</v>
+      </c>
+      <c r="D64">
+        <v>0</v>
+      </c>
+      <c r="E64">
+        <v>0</v>
+      </c>
+      <c r="F64">
+        <v>0</v>
+      </c>
+      <c r="G64" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>4012</v>
+      </c>
+      <c r="B65" t="str">
+        <v>ours only</v>
+      </c>
+      <c r="C65">
+        <v>0</v>
+      </c>
+      <c r="D65">
+        <v>0</v>
+      </c>
+      <c r="E65">
+        <v>0</v>
+      </c>
+      <c r="F65">
+        <v>0</v>
+      </c>
+      <c r="G65" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>9998</v>
+      </c>
+      <c r="B66" t="str">
+        <v>ours only</v>
+      </c>
+      <c r="C66">
+        <v>0</v>
+      </c>
+      <c r="D66">
+        <v>0</v>
+      </c>
+      <c r="E66">
+        <v>0</v>
+      </c>
+      <c r="F66">
+        <v>0</v>
+      </c>
+      <c r="G66" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
         <v>13425</v>
       </c>
-      <c r="B57" t="str">
+      <c r="B67" t="str">
         <v>ours only</v>
       </c>
-      <c r="C57">
+      <c r="C67">
         <v>858.01</v>
       </c>
-      <c r="D57">
+      <c r="D67">
         <v>774.97</v>
       </c>
-      <c r="E57">
+      <c r="E67">
         <v>858.01</v>
       </c>
-      <c r="F57">
+      <c r="F67">
         <v>2490.99</v>
       </c>
-      <c r="G57" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="str">
-        <v/>
-      </c>
-      <c r="B58" t="str">
-        <v/>
-      </c>
-      <c r="C58" t="str">
-        <v/>
-      </c>
-      <c r="D58" t="str">
-        <v/>
-      </c>
-      <c r="E58" t="str">
-        <v/>
-      </c>
-      <c r="F58" t="str">
-        <v/>
-      </c>
-      <c r="G58" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="str">
+      <c r="G67" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v/>
+      </c>
+      <c r="B68" t="str">
+        <v/>
+      </c>
+      <c r="C68" t="str">
+        <v/>
+      </c>
+      <c r="D68" t="str">
+        <v/>
+      </c>
+      <c r="E68" t="str">
+        <v/>
+      </c>
+      <c r="F68" t="str">
+        <v/>
+      </c>
+      <c r="G68" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
         <v>── untagged ──</v>
       </c>
-      <c r="B59" t="str">
-        <v/>
-      </c>
-      <c r="C59" t="str">
-        <v/>
-      </c>
-      <c r="D59" t="str">
-        <v/>
-      </c>
-      <c r="E59" t="str">
-        <v/>
-      </c>
-      <c r="F59" t="str">
-        <v/>
-      </c>
-      <c r="G59" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="str">
+      <c r="B69" t="str">
+        <v/>
+      </c>
+      <c r="C69" t="str">
+        <v/>
+      </c>
+      <c r="D69" t="str">
+        <v/>
+      </c>
+      <c r="E69" t="str">
+        <v/>
+      </c>
+      <c r="F69" t="str">
+        <v/>
+      </c>
+      <c r="G69" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
         <v>untagged</v>
       </c>
-      <c r="B60" t="str">
-        <v>both</v>
-      </c>
-      <c r="C60">
+      <c r="B70" t="str">
+        <v>both</v>
+      </c>
+      <c r="C70">
         <v>61884.66</v>
       </c>
-      <c r="D60">
+      <c r="D70">
         <v>43197.23</v>
       </c>
-      <c r="E60">
+      <c r="E70">
         <v>70821.38</v>
       </c>
-      <c r="F60">
+      <c r="F70">
         <v>175903.27</v>
       </c>
-      <c r="G60" t="str">
+      <c r="G70" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G60"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G70"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G62"/>
+  <dimension ref="A1:G70"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
@@ -7287,230 +8221,230 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>0</v>
+      <c r="A2" t="str">
+        <v>0 (spUSDC)</v>
       </c>
       <c r="B2" t="str">
         <v>spark only</v>
       </c>
       <c r="C2">
-        <v>79854.22</v>
+        <v>0</v>
       </c>
       <c r="D2">
-        <v>65755.52</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>73160.49</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>218770.23</v>
+        <v>0</v>
       </c>
       <c r="G2" t="str">
-        <v>Diff vs Spark = Chronicle farm (USDS-CLE) only. Spark does not track this farm.</v>
+        <v/>
       </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>1</v>
+      <c r="A3" t="str">
+        <v>0 (stUSDS)</v>
       </c>
       <c r="B3" t="str">
         <v>spark only</v>
       </c>
       <c r="C3">
-        <v>124488.83</v>
+        <v>0</v>
       </c>
       <c r="D3">
-        <v>92700.48</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>114551.76</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>331741.07</v>
+        <v>0</v>
       </c>
       <c r="G3" t="str">
-        <v>Diff vs Spark = Chronicle farm (USDS-CLE) only. Spark does not track this farm.</v>
+        <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>2</v>
+      <c r="A4" t="str">
+        <v>0 (sUSDC)</v>
       </c>
       <c r="B4" t="str">
         <v>spark only</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>12.77</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>13.93</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="G4" t="str">
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>126</v>
+      <c r="A5" t="str">
+        <v>0 (sUSDS)</v>
       </c>
       <c r="B5" t="str">
         <v>spark only</v>
       </c>
       <c r="C5">
-        <v>106392.55</v>
+        <v>79746.04</v>
       </c>
       <c r="D5">
-        <v>114516.89</v>
+        <v>65657.97</v>
       </c>
       <c r="E5">
-        <v>122957.88</v>
+        <v>72961.66</v>
       </c>
       <c r="F5">
-        <v>343867.32</v>
+        <v>218365.67</v>
       </c>
       <c r="G5" t="str">
-        <v>Subproxy holdings, no DR applied. Handled in Supply Side MSC.</v>
+        <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>127</v>
+      <c r="A6" t="str">
+        <v>0 (USDS-SKY)</v>
       </c>
       <c r="B6" t="str">
-        <v>both</v>
+        <v>spark only</v>
       </c>
       <c r="C6">
-        <v>-10859.98</v>
+        <v>93.87</v>
       </c>
       <c r="D6">
-        <v>-6313.93</v>
+        <v>84.78</v>
       </c>
       <c r="E6">
-        <v>-27182.98</v>
+        <v>4.31</v>
       </c>
       <c r="F6">
-        <v>-44356.89</v>
+        <v>182.96</v>
       </c>
       <c r="G6" t="str">
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>128</v>
+      <c r="A7" t="str">
+        <v>0 (USDS-SPK)</v>
       </c>
       <c r="B7" t="str">
-        <v>both</v>
+        <v>spark only</v>
       </c>
       <c r="C7">
-        <v>-296403.31</v>
+        <v>0</v>
       </c>
       <c r="D7">
-        <v>-195898.7</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>-252945.74</v>
+        <v>180.6</v>
       </c>
       <c r="F7">
-        <v>-745247.75</v>
+        <v>180.6</v>
       </c>
       <c r="G7" t="str">
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>129</v>
+      <c r="A8" t="str">
+        <v>1 (stUSDS)</v>
       </c>
       <c r="B8" t="str">
-        <v>both</v>
+        <v>spark only</v>
       </c>
       <c r="C8">
-        <v>-1.57</v>
+        <v>1800.55</v>
       </c>
       <c r="D8">
-        <v>-0.38</v>
+        <v>3037.92</v>
       </c>
       <c r="E8">
-        <v>-0.23</v>
+        <v>2945.79</v>
       </c>
       <c r="F8">
-        <v>-2.18</v>
+        <v>7784.26</v>
       </c>
       <c r="G8" t="str">
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>130</v>
+      <c r="A9" t="str">
+        <v>1 (sUSDS)</v>
       </c>
       <c r="B9" t="str">
         <v>spark only</v>
       </c>
       <c r="C9">
-        <v>266.96</v>
+        <v>81433.39</v>
       </c>
       <c r="D9">
-        <v>252.94</v>
+        <v>66656.73</v>
       </c>
       <c r="E9">
-        <v>3701.44</v>
+        <v>97033.4</v>
       </c>
       <c r="F9">
-        <v>4221.34</v>
+        <v>245123.52</v>
       </c>
       <c r="G9" t="str">
-        <v>Found in Spark datasets only, no onchain events.</v>
+        <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>170</v>
+      <c r="A10" t="str">
+        <v>1 (USDS-SKY)</v>
       </c>
       <c r="B10" t="str">
-        <v>both</v>
+        <v>spark only</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>26939.34</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>5782.4</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>2741.32</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>35463.06</v>
       </c>
       <c r="G10" t="str">
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>171</v>
+      <c r="A11" t="str">
+        <v>1 (USDS-SPK)</v>
       </c>
       <c r="B11" t="str">
-        <v>both</v>
+        <v>spark only</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>14315.55</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>17223.43</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>11831.25</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>43370.23</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -7518,22 +8452,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>182</v>
+        <v>2</v>
       </c>
       <c r="B12" t="str">
-        <v>both</v>
+        <v>spark only</v>
       </c>
       <c r="C12">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="D12">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="E12">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="F12">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -7541,45 +8475,45 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>183</v>
+        <v>126</v>
       </c>
       <c r="B13" t="str">
-        <v>both</v>
+        <v>spark only</v>
       </c>
       <c r="C13">
-        <v>-5.92</v>
+        <v>106392.55</v>
       </c>
       <c r="D13">
-        <v>2.63</v>
+        <v>114516.89</v>
       </c>
       <c r="E13">
-        <v>4.56</v>
+        <v>122957.88</v>
       </c>
       <c r="F13">
-        <v>1.27</v>
+        <v>343867.32</v>
       </c>
       <c r="G13" t="str">
-        <v/>
+        <v>Subproxy holdings, no DR applied. Handled in Supply Side MSC.</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>186</v>
+        <v>127</v>
       </c>
       <c r="B14" t="str">
         <v>both</v>
       </c>
       <c r="C14">
-        <v>-684.59</v>
+        <v>-10859.98</v>
       </c>
       <c r="D14">
-        <v>-918.21</v>
+        <v>-6313.93</v>
       </c>
       <c r="E14">
-        <v>-1727.2</v>
+        <v>-27182.98</v>
       </c>
       <c r="F14">
-        <v>-3330</v>
+        <v>-44356.89</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -7587,22 +8521,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>188</v>
+        <v>128</v>
       </c>
       <c r="B15" t="str">
         <v>both</v>
       </c>
       <c r="C15">
-        <v>-711.58</v>
+        <v>-296403.31</v>
       </c>
       <c r="D15">
-        <v>-161.84</v>
+        <v>-195898.7</v>
       </c>
       <c r="E15">
-        <v>-7105.91</v>
+        <v>-252945.74</v>
       </c>
       <c r="F15">
-        <v>-7979.33</v>
+        <v>-745247.75</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -7610,22 +8544,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>190</v>
+        <v>129</v>
       </c>
       <c r="B16" t="str">
         <v>both</v>
       </c>
       <c r="C16">
-        <v>-14421.49</v>
+        <v>-1.57</v>
       </c>
       <c r="D16">
-        <v>-7690.97</v>
+        <v>-0.38</v>
       </c>
       <c r="E16">
-        <v>-5975.1</v>
+        <v>-0.23</v>
       </c>
       <c r="F16">
-        <v>-28087.56</v>
+        <v>-2.18</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -7633,45 +8567,45 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>191</v>
+        <v>130</v>
       </c>
       <c r="B17" t="str">
-        <v>both</v>
+        <v>spark only</v>
       </c>
       <c r="C17">
-        <v>-4608.45</v>
+        <v>266.96</v>
       </c>
       <c r="D17">
-        <v>-7101.14</v>
+        <v>252.94</v>
       </c>
       <c r="E17">
-        <v>-10750.47</v>
+        <v>3701.44</v>
       </c>
       <c r="F17">
-        <v>-22460.06</v>
+        <v>4221.34</v>
       </c>
       <c r="G17" t="str">
-        <v/>
+        <v>Found in Spark datasets only, no onchain events.</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>192</v>
+        <v>170</v>
       </c>
       <c r="B18" t="str">
         <v>both</v>
       </c>
       <c r="C18">
-        <v>-33983.76</v>
+        <v>0</v>
       </c>
       <c r="D18">
-        <v>-25010.79</v>
+        <v>0</v>
       </c>
       <c r="E18">
-        <v>-28921.53</v>
+        <v>0</v>
       </c>
       <c r="F18">
-        <v>-87916.08</v>
+        <v>0</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -7679,22 +8613,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>194</v>
+        <v>171</v>
       </c>
       <c r="B19" t="str">
         <v>both</v>
       </c>
       <c r="C19">
-        <v>-3.01</v>
+        <v>0</v>
       </c>
       <c r="D19">
-        <v>-2.6</v>
+        <v>0</v>
       </c>
       <c r="E19">
-        <v>-2.82</v>
+        <v>0</v>
       </c>
       <c r="F19">
-        <v>-8.43</v>
+        <v>0</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -7702,22 +8636,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="B20" t="str">
         <v>both</v>
       </c>
       <c r="C20">
-        <v>-2327.51</v>
+        <v>0.01</v>
       </c>
       <c r="D20">
-        <v>-1000.51</v>
+        <v>0.01</v>
       </c>
       <c r="E20">
-        <v>-4561.24</v>
+        <v>0.01</v>
       </c>
       <c r="F20">
-        <v>-7889.26</v>
+        <v>0.03</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -7725,22 +8659,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="B21" t="str">
         <v>both</v>
       </c>
       <c r="C21">
-        <v>0.01</v>
+        <v>-5.92</v>
       </c>
       <c r="D21">
-        <v>-0.11</v>
+        <v>2.63</v>
       </c>
       <c r="E21">
-        <v>-0.2</v>
+        <v>4.56</v>
       </c>
       <c r="F21">
-        <v>-0.3</v>
+        <v>1.27</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -7748,22 +8682,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="B22" t="str">
         <v>both</v>
       </c>
       <c r="C22">
-        <v>-27119.81</v>
+        <v>-684.59</v>
       </c>
       <c r="D22">
-        <v>-25149.75</v>
+        <v>-918.21</v>
       </c>
       <c r="E22">
-        <v>6.87</v>
+        <v>-1727.2</v>
       </c>
       <c r="F22">
-        <v>-52262.69</v>
+        <v>-3330</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -7771,22 +8705,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="B23" t="str">
         <v>both</v>
       </c>
       <c r="C23">
-        <v>0.02</v>
+        <v>-711.58</v>
       </c>
       <c r="D23">
-        <v>0.02</v>
+        <v>-161.84</v>
       </c>
       <c r="E23">
-        <v>0.02</v>
+        <v>-7105.91</v>
       </c>
       <c r="F23">
-        <v>0.06</v>
+        <v>-7979.33</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -7794,22 +8728,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="B24" t="str">
         <v>both</v>
       </c>
       <c r="C24">
-        <v>-2.74</v>
+        <v>-14421.49</v>
       </c>
       <c r="D24">
-        <v>-0.85</v>
+        <v>-7690.97</v>
       </c>
       <c r="E24">
-        <v>-7.61</v>
+        <v>-5975.1</v>
       </c>
       <c r="F24">
-        <v>-11.2</v>
+        <v>-28087.56</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -7817,22 +8751,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="B25" t="str">
         <v>both</v>
       </c>
       <c r="C25">
-        <v>-39.86</v>
+        <v>-4608.45</v>
       </c>
       <c r="D25">
-        <v>-44.41</v>
+        <v>-7101.14</v>
       </c>
       <c r="E25">
-        <v>-55.54</v>
+        <v>-10750.47</v>
       </c>
       <c r="F25">
-        <v>-139.81</v>
+        <v>-22460.06</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -7840,22 +8774,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="B26" t="str">
         <v>both</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>-33983.76</v>
       </c>
       <c r="D26">
-        <v>-2.39</v>
+        <v>-25010.79</v>
       </c>
       <c r="E26">
-        <v>-24.69</v>
+        <v>-28921.53</v>
       </c>
       <c r="F26">
-        <v>-27.08</v>
+        <v>-87916.08</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -7863,22 +8797,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="B27" t="str">
         <v>both</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>-3.01</v>
       </c>
       <c r="D27">
-        <v>0.02</v>
+        <v>-2.6</v>
       </c>
       <c r="E27">
-        <v>-0.3</v>
+        <v>-2.82</v>
       </c>
       <c r="F27">
-        <v>-0.28</v>
+        <v>-8.43</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -7886,22 +8820,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="B28" t="str">
-        <v>spark only</v>
+        <v>both</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>-2327.51</v>
       </c>
       <c r="D28">
-        <v>0</v>
+        <v>-1000.51</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>-4561.24</v>
       </c>
       <c r="F28">
-        <v>0</v>
+        <v>-7889.26</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -7909,22 +8843,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>214</v>
+        <v>196</v>
       </c>
       <c r="B29" t="str">
-        <v>spark only</v>
+        <v>both</v>
       </c>
       <c r="C29">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="D29">
-        <v>0</v>
+        <v>-0.11</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="F29">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -7932,22 +8866,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>216</v>
+        <v>197</v>
       </c>
       <c r="B30" t="str">
         <v>both</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>-27119.81</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>-25149.75</v>
       </c>
       <c r="E30">
-        <v>-129.73</v>
+        <v>6.87</v>
       </c>
       <c r="F30">
-        <v>-129.73</v>
+        <v>-52262.69</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -7955,22 +8889,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>219</v>
+        <v>198</v>
       </c>
       <c r="B31" t="str">
         <v>both</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="D31">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="E31">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="F31">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -7978,22 +8912,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>223</v>
+        <v>200</v>
       </c>
       <c r="B32" t="str">
-        <v>spark only</v>
+        <v>both</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>-2.74</v>
       </c>
       <c r="D32">
-        <v>0</v>
+        <v>-0.85</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>-7.61</v>
       </c>
       <c r="F32">
-        <v>0</v>
+        <v>-11.2</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -8001,22 +8935,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>224</v>
+        <v>202</v>
       </c>
       <c r="B33" t="str">
-        <v>spark only</v>
+        <v>both</v>
       </c>
       <c r="C33">
-        <v>0</v>
+        <v>-39.86</v>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>-44.41</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>-55.54</v>
       </c>
       <c r="F33">
-        <v>0</v>
+        <v>-139.81</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -8024,7 +8958,7 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>303</v>
+        <v>204</v>
       </c>
       <c r="B34" t="str">
         <v>both</v>
@@ -8033,13 +8967,13 @@
         <v>0</v>
       </c>
       <c r="D34">
-        <v>0</v>
+        <v>-2.39</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>-24.69</v>
       </c>
       <c r="F34">
-        <v>0</v>
+        <v>-27.08</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -8047,7 +8981,7 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>555</v>
+        <v>205</v>
       </c>
       <c r="B35" t="str">
         <v>both</v>
@@ -8056,13 +8990,13 @@
         <v>0</v>
       </c>
       <c r="D35">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="F35">
-        <v>0</v>
+        <v>-0.28</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -8070,22 +9004,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>1001</v>
+        <v>206</v>
       </c>
       <c r="B36" t="str">
-        <v>both</v>
+        <v>spark only</v>
       </c>
       <c r="C36">
-        <v>-83.28</v>
+        <v>0</v>
       </c>
       <c r="D36">
-        <v>1561.38</v>
+        <v>0</v>
       </c>
       <c r="E36">
-        <v>1611.23</v>
+        <v>0</v>
       </c>
       <c r="F36">
-        <v>3089.33</v>
+        <v>0</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -8093,22 +9027,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>1002</v>
+        <v>214</v>
       </c>
       <c r="B37" t="str">
-        <v>both</v>
+        <v>spark only</v>
       </c>
       <c r="C37">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
       <c r="D37">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="E37">
-        <v>11.65</v>
+        <v>0</v>
       </c>
       <c r="F37">
-        <v>12.16</v>
+        <v>0</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -8116,22 +9050,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>1003</v>
+        <v>216</v>
       </c>
       <c r="B38" t="str">
-        <v>amatsu only</v>
+        <v>both</v>
       </c>
       <c r="C38">
-        <v>-67207.7</v>
+        <v>0</v>
       </c>
       <c r="D38">
-        <v>-52633.8</v>
+        <v>0</v>
       </c>
       <c r="E38">
-        <v>-58463.7</v>
+        <v>-129.73</v>
       </c>
       <c r="F38">
-        <v>-178305.2</v>
+        <v>-129.73</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -8139,22 +9073,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>1004</v>
+        <v>219</v>
       </c>
       <c r="B39" t="str">
         <v>both</v>
       </c>
       <c r="C39">
-        <v>-228.59</v>
+        <v>0</v>
       </c>
       <c r="D39">
-        <v>-266.4</v>
+        <v>0</v>
       </c>
       <c r="E39">
-        <v>-529.59</v>
+        <v>0</v>
       </c>
       <c r="F39">
-        <v>-1024.58</v>
+        <v>0</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -8162,22 +9096,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>1007</v>
+        <v>223</v>
       </c>
       <c r="B40" t="str">
-        <v>both</v>
+        <v>spark only</v>
       </c>
       <c r="C40">
-        <v>-0.29</v>
+        <v>0</v>
       </c>
       <c r="D40">
-        <v>-1.54</v>
+        <v>0</v>
       </c>
       <c r="E40">
-        <v>7.33</v>
+        <v>0</v>
       </c>
       <c r="F40">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -8185,10 +9119,10 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>1015</v>
+        <v>224</v>
       </c>
       <c r="B41" t="str">
-        <v>both</v>
+        <v>spark only</v>
       </c>
       <c r="C41">
         <v>0</v>
@@ -8208,22 +9142,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>1016</v>
+        <v>303</v>
       </c>
       <c r="B42" t="str">
         <v>both</v>
       </c>
       <c r="C42">
-        <v>-3596.75</v>
+        <v>0</v>
       </c>
       <c r="D42">
-        <v>-3197.86</v>
+        <v>0</v>
       </c>
       <c r="E42">
-        <v>-4503.92</v>
+        <v>0</v>
       </c>
       <c r="F42">
-        <v>-11298.53</v>
+        <v>0</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -8231,22 +9165,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>1017</v>
+        <v>555</v>
       </c>
       <c r="B43" t="str">
         <v>both</v>
       </c>
       <c r="C43">
-        <v>-320.85</v>
+        <v>0</v>
       </c>
       <c r="D43">
-        <v>-209.86</v>
+        <v>0</v>
       </c>
       <c r="E43">
-        <v>-221.4</v>
+        <v>0</v>
       </c>
       <c r="F43">
-        <v>-752.11</v>
+        <v>0</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -8254,22 +9188,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>2000</v>
+        <v>1001</v>
       </c>
       <c r="B44" t="str">
         <v>both</v>
       </c>
       <c r="C44">
-        <v>0</v>
+        <v>-83.28</v>
       </c>
       <c r="D44">
-        <v>0</v>
+        <v>1561.38</v>
       </c>
       <c r="E44">
-        <v>0</v>
+        <v>1611.23</v>
       </c>
       <c r="F44">
-        <v>0</v>
+        <v>3089.33</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -8277,22 +9211,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>2001</v>
+        <v>1002</v>
       </c>
       <c r="B45" t="str">
         <v>both</v>
       </c>
       <c r="C45">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
       <c r="D45">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="E45">
-        <v>0</v>
+        <v>11.65</v>
       </c>
       <c r="F45">
-        <v>0</v>
+        <v>12.16</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -8300,22 +9234,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>2002</v>
+        <v>1003</v>
       </c>
       <c r="B46" t="str">
-        <v>both</v>
+        <v>amatsu only</v>
       </c>
       <c r="C46">
-        <v>0</v>
+        <v>-67207.7</v>
       </c>
       <c r="D46">
-        <v>0</v>
+        <v>-52633.8</v>
       </c>
       <c r="E46">
-        <v>61.28</v>
+        <v>-58463.7</v>
       </c>
       <c r="F46">
-        <v>61.28</v>
+        <v>-178305.2</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -8323,22 +9257,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>2003</v>
+        <v>1004</v>
       </c>
       <c r="B47" t="str">
         <v>both</v>
       </c>
       <c r="C47">
-        <v>0</v>
+        <v>-228.59</v>
       </c>
       <c r="D47">
-        <v>0</v>
+        <v>-266.4</v>
       </c>
       <c r="E47">
-        <v>0</v>
+        <v>-529.59</v>
       </c>
       <c r="F47">
-        <v>0</v>
+        <v>-1024.58</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -8346,22 +9280,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>2005</v>
+        <v>1007</v>
       </c>
       <c r="B48" t="str">
         <v>both</v>
       </c>
       <c r="C48">
-        <v>0</v>
+        <v>-0.29</v>
       </c>
       <c r="D48">
-        <v>0</v>
+        <v>-1.54</v>
       </c>
       <c r="E48">
-        <v>15.07</v>
+        <v>7.33</v>
       </c>
       <c r="F48">
-        <v>15.07</v>
+        <v>5.5</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -8369,10 +9303,10 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>2008</v>
+        <v>1015</v>
       </c>
       <c r="B49" t="str">
-        <v>spark only</v>
+        <v>both</v>
       </c>
       <c r="C49">
         <v>0</v>
@@ -8392,22 +9326,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>2222</v>
+        <v>1016</v>
       </c>
       <c r="B50" t="str">
         <v>both</v>
       </c>
       <c r="C50">
-        <v>0</v>
+        <v>-3596.75</v>
       </c>
       <c r="D50">
-        <v>0</v>
+        <v>-3197.86</v>
       </c>
       <c r="E50">
-        <v>0</v>
+        <v>-4503.92</v>
       </c>
       <c r="F50">
-        <v>0</v>
+        <v>-11298.53</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -8415,22 +9349,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>3000</v>
+        <v>1017</v>
       </c>
       <c r="B51" t="str">
-        <v>spark only</v>
+        <v>both</v>
       </c>
       <c r="C51">
-        <v>0</v>
+        <v>-320.85</v>
       </c>
       <c r="D51">
-        <v>0</v>
+        <v>-209.86</v>
       </c>
       <c r="E51">
-        <v>0</v>
+        <v>-221.4</v>
       </c>
       <c r="F51">
-        <v>0</v>
+        <v>-752.11</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -8438,10 +9372,10 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>3001</v>
+        <v>2000</v>
       </c>
       <c r="B52" t="str">
-        <v>spark only</v>
+        <v>both</v>
       </c>
       <c r="C52">
         <v>0</v>
@@ -8461,22 +9395,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>3333</v>
+        <v>2001</v>
       </c>
       <c r="B53" t="str">
-        <v>spark only</v>
+        <v>both</v>
       </c>
       <c r="C53">
-        <v>0.71</v>
+        <v>0</v>
       </c>
       <c r="D53">
-        <v>0.41</v>
+        <v>0</v>
       </c>
       <c r="E53">
-        <v>0.48</v>
+        <v>0</v>
       </c>
       <c r="F53">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -8484,10 +9418,10 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>4011</v>
+        <v>2002</v>
       </c>
       <c r="B54" t="str">
-        <v>spark only</v>
+        <v>both</v>
       </c>
       <c r="C54">
         <v>0</v>
@@ -8496,10 +9430,10 @@
         <v>0</v>
       </c>
       <c r="E54">
-        <v>0</v>
+        <v>61.28</v>
       </c>
       <c r="F54">
-        <v>0</v>
+        <v>61.28</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -8507,10 +9441,10 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>4012</v>
+        <v>2003</v>
       </c>
       <c r="B55" t="str">
-        <v>spark only</v>
+        <v>both</v>
       </c>
       <c r="C55">
         <v>0</v>
@@ -8530,10 +9464,10 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>9998</v>
+        <v>2005</v>
       </c>
       <c r="B56" t="str">
-        <v>spark only</v>
+        <v>both</v>
       </c>
       <c r="C56">
         <v>0</v>
@@ -8542,10 +9476,10 @@
         <v>0</v>
       </c>
       <c r="E56">
-        <v>0</v>
+        <v>15.07</v>
       </c>
       <c r="F56">
-        <v>0</v>
+        <v>15.07</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -8553,68 +9487,68 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>13425</v>
+        <v>2008</v>
       </c>
       <c r="B57" t="str">
         <v>spark only</v>
       </c>
       <c r="C57">
-        <v>858.01</v>
+        <v>0</v>
       </c>
       <c r="D57">
-        <v>774.97</v>
+        <v>0</v>
       </c>
       <c r="E57">
-        <v>858.01</v>
+        <v>0</v>
       </c>
       <c r="F57">
-        <v>2490.99</v>
+        <v>0</v>
       </c>
       <c r="G57" t="str">
         <v/>
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="str">
-        <v/>
+      <c r="A58">
+        <v>2222</v>
       </c>
       <c r="B58" t="str">
-        <v/>
-      </c>
-      <c r="C58" t="str">
-        <v/>
-      </c>
-      <c r="D58" t="str">
-        <v/>
-      </c>
-      <c r="E58" t="str">
-        <v/>
-      </c>
-      <c r="F58" t="str">
-        <v/>
+        <v>both</v>
+      </c>
+      <c r="C58">
+        <v>0</v>
+      </c>
+      <c r="D58">
+        <v>0</v>
+      </c>
+      <c r="E58">
+        <v>0</v>
+      </c>
+      <c r="F58">
+        <v>0</v>
       </c>
       <c r="G58" t="str">
         <v/>
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="str">
-        <v>── untagged ──</v>
+      <c r="A59">
+        <v>3000</v>
       </c>
       <c r="B59" t="str">
-        <v/>
-      </c>
-      <c r="C59" t="str">
-        <v/>
-      </c>
-      <c r="D59" t="str">
-        <v/>
-      </c>
-      <c r="E59" t="str">
-        <v/>
-      </c>
-      <c r="F59" t="str">
-        <v/>
+        <v>spark only</v>
+      </c>
+      <c r="C59">
+        <v>0</v>
+      </c>
+      <c r="D59">
+        <v>0</v>
+      </c>
+      <c r="E59">
+        <v>0</v>
+      </c>
+      <c r="F59">
+        <v>0</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -8622,7 +9556,7 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>123623963915635</v>
+        <v>3001</v>
       </c>
       <c r="B60" t="str">
         <v>spark only</v>
@@ -8634,10 +9568,10 @@
         <v>0</v>
       </c>
       <c r="E60">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="F60">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -8645,53 +9579,237 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>90000000000000000000</v>
+        <v>3333</v>
       </c>
       <c r="B61" t="str">
         <v>spark only</v>
       </c>
       <c r="C61">
+        <v>0.71</v>
+      </c>
+      <c r="D61">
+        <v>0.41</v>
+      </c>
+      <c r="E61">
+        <v>0.48</v>
+      </c>
+      <c r="F61">
+        <v>1.6</v>
+      </c>
+      <c r="G61" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>4011</v>
+      </c>
+      <c r="B62" t="str">
+        <v>spark only</v>
+      </c>
+      <c r="C62">
+        <v>0</v>
+      </c>
+      <c r="D62">
+        <v>0</v>
+      </c>
+      <c r="E62">
+        <v>0</v>
+      </c>
+      <c r="F62">
+        <v>0</v>
+      </c>
+      <c r="G62" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>4012</v>
+      </c>
+      <c r="B63" t="str">
+        <v>spark only</v>
+      </c>
+      <c r="C63">
+        <v>0</v>
+      </c>
+      <c r="D63">
+        <v>0</v>
+      </c>
+      <c r="E63">
+        <v>0</v>
+      </c>
+      <c r="F63">
+        <v>0</v>
+      </c>
+      <c r="G63" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>9998</v>
+      </c>
+      <c r="B64" t="str">
+        <v>spark only</v>
+      </c>
+      <c r="C64">
+        <v>0</v>
+      </c>
+      <c r="D64">
+        <v>0</v>
+      </c>
+      <c r="E64">
+        <v>0</v>
+      </c>
+      <c r="F64">
+        <v>0</v>
+      </c>
+      <c r="G64" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>13425</v>
+      </c>
+      <c r="B65" t="str">
+        <v>spark only</v>
+      </c>
+      <c r="C65">
+        <v>858.01</v>
+      </c>
+      <c r="D65">
+        <v>774.97</v>
+      </c>
+      <c r="E65">
+        <v>858.01</v>
+      </c>
+      <c r="F65">
+        <v>2490.99</v>
+      </c>
+      <c r="G65" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v/>
+      </c>
+      <c r="B66" t="str">
+        <v/>
+      </c>
+      <c r="C66" t="str">
+        <v/>
+      </c>
+      <c r="D66" t="str">
+        <v/>
+      </c>
+      <c r="E66" t="str">
+        <v/>
+      </c>
+      <c r="F66" t="str">
+        <v/>
+      </c>
+      <c r="G66" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>── untagged ──</v>
+      </c>
+      <c r="B67" t="str">
+        <v/>
+      </c>
+      <c r="C67" t="str">
+        <v/>
+      </c>
+      <c r="D67" t="str">
+        <v/>
+      </c>
+      <c r="E67" t="str">
+        <v/>
+      </c>
+      <c r="F67" t="str">
+        <v/>
+      </c>
+      <c r="G67" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>123623963915635</v>
+      </c>
+      <c r="B68" t="str">
+        <v>spark only</v>
+      </c>
+      <c r="C68">
+        <v>0</v>
+      </c>
+      <c r="D68">
+        <v>0</v>
+      </c>
+      <c r="E68">
+        <v>0.01</v>
+      </c>
+      <c r="F68">
+        <v>0.01</v>
+      </c>
+      <c r="G68" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>90000000000000000000</v>
+      </c>
+      <c r="B69" t="str">
+        <v>spark only</v>
+      </c>
+      <c r="C69">
         <v>0.06</v>
       </c>
-      <c r="D61">
+      <c r="D69">
         <v>0.01</v>
       </c>
-      <c r="E61">
-        <v>0</v>
-      </c>
-      <c r="F61">
+      <c r="E69">
+        <v>0</v>
+      </c>
+      <c r="F69">
         <v>0.07</v>
       </c>
-      <c r="G61" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="str">
+      <c r="G69" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
         <v>untagged</v>
       </c>
-      <c r="B62" t="str">
-        <v>both</v>
-      </c>
-      <c r="C62">
+      <c r="B70" t="str">
+        <v>both</v>
+      </c>
+      <c r="C70">
         <v>-140741.72</v>
       </c>
-      <c r="D62">
+      <c r="D70">
         <v>-224458.55</v>
       </c>
-      <c r="E62">
+      <c r="E70">
         <v>-232171.91</v>
       </c>
-      <c r="F62">
+      <c r="F70">
         <v>-597372.18</v>
       </c>
-      <c r="G62" t="str">
+      <c r="G70" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G62"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G70"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/dune-results/dr_comparison_2026.xlsx
+++ b/dune-results/dr_comparison_2026.xlsx
@@ -3,11 +3,11 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Our Data" sheetId="1" r:id="rId1"/>
+    <sheet name="Soter Data" sheetId="1" r:id="rId1"/>
     <sheet name="Spark" sheetId="2" r:id="rId2"/>
     <sheet name="Amatsu" sheetId="3" r:id="rId3"/>
-    <sheet name="Diff Ours-Spark" sheetId="4" r:id="rId4"/>
-    <sheet name="Diff Ours-Amatsu" sheetId="5" r:id="rId5"/>
+    <sheet name="Diff Soter-Spark" sheetId="4" r:id="rId4"/>
+    <sheet name="Diff Soter-Amatsu" sheetId="5" r:id="rId5"/>
     <sheet name="Diff Spark-Amatsu" sheetId="6" r:id="rId6"/>
   </sheets>
 </workbook>
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G70"/>
+  <dimension ref="A1:H76"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="13.83203125" customWidth="1"/>
@@ -411,6 +411,7 @@
     <col min="5" max="5" width="13.83203125" customWidth="1"/>
     <col min="6" max="6" width="13.83203125" customWidth="1"/>
     <col min="7" max="7" width="13.83203125" customWidth="1"/>
+    <col min="8" max="8" width="55.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -435,6 +436,9 @@
       <c r="G1" t="str">
         <v>total</v>
       </c>
+      <c r="H1" t="str">
+        <v>notes</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -458,6 +462,9 @@
       <c r="G2">
         <v>0</v>
       </c>
+      <c r="H2" t="str">
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -481,6 +488,9 @@
       <c r="G3">
         <v>0</v>
       </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -504,6 +514,9 @@
       <c r="G4">
         <v>62.45</v>
       </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -527,6 +540,9 @@
       <c r="G5">
         <v>367746.75</v>
       </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -550,6 +566,9 @@
       <c r="G6">
         <v>1786.39</v>
       </c>
+      <c r="H6" t="str">
+        <v>Chronicle farm — not tracked by Spark/BA.</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
@@ -573,6 +592,9 @@
       <c r="G7">
         <v>183.39</v>
       </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
@@ -596,6 +618,9 @@
       <c r="G8">
         <v>476.01</v>
       </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
@@ -619,6 +644,9 @@
       <c r="G9">
         <v>14506.79</v>
       </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
@@ -642,6 +670,9 @@
       <c r="G10">
         <v>443531.96</v>
       </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
@@ -665,6 +696,9 @@
       <c r="G11">
         <v>29341.39</v>
       </c>
+      <c r="H11" t="str">
+        <v>Chronicle farm — not tracked by Spark/BA.</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
@@ -688,6 +722,9 @@
       <c r="G12">
         <v>38223.42</v>
       </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
@@ -711,6 +748,9 @@
       <c r="G13">
         <v>66951.14</v>
       </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14">
@@ -734,6 +774,9 @@
       <c r="G14">
         <v>0</v>
       </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15">
@@ -757,6 +800,9 @@
       <c r="G15">
         <v>0</v>
       </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16">
@@ -780,539 +826,611 @@
       <c r="G16">
         <v>0</v>
       </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>127</v>
-      </c>
-      <c r="B17">
-        <v>3037.15</v>
-      </c>
-      <c r="C17">
-        <v>2639.18</v>
-      </c>
-      <c r="D17">
-        <v>2167.44</v>
-      </c>
-      <c r="E17">
-        <v>1447.5</v>
-      </c>
-      <c r="F17">
-        <v>730.93</v>
+        <v>126</v>
+      </c>
+      <c r="B17" t="str">
+        <v/>
+      </c>
+      <c r="C17" t="str">
+        <v/>
+      </c>
+      <c r="D17" t="str">
+        <v/>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
+        <v/>
       </c>
       <c r="G17">
-        <v>10022.2</v>
+        <v>0</v>
+      </c>
+      <c r="H17" t="str">
+        <v>Subproxy holdings, no DR applied. Handled in Supply Side MSC.</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B18">
-        <v>826847.7</v>
+        <v>3037.15</v>
       </c>
       <c r="C18">
-        <v>837591.56</v>
+        <v>2639.18</v>
       </c>
       <c r="D18">
-        <v>1199709.46</v>
+        <v>2167.44</v>
       </c>
       <c r="E18">
-        <v>1321957.96</v>
+        <v>1447.5</v>
       </c>
       <c r="F18">
-        <v>1461137.84</v>
+        <v>730.93</v>
       </c>
       <c r="G18">
-        <v>5647244.52</v>
+        <v>10022.2</v>
+      </c>
+      <c r="H18" t="str">
+        <v>Spark untagged Savings, had boosted DR applied by Amatsu.</v>
       </c>
     </row>
     <row r="19">
       <c r="A19">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B19">
-        <v>1.03</v>
+        <v>826847.7</v>
       </c>
       <c r="C19">
-        <v>0.52</v>
+        <v>837591.56</v>
       </c>
       <c r="D19">
-        <v>0.67</v>
+        <v>1199709.46</v>
       </c>
       <c r="E19">
-        <v>0.77</v>
+        <v>1321957.96</v>
       </c>
       <c r="F19">
-        <v>1.13</v>
+        <v>1461137.84</v>
       </c>
       <c r="G19">
-        <v>4.12</v>
+        <v>5647244.52</v>
+      </c>
+      <c r="H19" t="str">
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>170</v>
+        <v>129</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>0.52</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>0.77</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="G20">
-        <v>0</v>
+        <v>4.12</v>
+      </c>
+      <c r="H20" t="str">
+        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <v>171</v>
-      </c>
-      <c r="B21">
-        <v>0</v>
-      </c>
-      <c r="C21">
-        <v>0</v>
-      </c>
-      <c r="D21">
-        <v>0</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-      <c r="F21">
-        <v>0</v>
+        <v>130</v>
+      </c>
+      <c r="B21" t="str">
+        <v/>
+      </c>
+      <c r="C21" t="str">
+        <v/>
+      </c>
+      <c r="D21" t="str">
+        <v/>
+      </c>
+      <c r="E21" t="str">
+        <v/>
+      </c>
+      <c r="F21" t="str">
+        <v/>
       </c>
       <c r="G21">
         <v>0</v>
+      </c>
+      <c r="H21" t="str">
+        <v>Found in Spark datasets only, no onchain events.</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>182</v>
+        <v>170</v>
       </c>
       <c r="B22">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="C22">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="D22">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="E22">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="F22">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="G22">
-        <v>0.05</v>
+        <v>0</v>
+      </c>
+      <c r="H22" t="str">
+        <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="B23">
-        <v>21333.38</v>
+        <v>0</v>
       </c>
       <c r="C23">
-        <v>13278.93</v>
+        <v>0</v>
       </c>
       <c r="D23">
-        <v>11113.76</v>
+        <v>0</v>
       </c>
       <c r="E23">
-        <v>9912.97</v>
+        <v>0</v>
       </c>
       <c r="F23">
-        <v>11847.6</v>
+        <v>0</v>
       </c>
       <c r="G23">
-        <v>67486.64</v>
+        <v>0</v>
+      </c>
+      <c r="H23" t="str">
+        <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="B24">
-        <v>467.21</v>
+        <v>0.01</v>
       </c>
       <c r="C24">
-        <v>638.59</v>
+        <v>0.01</v>
       </c>
       <c r="D24">
-        <v>1188.8</v>
+        <v>0.01</v>
       </c>
       <c r="E24">
-        <v>1386.57</v>
+        <v>0.01</v>
       </c>
       <c r="F24">
-        <v>1241.16</v>
+        <v>0.01</v>
       </c>
       <c r="G24">
-        <v>4922.33</v>
+        <v>0.05</v>
+      </c>
+      <c r="H24" t="str">
+        <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="B25">
-        <v>475.33</v>
+        <v>21333.38</v>
       </c>
       <c r="C25">
-        <v>108.27</v>
+        <v>13278.93</v>
       </c>
       <c r="D25">
-        <v>7201.39</v>
+        <v>11113.76</v>
       </c>
       <c r="E25">
-        <v>14582.19</v>
+        <v>9912.97</v>
       </c>
       <c r="F25">
-        <v>11608.11</v>
+        <v>11847.6</v>
       </c>
       <c r="G25">
-        <v>33975.29</v>
+        <v>67486.64</v>
+      </c>
+      <c r="H25" t="str">
+        <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="B26">
-        <v>10427.71</v>
+        <v>467.21</v>
       </c>
       <c r="C26">
-        <v>5314.13</v>
+        <v>638.59</v>
       </c>
       <c r="D26">
-        <v>4209.1</v>
+        <v>1188.8</v>
       </c>
       <c r="E26">
-        <v>2912.07</v>
+        <v>1386.57</v>
       </c>
       <c r="F26">
-        <v>2740.89</v>
+        <v>1241.16</v>
       </c>
       <c r="G26">
-        <v>25603.9</v>
+        <v>4922.33</v>
+      </c>
+      <c r="H26" t="str">
+        <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B27">
-        <v>3326.25</v>
+        <v>475.33</v>
       </c>
       <c r="C27">
-        <v>5352.96</v>
+        <v>108.27</v>
       </c>
       <c r="D27">
-        <v>8218.73</v>
+        <v>7201.39</v>
       </c>
       <c r="E27">
-        <v>12123.38</v>
+        <v>14582.19</v>
       </c>
       <c r="F27">
-        <v>23241.91</v>
+        <v>11608.11</v>
       </c>
       <c r="G27">
-        <v>52263.23</v>
+        <v>33975.29</v>
+      </c>
+      <c r="H27" t="str">
+        <v>Had boosted DR applied by Amatsu.</v>
       </c>
     </row>
     <row r="28">
       <c r="A28">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B28">
-        <v>22700.54</v>
+        <v>10427.71</v>
       </c>
       <c r="C28">
-        <v>16725.41</v>
+        <v>5314.13</v>
       </c>
       <c r="D28">
-        <v>19342.47</v>
+        <v>4209.1</v>
       </c>
       <c r="E28">
-        <v>15097.77</v>
+        <v>2912.07</v>
       </c>
       <c r="F28">
-        <v>10576.24</v>
+        <v>2740.89</v>
       </c>
       <c r="G28">
-        <v>84442.43</v>
+        <v>25603.9</v>
+      </c>
+      <c r="H28" t="str">
+        <v>Had boosted DR applied by Amatsu.</v>
       </c>
     </row>
     <row r="29">
       <c r="A29">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="B29">
-        <v>1.99</v>
+        <v>3326.25</v>
       </c>
       <c r="C29">
-        <v>1.7</v>
+        <v>5352.96</v>
       </c>
       <c r="D29">
-        <v>1.88</v>
+        <v>8218.73</v>
       </c>
       <c r="E29">
-        <v>1.72</v>
+        <v>12123.38</v>
       </c>
       <c r="F29">
-        <v>1.75</v>
+        <v>23241.91</v>
       </c>
       <c r="G29">
-        <v>9.04</v>
+        <v>52263.23</v>
+      </c>
+      <c r="H29" t="str">
+        <v>Had boosted DR applied by Amatsu.</v>
       </c>
     </row>
     <row r="30">
       <c r="A30">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B30">
-        <v>1554.29</v>
+        <v>22700.54</v>
       </c>
       <c r="C30">
-        <v>669.49</v>
+        <v>16725.41</v>
       </c>
       <c r="D30">
-        <v>3049.96</v>
+        <v>19342.47</v>
       </c>
       <c r="E30">
-        <v>1990.3</v>
+        <v>15097.77</v>
       </c>
       <c r="F30">
-        <v>1235.01</v>
+        <v>10576.24</v>
       </c>
       <c r="G30">
-        <v>8499.05</v>
+        <v>84442.43</v>
+      </c>
+      <c r="H30" t="str">
+        <v>Had boosted DR applied by Amatsu.</v>
       </c>
     </row>
     <row r="31">
       <c r="A31">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B31">
-        <v>0.01</v>
+        <v>1.99</v>
       </c>
       <c r="C31">
-        <v>0.09</v>
+        <v>1.7</v>
       </c>
       <c r="D31">
-        <v>0.1</v>
+        <v>1.88</v>
       </c>
       <c r="E31">
-        <v>0.1</v>
+        <v>1.72</v>
       </c>
       <c r="F31">
-        <v>0.1</v>
+        <v>1.75</v>
       </c>
       <c r="G31">
-        <v>0.4</v>
+        <v>9.04</v>
+      </c>
+      <c r="H31" t="str">
+        <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B32">
-        <v>6824.99</v>
+        <v>1554.29</v>
       </c>
       <c r="C32">
-        <v>6314.15</v>
+        <v>669.49</v>
       </c>
       <c r="D32">
-        <v>5576.07</v>
+        <v>3049.96</v>
       </c>
       <c r="E32">
-        <v>8508.93</v>
+        <v>1990.3</v>
       </c>
       <c r="F32">
-        <v>10729.88</v>
+        <v>1235.01</v>
       </c>
       <c r="G32">
-        <v>37954.02</v>
+        <v>8499.05</v>
+      </c>
+      <c r="H32" t="str">
+        <v>Had boosted DR applied by Amatsu.</v>
       </c>
     </row>
     <row r="33">
       <c r="A33">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B33">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="C33">
-        <v>0.02</v>
+        <v>0.09</v>
       </c>
       <c r="D33">
-        <v>0.02</v>
+        <v>0.1</v>
       </c>
       <c r="E33">
-        <v>0.02</v>
+        <v>0.1</v>
       </c>
       <c r="F33">
-        <v>0.02</v>
+        <v>0.1</v>
       </c>
       <c r="G33">
-        <v>0.1</v>
+        <v>0.4</v>
+      </c>
+      <c r="H33" t="str">
+        <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B34">
-        <v>1.96</v>
+        <v>6824.99</v>
       </c>
       <c r="C34">
-        <v>0.65</v>
+        <v>6314.15</v>
       </c>
       <c r="D34">
-        <v>5.79</v>
+        <v>5576.07</v>
       </c>
       <c r="E34">
-        <v>32.59</v>
+        <v>8508.93</v>
       </c>
       <c r="F34">
-        <v>91.6</v>
+        <v>10729.88</v>
       </c>
       <c r="G34">
-        <v>132.59</v>
+        <v>37954.02</v>
+      </c>
+      <c r="H34" t="str">
+        <v>stUSDS. Amatsu/BA applied DR in Jan./Feb. then switched to 0.1% after. s/b 0.1% always applied.</v>
       </c>
     </row>
     <row r="35">
       <c r="A35">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="B35">
-        <v>28.54</v>
+        <v>0.02</v>
       </c>
       <c r="C35">
-        <v>32.89</v>
+        <v>0.02</v>
       </c>
       <c r="D35">
-        <v>42.56</v>
+        <v>0.02</v>
       </c>
       <c r="E35">
-        <v>39.75</v>
+        <v>0.02</v>
       </c>
       <c r="F35">
-        <v>33.27</v>
+        <v>0.02</v>
       </c>
       <c r="G35">
-        <v>177.01</v>
+        <v>0.1</v>
+      </c>
+      <c r="H35" t="str">
+        <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36">
-        <v>204</v>
-      </c>
-      <c r="B36" t="str">
-        <v/>
+        <v>200</v>
+      </c>
+      <c r="B36">
+        <v>1.96</v>
       </c>
       <c r="C36">
-        <v>1.61</v>
+        <v>0.65</v>
       </c>
       <c r="D36">
-        <v>16.91</v>
+        <v>5.79</v>
       </c>
       <c r="E36">
-        <v>34.05</v>
+        <v>32.59</v>
       </c>
       <c r="F36">
-        <v>30.45</v>
+        <v>91.6</v>
       </c>
       <c r="G36">
-        <v>83.02</v>
+        <v>132.59</v>
+      </c>
+      <c r="H36" t="str">
+        <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B37">
-        <v>0</v>
+        <v>28.54</v>
       </c>
       <c r="C37">
-        <v>0.02</v>
+        <v>32.89</v>
       </c>
       <c r="D37">
-        <v>0.2</v>
+        <v>42.56</v>
       </c>
       <c r="E37">
-        <v>0.21</v>
+        <v>39.75</v>
       </c>
       <c r="F37">
-        <v>0.21</v>
+        <v>33.27</v>
       </c>
       <c r="G37">
-        <v>0.64</v>
+        <v>177.01</v>
+      </c>
+      <c r="H37" t="str">
+        <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B38" t="str">
         <v/>
       </c>
-      <c r="C38" t="str">
-        <v/>
-      </c>
-      <c r="D38" t="str">
-        <v/>
-      </c>
-      <c r="E38" t="str">
-        <v/>
+      <c r="C38">
+        <v>1.61</v>
+      </c>
+      <c r="D38">
+        <v>16.91</v>
+      </c>
+      <c r="E38">
+        <v>34.05</v>
       </c>
       <c r="F38">
-        <v>0</v>
+        <v>30.45</v>
       </c>
       <c r="G38">
-        <v>0</v>
+        <v>83.02</v>
+      </c>
+      <c r="H38" t="str">
+        <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39">
-        <v>214</v>
-      </c>
-      <c r="B39" t="str">
-        <v/>
-      </c>
-      <c r="C39" t="str">
-        <v/>
-      </c>
-      <c r="D39" t="str">
-        <v/>
-      </c>
-      <c r="E39" t="str">
-        <v/>
+        <v>205</v>
+      </c>
+      <c r="B39">
+        <v>0</v>
+      </c>
+      <c r="C39">
+        <v>0.02</v>
+      </c>
+      <c r="D39">
+        <v>0.2</v>
+      </c>
+      <c r="E39">
+        <v>0.21</v>
       </c>
       <c r="F39">
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="G39">
-        <v>0</v>
+        <v>0.64</v>
+      </c>
+      <c r="H39" t="str">
+        <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="B40" t="str">
         <v/>
@@ -1320,22 +1438,25 @@
       <c r="C40" t="str">
         <v/>
       </c>
-      <c r="D40">
-        <v>86.77</v>
-      </c>
-      <c r="E40">
-        <v>151.21</v>
+      <c r="D40" t="str">
+        <v/>
+      </c>
+      <c r="E40" t="str">
+        <v/>
       </c>
       <c r="F40">
-        <v>189.04</v>
+        <v>0</v>
       </c>
       <c r="G40">
-        <v>427.02</v>
+        <v>0</v>
+      </c>
+      <c r="H40" t="str">
+        <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="B41" t="str">
         <v/>
@@ -1346,19 +1467,22 @@
       <c r="D41" t="str">
         <v/>
       </c>
-      <c r="E41">
-        <v>14.26</v>
-      </c>
-      <c r="F41" t="str">
-        <v/>
+      <c r="E41" t="str">
+        <v/>
+      </c>
+      <c r="F41">
+        <v>0</v>
       </c>
       <c r="G41">
-        <v>14.26</v>
+        <v>0</v>
+      </c>
+      <c r="H41" t="str">
+        <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="B42" t="str">
         <v/>
@@ -1366,22 +1490,25 @@
       <c r="C42" t="str">
         <v/>
       </c>
-      <c r="D42" t="str">
-        <v/>
-      </c>
-      <c r="E42" t="str">
-        <v/>
+      <c r="D42">
+        <v>86.77</v>
+      </c>
+      <c r="E42">
+        <v>151.21</v>
       </c>
       <c r="F42">
-        <v>0</v>
+        <v>189.04</v>
       </c>
       <c r="G42">
-        <v>0</v>
+        <v>427.02</v>
+      </c>
+      <c r="H42" t="str">
+        <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="B43" t="str">
         <v/>
@@ -1392,235 +1519,265 @@
       <c r="D43" t="str">
         <v/>
       </c>
-      <c r="E43" t="str">
-        <v/>
-      </c>
-      <c r="F43">
-        <v>4582.17</v>
+      <c r="E43">
+        <v>14.26</v>
+      </c>
+      <c r="F43" t="str">
+        <v/>
       </c>
       <c r="G43">
-        <v>4582.17</v>
+        <v>14.26</v>
+      </c>
+      <c r="H43" t="str">
+        <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44">
-        <v>303</v>
-      </c>
-      <c r="B44">
-        <v>0</v>
-      </c>
-      <c r="C44">
-        <v>0</v>
-      </c>
-      <c r="D44">
-        <v>0</v>
-      </c>
-      <c r="E44">
-        <v>0</v>
+        <v>223</v>
+      </c>
+      <c r="B44" t="str">
+        <v/>
+      </c>
+      <c r="C44" t="str">
+        <v/>
+      </c>
+      <c r="D44" t="str">
+        <v/>
+      </c>
+      <c r="E44" t="str">
+        <v/>
       </c>
       <c r="F44">
         <v>0</v>
       </c>
       <c r="G44">
         <v>0</v>
+      </c>
+      <c r="H44" t="str">
+        <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45">
-        <v>555</v>
-      </c>
-      <c r="B45">
-        <v>0</v>
-      </c>
-      <c r="C45">
-        <v>0</v>
-      </c>
-      <c r="D45">
-        <v>0</v>
-      </c>
-      <c r="E45">
-        <v>0</v>
+        <v>224</v>
+      </c>
+      <c r="B45" t="str">
+        <v/>
+      </c>
+      <c r="C45" t="str">
+        <v/>
+      </c>
+      <c r="D45" t="str">
+        <v/>
+      </c>
+      <c r="E45" t="str">
+        <v/>
       </c>
       <c r="F45">
-        <v>0</v>
+        <v>4582.17</v>
       </c>
       <c r="G45">
-        <v>0</v>
+        <v>4582.17</v>
+      </c>
+      <c r="H45" t="str">
+        <v/>
       </c>
     </row>
     <row r="46">
       <c r="A46">
-        <v>1001</v>
+        <v>303</v>
       </c>
       <c r="B46">
-        <v>2254.8</v>
+        <v>0</v>
       </c>
       <c r="C46">
-        <v>1601.44</v>
+        <v>0</v>
       </c>
       <c r="D46">
-        <v>1655.49</v>
+        <v>0</v>
       </c>
       <c r="E46">
-        <v>1433.94</v>
+        <v>0</v>
       </c>
       <c r="F46">
-        <v>912.57</v>
+        <v>0</v>
       </c>
       <c r="G46">
-        <v>7858.24</v>
+        <v>0</v>
+      </c>
+      <c r="H46" t="str">
+        <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47">
-        <v>1002</v>
+        <v>555</v>
       </c>
       <c r="B47">
-        <v>1969.51</v>
+        <v>0</v>
       </c>
       <c r="C47">
-        <v>2970.51</v>
+        <v>0</v>
       </c>
       <c r="D47">
-        <v>29195.53</v>
+        <v>0</v>
       </c>
       <c r="E47">
-        <v>28955.22</v>
+        <v>0</v>
       </c>
       <c r="F47">
-        <v>33175.15</v>
+        <v>0</v>
       </c>
       <c r="G47">
-        <v>96265.92</v>
+        <v>0</v>
+      </c>
+      <c r="H47" t="str">
+        <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48">
-        <v>1004</v>
+        <v>1001</v>
       </c>
       <c r="B48">
-        <v>0.01</v>
+        <v>2254.8</v>
       </c>
       <c r="C48">
-        <v>0</v>
+        <v>1601.44</v>
       </c>
       <c r="D48">
-        <v>0.01</v>
+        <v>1655.49</v>
       </c>
       <c r="E48">
-        <v>0.01</v>
+        <v>1433.94</v>
       </c>
       <c r="F48">
-        <v>0.01</v>
+        <v>912.57</v>
       </c>
       <c r="G48">
-        <v>0.04</v>
+        <v>7858.24</v>
+      </c>
+      <c r="H48" t="str">
+        <v>Feb. and Mar. had no DR by Amatsu.</v>
       </c>
     </row>
     <row r="49">
       <c r="A49">
-        <v>1007</v>
+        <v>1002</v>
       </c>
       <c r="B49">
-        <v>10082.51</v>
+        <v>1969.51</v>
       </c>
       <c r="C49">
-        <v>13745.06</v>
+        <v>2970.51</v>
       </c>
       <c r="D49">
-        <v>15859.43</v>
+        <v>29195.53</v>
       </c>
       <c r="E49">
-        <v>14112.17</v>
+        <v>28955.22</v>
       </c>
       <c r="F49">
-        <v>10762.39</v>
+        <v>33175.15</v>
       </c>
       <c r="G49">
-        <v>64561.56</v>
+        <v>96265.92</v>
+      </c>
+      <c r="H49" t="str">
+        <v/>
       </c>
     </row>
     <row r="50">
       <c r="A50">
-        <v>1015</v>
-      </c>
-      <c r="B50">
-        <v>0</v>
-      </c>
-      <c r="C50">
-        <v>0</v>
-      </c>
-      <c r="D50">
-        <v>0</v>
-      </c>
-      <c r="E50">
-        <v>0</v>
-      </c>
-      <c r="F50">
-        <v>0</v>
+        <v>1003</v>
+      </c>
+      <c r="B50" t="str">
+        <v/>
+      </c>
+      <c r="C50" t="str">
+        <v/>
+      </c>
+      <c r="D50" t="str">
+        <v/>
+      </c>
+      <c r="E50" t="str">
+        <v/>
+      </c>
+      <c r="F50" t="str">
+        <v/>
       </c>
       <c r="G50">
         <v>0</v>
+      </c>
+      <c r="H50" t="str">
+        <v/>
       </c>
     </row>
     <row r="51">
       <c r="A51">
-        <v>1016</v>
+        <v>1004</v>
       </c>
       <c r="B51">
-        <v>1201.05</v>
+        <v>0.01</v>
       </c>
       <c r="C51">
-        <v>167.54</v>
+        <v>0</v>
       </c>
       <c r="D51">
-        <v>8.98</v>
+        <v>0.01</v>
       </c>
       <c r="E51">
-        <v>0.59</v>
-      </c>
-      <c r="F51" t="str">
-        <v/>
+        <v>0.01</v>
+      </c>
+      <c r="F51">
+        <v>0.01</v>
       </c>
       <c r="G51">
-        <v>1378.16</v>
+        <v>0.04</v>
+      </c>
+      <c r="H51" t="str">
+        <v/>
       </c>
     </row>
     <row r="52">
       <c r="A52">
-        <v>1017</v>
+        <v>1007</v>
       </c>
       <c r="B52">
-        <v>215.45</v>
+        <v>10082.51</v>
       </c>
       <c r="C52">
-        <v>140.34</v>
+        <v>13745.06</v>
       </c>
       <c r="D52">
-        <v>148.1</v>
+        <v>15859.43</v>
       </c>
       <c r="E52">
-        <v>85.99</v>
+        <v>14112.17</v>
       </c>
       <c r="F52">
-        <v>3.52</v>
+        <v>10762.39</v>
       </c>
       <c r="G52">
-        <v>593.4</v>
+        <v>64561.56</v>
+      </c>
+      <c r="H52" t="str">
+        <v/>
       </c>
     </row>
     <row r="53">
       <c r="A53">
-        <v>2000</v>
-      </c>
-      <c r="B53" t="str">
-        <v/>
-      </c>
-      <c r="C53" t="str">
-        <v/>
-      </c>
-      <c r="D53" t="str">
-        <v/>
+        <v>1015</v>
+      </c>
+      <c r="B53">
+        <v>0</v>
+      </c>
+      <c r="C53">
+        <v>0</v>
+      </c>
+      <c r="D53">
+        <v>0</v>
       </c>
       <c r="E53">
         <v>0</v>
@@ -1630,57 +1787,66 @@
       </c>
       <c r="G53">
         <v>0</v>
+      </c>
+      <c r="H53" t="str">
+        <v/>
       </c>
     </row>
     <row r="54">
       <c r="A54">
-        <v>2001</v>
-      </c>
-      <c r="B54" t="str">
-        <v/>
+        <v>1016</v>
+      </c>
+      <c r="B54">
+        <v>1201.05</v>
       </c>
       <c r="C54">
-        <v>0</v>
+        <v>167.54</v>
       </c>
       <c r="D54">
-        <v>0</v>
+        <v>8.98</v>
       </c>
       <c r="E54">
-        <v>82.24</v>
-      </c>
-      <c r="F54">
-        <v>8467.99</v>
+        <v>0.59</v>
+      </c>
+      <c r="F54" t="str">
+        <v/>
       </c>
       <c r="G54">
-        <v>8550.23</v>
+        <v>1378.16</v>
+      </c>
+      <c r="H54" t="str">
+        <v>Amatsu included DR for sUSDC, sUSDS, SKY, while onchain, only events for SKY can be found. unknown which balances or events to use for sUSDC and sUSDS.</v>
       </c>
     </row>
     <row r="55">
       <c r="A55">
-        <v>2002</v>
-      </c>
-      <c r="B55" t="str">
-        <v/>
-      </c>
-      <c r="C55" t="str">
-        <v/>
+        <v>1017</v>
+      </c>
+      <c r="B55">
+        <v>215.45</v>
+      </c>
+      <c r="C55">
+        <v>140.34</v>
       </c>
       <c r="D55">
-        <v>174574.28</v>
+        <v>148.1</v>
       </c>
       <c r="E55">
-        <v>116737.37</v>
+        <v>85.99</v>
       </c>
       <c r="F55">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="G55">
-        <v>291311.65</v>
+        <v>593.4</v>
+      </c>
+      <c r="H55" t="str">
+        <v/>
       </c>
     </row>
     <row r="56">
       <c r="A56">
-        <v>2003</v>
+        <v>2000</v>
       </c>
       <c r="B56" t="str">
         <v/>
@@ -1699,34 +1865,40 @@
       </c>
       <c r="G56">
         <v>0</v>
+      </c>
+      <c r="H56" t="str">
+        <v/>
       </c>
     </row>
     <row r="57">
       <c r="A57">
-        <v>2005</v>
+        <v>2001</v>
       </c>
       <c r="B57" t="str">
         <v/>
       </c>
-      <c r="C57" t="str">
-        <v/>
+      <c r="C57">
+        <v>0</v>
       </c>
       <c r="D57">
-        <v>17144.97</v>
+        <v>0</v>
       </c>
       <c r="E57">
-        <v>8259.88</v>
-      </c>
-      <c r="F57" t="str">
-        <v/>
+        <v>82.24</v>
+      </c>
+      <c r="F57">
+        <v>8467.99</v>
       </c>
       <c r="G57">
-        <v>25404.85</v>
+        <v>8550.23</v>
+      </c>
+      <c r="H57" t="str">
+        <v/>
       </c>
     </row>
     <row r="58">
       <c r="A58">
-        <v>2008</v>
+        <v>2002</v>
       </c>
       <c r="B58" t="str">
         <v/>
@@ -1734,22 +1906,25 @@
       <c r="C58" t="str">
         <v/>
       </c>
-      <c r="D58" t="str">
-        <v/>
-      </c>
-      <c r="E58" t="str">
-        <v/>
+      <c r="D58">
+        <v>174574.28</v>
+      </c>
+      <c r="E58">
+        <v>116737.37</v>
       </c>
       <c r="F58">
-        <v>12035.78</v>
+        <v>0</v>
       </c>
       <c r="G58">
-        <v>12035.78</v>
+        <v>291311.65</v>
+      </c>
+      <c r="H58" t="str">
+        <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59">
-        <v>2222</v>
+        <v>2003</v>
       </c>
       <c r="B59" t="str">
         <v/>
@@ -1761,18 +1936,21 @@
         <v/>
       </c>
       <c r="E59">
-        <v>10.68</v>
+        <v>0</v>
       </c>
       <c r="F59">
-        <v>14.75</v>
+        <v>0</v>
       </c>
       <c r="G59">
-        <v>25.43</v>
+        <v>0</v>
+      </c>
+      <c r="H59" t="str">
+        <v/>
       </c>
     </row>
     <row r="60">
       <c r="A60">
-        <v>3000</v>
+        <v>2005</v>
       </c>
       <c r="B60" t="str">
         <v/>
@@ -1780,22 +1958,25 @@
       <c r="C60" t="str">
         <v/>
       </c>
-      <c r="D60" t="str">
-        <v/>
+      <c r="D60">
+        <v>17144.97</v>
       </c>
       <c r="E60">
-        <v>0</v>
-      </c>
-      <c r="F60">
-        <v>0</v>
+        <v>8259.88</v>
+      </c>
+      <c r="F60" t="str">
+        <v/>
       </c>
       <c r="G60">
-        <v>0</v>
+        <v>25404.85</v>
+      </c>
+      <c r="H60" t="str">
+        <v/>
       </c>
     </row>
     <row r="61">
       <c r="A61">
-        <v>3001</v>
+        <v>2008</v>
       </c>
       <c r="B61" t="str">
         <v/>
@@ -1810,38 +1991,44 @@
         <v/>
       </c>
       <c r="F61">
-        <v>0</v>
+        <v>12035.78</v>
       </c>
       <c r="G61">
-        <v>0</v>
+        <v>12035.78</v>
+      </c>
+      <c r="H61" t="str">
+        <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62">
-        <v>3333</v>
-      </c>
-      <c r="B62">
-        <v>0.71</v>
-      </c>
-      <c r="C62">
-        <v>0.41</v>
-      </c>
-      <c r="D62">
-        <v>0.48</v>
+        <v>2222</v>
+      </c>
+      <c r="B62" t="str">
+        <v/>
+      </c>
+      <c r="C62" t="str">
+        <v/>
+      </c>
+      <c r="D62" t="str">
+        <v/>
       </c>
       <c r="E62">
-        <v>0.49</v>
+        <v>10.68</v>
       </c>
       <c r="F62">
-        <v>0.48</v>
+        <v>14.75</v>
       </c>
       <c r="G62">
-        <v>2.57</v>
+        <v>25.43</v>
+      </c>
+      <c r="H62" t="str">
+        <v/>
       </c>
     </row>
     <row r="63">
       <c r="A63">
-        <v>4011</v>
+        <v>3000</v>
       </c>
       <c r="B63" t="str">
         <v/>
@@ -1852,19 +2039,22 @@
       <c r="D63" t="str">
         <v/>
       </c>
-      <c r="E63" t="str">
-        <v/>
+      <c r="E63">
+        <v>0</v>
       </c>
       <c r="F63">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="G63">
-        <v>0.01</v>
+        <v>0</v>
+      </c>
+      <c r="H63" t="str">
+        <v/>
       </c>
     </row>
     <row r="64">
       <c r="A64">
-        <v>4012</v>
+        <v>3001</v>
       </c>
       <c r="B64" t="str">
         <v/>
@@ -1883,57 +2073,66 @@
       </c>
       <c r="G64">
         <v>0</v>
+      </c>
+      <c r="H64" t="str">
+        <v/>
       </c>
     </row>
     <row r="65">
       <c r="A65">
-        <v>9998</v>
+        <v>3333</v>
       </c>
       <c r="B65">
-        <v>0</v>
+        <v>0.71</v>
       </c>
       <c r="C65">
-        <v>0</v>
+        <v>0.41</v>
       </c>
       <c r="D65">
-        <v>0</v>
+        <v>0.48</v>
       </c>
       <c r="E65">
-        <v>0</v>
+        <v>0.49</v>
       </c>
       <c r="F65">
-        <v>0</v>
+        <v>0.48</v>
       </c>
       <c r="G65">
-        <v>0</v>
+        <v>2.57</v>
+      </c>
+      <c r="H65" t="str">
+        <v/>
       </c>
     </row>
     <row r="66">
       <c r="A66">
-        <v>13425</v>
-      </c>
-      <c r="B66">
-        <v>858.01</v>
-      </c>
-      <c r="C66">
-        <v>774.97</v>
-      </c>
-      <c r="D66">
-        <v>858.01</v>
-      </c>
-      <c r="E66">
-        <v>641.16</v>
+        <v>4011</v>
+      </c>
+      <c r="B66" t="str">
+        <v/>
+      </c>
+      <c r="C66" t="str">
+        <v/>
+      </c>
+      <c r="D66" t="str">
+        <v/>
+      </c>
+      <c r="E66" t="str">
+        <v/>
       </c>
       <c r="F66">
-        <v>9.67</v>
+        <v>0.01</v>
       </c>
       <c r="G66">
-        <v>3141.82</v>
+        <v>0.01</v>
+      </c>
+      <c r="H66" t="str">
+        <v/>
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="str">
-        <v/>
+      <c r="A67">
+        <v>4012</v>
       </c>
       <c r="B67" t="str">
         <v/>
@@ -1947,92 +2146,260 @@
       <c r="E67" t="str">
         <v/>
       </c>
-      <c r="F67" t="str">
-        <v/>
-      </c>
-      <c r="G67" t="str">
+      <c r="F67">
+        <v>0</v>
+      </c>
+      <c r="G67">
+        <v>0</v>
+      </c>
+      <c r="H67" t="str">
         <v/>
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="str">
-        <v>── untagged ──</v>
-      </c>
-      <c r="B68" t="str">
-        <v/>
-      </c>
-      <c r="C68" t="str">
-        <v/>
-      </c>
-      <c r="D68" t="str">
-        <v/>
-      </c>
-      <c r="E68" t="str">
-        <v/>
-      </c>
-      <c r="F68" t="str">
-        <v/>
-      </c>
-      <c r="G68" t="str">
+      <c r="A68">
+        <v>9998</v>
+      </c>
+      <c r="B68">
+        <v>0</v>
+      </c>
+      <c r="C68">
+        <v>0</v>
+      </c>
+      <c r="D68">
+        <v>0</v>
+      </c>
+      <c r="E68">
+        <v>0</v>
+      </c>
+      <c r="F68">
+        <v>0</v>
+      </c>
+      <c r="G68">
+        <v>0</v>
+      </c>
+      <c r="H68" t="str">
         <v/>
       </c>
     </row>
     <row r="69">
       <c r="A69">
+        <v>13425</v>
+      </c>
+      <c r="B69">
+        <v>858.01</v>
+      </c>
+      <c r="C69">
+        <v>774.97</v>
+      </c>
+      <c r="D69">
+        <v>858.01</v>
+      </c>
+      <c r="E69">
+        <v>641.16</v>
+      </c>
+      <c r="F69">
+        <v>9.67</v>
+      </c>
+      <c r="G69">
+        <v>3141.82</v>
+      </c>
+      <c r="H69" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v/>
+      </c>
+      <c r="B70" t="str">
+        <v/>
+      </c>
+      <c r="C70" t="str">
+        <v/>
+      </c>
+      <c r="D70" t="str">
+        <v/>
+      </c>
+      <c r="E70" t="str">
+        <v/>
+      </c>
+      <c r="F70" t="str">
+        <v/>
+      </c>
+      <c r="G70" t="str">
+        <v/>
+      </c>
+      <c r="H70" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>── untagged ──</v>
+      </c>
+      <c r="B71" t="str">
+        <v/>
+      </c>
+      <c r="C71" t="str">
+        <v/>
+      </c>
+      <c r="D71" t="str">
+        <v/>
+      </c>
+      <c r="E71" t="str">
+        <v/>
+      </c>
+      <c r="F71" t="str">
+        <v/>
+      </c>
+      <c r="G71" t="str">
+        <v/>
+      </c>
+      <c r="H71" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
         <v>-999999</v>
       </c>
-      <c r="B69">
+      <c r="B72">
         <v>17418.88</v>
       </c>
-      <c r="C69">
+      <c r="C72">
         <v>10907.25</v>
       </c>
-      <c r="D69">
+      <c r="D72">
         <v>25305.28</v>
       </c>
-      <c r="E69">
+      <c r="E72">
         <v>18026.83</v>
       </c>
-      <c r="F69">
+      <c r="F72">
         <v>15780.23</v>
       </c>
-      <c r="G69">
+      <c r="G72">
         <v>87438.47</v>
       </c>
-    </row>
-    <row r="70">
-      <c r="A70">
+      <c r="H72" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
         <v>99</v>
       </c>
-      <c r="B70">
+      <c r="B73">
         <v>1602756.97</v>
       </c>
-      <c r="C70">
+      <c r="C73">
         <v>1541979.87</v>
       </c>
-      <c r="D70">
+      <c r="D73">
         <v>1790892.59</v>
       </c>
-      <c r="E70">
+      <c r="E73">
         <v>1722310.47</v>
       </c>
-      <c r="F70">
+      <c r="F73">
         <v>1895178.54</v>
       </c>
-      <c r="G70">
+      <c r="G73">
         <v>8553118.44</v>
+      </c>
+      <c r="H73" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>123623963915635</v>
+      </c>
+      <c r="B74" t="str">
+        <v/>
+      </c>
+      <c r="C74" t="str">
+        <v/>
+      </c>
+      <c r="D74" t="str">
+        <v/>
+      </c>
+      <c r="E74" t="str">
+        <v/>
+      </c>
+      <c r="F74" t="str">
+        <v/>
+      </c>
+      <c r="G74">
+        <v>0</v>
+      </c>
+      <c r="H74" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>90000000000000000000</v>
+      </c>
+      <c r="B75" t="str">
+        <v/>
+      </c>
+      <c r="C75" t="str">
+        <v/>
+      </c>
+      <c r="D75" t="str">
+        <v/>
+      </c>
+      <c r="E75" t="str">
+        <v/>
+      </c>
+      <c r="F75" t="str">
+        <v/>
+      </c>
+      <c r="G75">
+        <v>0</v>
+      </c>
+      <c r="H75" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>untagged</v>
+      </c>
+      <c r="B76" t="str">
+        <v/>
+      </c>
+      <c r="C76" t="str">
+        <v/>
+      </c>
+      <c r="D76" t="str">
+        <v/>
+      </c>
+      <c r="E76" t="str">
+        <v/>
+      </c>
+      <c r="F76" t="str">
+        <v/>
+      </c>
+      <c r="G76">
+        <v>0</v>
+      </c>
+      <c r="H76" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G70"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H76"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G69"/>
+  <dimension ref="A1:H69"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="13.83203125" customWidth="1"/>
@@ -2041,6 +2408,7 @@
     <col min="5" max="5" width="13.83203125" customWidth="1"/>
     <col min="6" max="6" width="13.83203125" customWidth="1"/>
     <col min="7" max="7" width="13.83203125" customWidth="1"/>
+    <col min="8" max="8" width="55.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2065,6 +2433,9 @@
       <c r="G1" t="str">
         <v>total</v>
       </c>
+      <c r="H1" t="str">
+        <v>notes</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -2088,6 +2459,9 @@
       <c r="G2">
         <v>0</v>
       </c>
+      <c r="H2" t="str">
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -2111,6 +2485,9 @@
       <c r="G3">
         <v>0</v>
       </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -2134,6 +2511,9 @@
       <c r="G4">
         <v>62.45</v>
       </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -2157,6 +2537,9 @@
       <c r="G5">
         <v>367746.73</v>
       </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -2180,6 +2563,9 @@
       <c r="G6">
         <v>183.39</v>
       </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
@@ -2203,6 +2589,9 @@
       <c r="G7">
         <v>476.01</v>
       </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
@@ -2226,6 +2615,9 @@
       <c r="G8">
         <v>14506.79</v>
       </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
@@ -2249,6 +2641,9 @@
       <c r="G9">
         <v>443531.96</v>
       </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
@@ -2272,6 +2667,9 @@
       <c r="G10">
         <v>38223.42</v>
       </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
@@ -2295,6 +2693,9 @@
       <c r="G11">
         <v>66951.14</v>
       </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12">
@@ -2318,6 +2719,9 @@
       <c r="G12">
         <v>0</v>
       </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13">
@@ -2341,6 +2745,9 @@
       <c r="G13">
         <v>577794.63</v>
       </c>
+      <c r="H13" t="str">
+        <v>Subproxy holdings, no DR applied. Handled in Supply Side MSC.</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14">
@@ -2364,6 +2771,9 @@
       <c r="G14">
         <v>11597.75</v>
       </c>
+      <c r="H14" t="str">
+        <v>Spark untagged Savings, had boosted DR applied by Amatsu.</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15">
@@ -2387,6 +2797,9 @@
       <c r="G15">
         <v>5643549.22</v>
       </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16">
@@ -2410,6 +2823,9 @@
       <c r="G16">
         <v>4.12</v>
       </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17">
@@ -2433,6 +2849,9 @@
       <c r="G17">
         <v>12460.39</v>
       </c>
+      <c r="H17" t="str">
+        <v>Found in Spark datasets only, no onchain events.</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18">
@@ -2456,6 +2875,9 @@
       <c r="G18">
         <v>0</v>
       </c>
+      <c r="H18" t="str">
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19">
@@ -2479,6 +2901,9 @@
       <c r="G19">
         <v>0</v>
       </c>
+      <c r="H19" t="str">
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20">
@@ -2502,6 +2927,9 @@
       <c r="G20">
         <v>0.05</v>
       </c>
+      <c r="H20" t="str">
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21">
@@ -2525,6 +2953,9 @@
       <c r="G21">
         <v>67486.64</v>
       </c>
+      <c r="H21" t="str">
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22">
@@ -2548,6 +2979,9 @@
       <c r="G22">
         <v>4922.33</v>
       </c>
+      <c r="H22" t="str">
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23">
@@ -2571,6 +3005,9 @@
       <c r="G23">
         <v>36868.99</v>
       </c>
+      <c r="H23" t="str">
+        <v>Had boosted DR applied by Amatsu.</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24">
@@ -2594,6 +3031,9 @@
       <c r="G24">
         <v>25603.9</v>
       </c>
+      <c r="H24" t="str">
+        <v>Had boosted DR applied by Amatsu.</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25">
@@ -2617,6 +3057,9 @@
       <c r="G25">
         <v>52263.23</v>
       </c>
+      <c r="H25" t="str">
+        <v>Had boosted DR applied by Amatsu.</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26">
@@ -2640,6 +3083,9 @@
       <c r="G26">
         <v>84442.43</v>
       </c>
+      <c r="H26" t="str">
+        <v>Had boosted DR applied by Amatsu.</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27">
@@ -2663,6 +3109,9 @@
       <c r="G27">
         <v>9.04</v>
       </c>
+      <c r="H27" t="str">
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28">
@@ -2686,6 +3135,9 @@
       <c r="G28">
         <v>8499.05</v>
       </c>
+      <c r="H28" t="str">
+        <v>Had boosted DR applied by Amatsu.</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29">
@@ -2709,6 +3161,9 @@
       <c r="G29">
         <v>0.4</v>
       </c>
+      <c r="H29" t="str">
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30">
@@ -2732,6 +3187,9 @@
       <c r="G30">
         <v>37954.02</v>
       </c>
+      <c r="H30" t="str">
+        <v>stUSDS. Amatsu/BA applied DR in Jan./Feb. then switched to 0.1% after. s/b 0.1% always applied.</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31">
@@ -2755,6 +3213,9 @@
       <c r="G31">
         <v>0.1</v>
       </c>
+      <c r="H31" t="str">
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32">
@@ -2778,6 +3239,9 @@
       <c r="G32">
         <v>132.59</v>
       </c>
+      <c r="H32" t="str">
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33">
@@ -2801,6 +3265,9 @@
       <c r="G33">
         <v>177.01</v>
       </c>
+      <c r="H33" t="str">
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34">
@@ -2824,6 +3291,9 @@
       <c r="G34">
         <v>83.02</v>
       </c>
+      <c r="H34" t="str">
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35">
@@ -2847,6 +3317,9 @@
       <c r="G35">
         <v>0.64</v>
       </c>
+      <c r="H35" t="str">
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36">
@@ -2870,6 +3343,9 @@
       <c r="G36">
         <v>0</v>
       </c>
+      <c r="H36" t="str">
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37">
@@ -2893,6 +3369,9 @@
       <c r="G37">
         <v>0</v>
       </c>
+      <c r="H37" t="str">
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38">
@@ -2916,6 +3395,9 @@
       <c r="G38">
         <v>427.02</v>
       </c>
+      <c r="H38" t="str">
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39">
@@ -2939,6 +3421,9 @@
       <c r="G39">
         <v>14.26</v>
       </c>
+      <c r="H39" t="str">
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40">
@@ -2962,6 +3447,9 @@
       <c r="G40">
         <v>0</v>
       </c>
+      <c r="H40" t="str">
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41">
@@ -2985,6 +3473,9 @@
       <c r="G41">
         <v>4582.17</v>
       </c>
+      <c r="H41" t="str">
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42">
@@ -3008,6 +3499,9 @@
       <c r="G42">
         <v>0</v>
       </c>
+      <c r="H42" t="str">
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43">
@@ -3031,6 +3525,9 @@
       <c r="G43">
         <v>0</v>
       </c>
+      <c r="H43" t="str">
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="A44">
@@ -3054,6 +3551,9 @@
       <c r="G44">
         <v>7604.96</v>
       </c>
+      <c r="H44" t="str">
+        <v>Feb. and Mar. had no DR by Amatsu.</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45">
@@ -3077,6 +3577,9 @@
       <c r="G45">
         <v>96262.58</v>
       </c>
+      <c r="H45" t="str">
+        <v/>
+      </c>
     </row>
     <row r="46">
       <c r="A46">
@@ -3100,6 +3603,9 @@
       <c r="G46">
         <v>0.04</v>
       </c>
+      <c r="H46" t="str">
+        <v/>
+      </c>
     </row>
     <row r="47">
       <c r="A47">
@@ -3123,6 +3629,9 @@
       <c r="G47">
         <v>64561.56</v>
       </c>
+      <c r="H47" t="str">
+        <v/>
+      </c>
     </row>
     <row r="48">
       <c r="A48">
@@ -3146,6 +3655,9 @@
       <c r="G48">
         <v>0</v>
       </c>
+      <c r="H48" t="str">
+        <v/>
+      </c>
     </row>
     <row r="49">
       <c r="A49">
@@ -3169,6 +3681,9 @@
       <c r="G49">
         <v>1378.16</v>
       </c>
+      <c r="H49" t="str">
+        <v>Amatsu included DR for sUSDC, sUSDS, SKY, while onchain, only events for SKY can be found. unknown which balances or events to use for sUSDC and sUSDS.</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50">
@@ -3192,6 +3707,9 @@
       <c r="G50">
         <v>593.4</v>
       </c>
+      <c r="H50" t="str">
+        <v/>
+      </c>
     </row>
     <row r="51">
       <c r="A51">
@@ -3215,6 +3733,9 @@
       <c r="G51">
         <v>0</v>
       </c>
+      <c r="H51" t="str">
+        <v/>
+      </c>
     </row>
     <row r="52">
       <c r="A52">
@@ -3238,6 +3759,9 @@
       <c r="G52">
         <v>8550.23</v>
       </c>
+      <c r="H52" t="str">
+        <v/>
+      </c>
     </row>
     <row r="53">
       <c r="A53">
@@ -3261,6 +3785,9 @@
       <c r="G53">
         <v>291311.65</v>
       </c>
+      <c r="H53" t="str">
+        <v/>
+      </c>
     </row>
     <row r="54">
       <c r="A54">
@@ -3284,6 +3811,9 @@
       <c r="G54">
         <v>0</v>
       </c>
+      <c r="H54" t="str">
+        <v/>
+      </c>
     </row>
     <row r="55">
       <c r="A55">
@@ -3307,6 +3837,9 @@
       <c r="G55">
         <v>25404.85</v>
       </c>
+      <c r="H55" t="str">
+        <v/>
+      </c>
     </row>
     <row r="56">
       <c r="A56">
@@ -3330,6 +3863,9 @@
       <c r="G56">
         <v>12035.78</v>
       </c>
+      <c r="H56" t="str">
+        <v/>
+      </c>
     </row>
     <row r="57">
       <c r="A57">
@@ -3353,6 +3889,9 @@
       <c r="G57">
         <v>25.43</v>
       </c>
+      <c r="H57" t="str">
+        <v/>
+      </c>
     </row>
     <row r="58">
       <c r="A58">
@@ -3376,6 +3915,9 @@
       <c r="G58">
         <v>0</v>
       </c>
+      <c r="H58" t="str">
+        <v/>
+      </c>
     </row>
     <row r="59">
       <c r="A59">
@@ -3399,6 +3941,9 @@
       <c r="G59">
         <v>0</v>
       </c>
+      <c r="H59" t="str">
+        <v/>
+      </c>
     </row>
     <row r="60">
       <c r="A60">
@@ -3422,6 +3967,9 @@
       <c r="G60">
         <v>2.57</v>
       </c>
+      <c r="H60" t="str">
+        <v/>
+      </c>
     </row>
     <row r="61">
       <c r="A61">
@@ -3445,6 +3993,9 @@
       <c r="G61">
         <v>0.01</v>
       </c>
+      <c r="H61" t="str">
+        <v/>
+      </c>
     </row>
     <row r="62">
       <c r="A62">
@@ -3468,6 +4019,9 @@
       <c r="G62">
         <v>0</v>
       </c>
+      <c r="H62" t="str">
+        <v/>
+      </c>
     </row>
     <row r="63">
       <c r="A63">
@@ -3491,6 +4045,9 @@
       <c r="G63">
         <v>0</v>
       </c>
+      <c r="H63" t="str">
+        <v/>
+      </c>
     </row>
     <row r="64">
       <c r="A64">
@@ -3514,6 +4071,9 @@
       <c r="G64">
         <v>3141.82</v>
       </c>
+      <c r="H64" t="str">
+        <v/>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
@@ -3535,6 +4095,9 @@
         <v/>
       </c>
       <c r="G65" t="str">
+        <v/>
+      </c>
+      <c r="H65" t="str">
         <v/>
       </c>
     </row>
@@ -3560,6 +4123,9 @@
       <c r="G66" t="str">
         <v/>
       </c>
+      <c r="H66" t="str">
+        <v/>
+      </c>
     </row>
     <row r="67">
       <c r="A67">
@@ -3583,6 +4149,9 @@
       <c r="G67">
         <v>7260378.37</v>
       </c>
+      <c r="H67" t="str">
+        <v/>
+      </c>
     </row>
     <row r="68">
       <c r="A68">
@@ -3606,6 +4175,9 @@
       <c r="G68">
         <v>0.02</v>
       </c>
+      <c r="H68" t="str">
+        <v/>
+      </c>
     </row>
     <row r="69">
       <c r="A69">
@@ -3629,23 +4201,27 @@
       <c r="G69">
         <v>0.07</v>
       </c>
+      <c r="H69" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G69"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H69"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:F43"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="13.83203125" customWidth="1"/>
     <col min="3" max="3" width="13.83203125" customWidth="1"/>
     <col min="4" max="4" width="13.83203125" customWidth="1"/>
     <col min="5" max="5" width="13.83203125" customWidth="1"/>
+    <col min="6" max="6" width="55.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3664,6 +4240,9 @@
       <c r="E1" t="str">
         <v>total</v>
       </c>
+      <c r="F1" t="str">
+        <v>notes</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -3681,6 +4260,9 @@
       <c r="E2">
         <v>53206</v>
       </c>
+      <c r="F2" t="str">
+        <v>Spark untagged Savings, had boosted DR applied by Amatsu.</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3">
@@ -3698,6 +4280,9 @@
       <c r="E3">
         <v>3602072.3</v>
       </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4">
@@ -3715,6 +4300,9 @@
       <c r="E4">
         <v>4.4</v>
       </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5">
@@ -3732,6 +4320,9 @@
       <c r="E5">
         <v>0</v>
       </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6">
@@ -3749,6 +4340,9 @@
       <c r="E6">
         <v>0</v>
       </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7">
@@ -3766,6 +4360,9 @@
       <c r="E7">
         <v>0</v>
       </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8">
@@ -3783,6 +4380,9 @@
       <c r="E8">
         <v>45724.8</v>
       </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9">
@@ -3800,6 +4400,9 @@
       <c r="E9">
         <v>5624.6</v>
       </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10">
@@ -3817,6 +4420,9 @@
       <c r="E10">
         <v>18219.7</v>
       </c>
+      <c r="F10" t="str">
+        <v>Had boosted DR applied by Amatsu.</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11">
@@ -3834,6 +4440,9 @@
       <c r="E11">
         <v>48038.5</v>
       </c>
+      <c r="F11" t="str">
+        <v>Had boosted DR applied by Amatsu.</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12">
@@ -3851,6 +4460,9 @@
       <c r="E12">
         <v>39358</v>
       </c>
+      <c r="F12" t="str">
+        <v>Had boosted DR applied by Amatsu.</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13">
@@ -3868,6 +4480,9 @@
       <c r="E13">
         <v>146684.5</v>
       </c>
+      <c r="F13" t="str">
+        <v>Had boosted DR applied by Amatsu.</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14">
@@ -3885,6 +4500,9 @@
       <c r="E14">
         <v>14</v>
       </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15">
@@ -3902,6 +4520,9 @@
       <c r="E15">
         <v>13163</v>
       </c>
+      <c r="F15" t="str">
+        <v>Had boosted DR applied by Amatsu.</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16">
@@ -3919,6 +4540,9 @@
       <c r="E16">
         <v>0.5</v>
       </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17">
@@ -3936,6 +4560,9 @@
       <c r="E17">
         <v>70977.9</v>
       </c>
+      <c r="F17" t="str">
+        <v>stUSDS. Amatsu/BA applied DR in Jan./Feb. then switched to 0.1% after. s/b 0.1% always applied.</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18">
@@ -3953,6 +4580,9 @@
       <c r="E18">
         <v>0</v>
       </c>
+      <c r="F18" t="str">
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19">
@@ -3970,6 +4600,9 @@
       <c r="E19">
         <v>19.6</v>
       </c>
+      <c r="F19" t="str">
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20">
@@ -3987,6 +4620,9 @@
       <c r="E20">
         <v>243.8</v>
       </c>
+      <c r="F20" t="str">
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21">
@@ -4004,6 +4640,9 @@
       <c r="E21">
         <v>45.6</v>
       </c>
+      <c r="F21" t="str">
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22">
@@ -4021,6 +4660,9 @@
       <c r="E22">
         <v>0.5</v>
       </c>
+      <c r="F22" t="str">
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23">
@@ -4038,6 +4680,9 @@
       <c r="E23">
         <v>216.5</v>
       </c>
+      <c r="F23" t="str">
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24">
@@ -4055,6 +4700,9 @@
       <c r="E24">
         <v>0</v>
       </c>
+      <c r="F24" t="str">
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25">
@@ -4072,6 +4720,9 @@
       <c r="E25">
         <v>0</v>
       </c>
+      <c r="F25" t="str">
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26">
@@ -4089,6 +4740,9 @@
       <c r="E26">
         <v>0</v>
       </c>
+      <c r="F26" t="str">
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27">
@@ -4106,6 +4760,9 @@
       <c r="E27">
         <v>2255</v>
       </c>
+      <c r="F27" t="str">
+        <v>Feb. and Mar. had no DR by Amatsu.</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28">
@@ -4123,6 +4780,9 @@
       <c r="E28">
         <v>34121.3</v>
       </c>
+      <c r="F28" t="str">
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29">
@@ -4140,6 +4800,9 @@
       <c r="E29">
         <v>178305.2</v>
       </c>
+      <c r="F29" t="str">
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30">
@@ -4157,6 +4820,9 @@
       <c r="E30">
         <v>1024.6</v>
       </c>
+      <c r="F30" t="str">
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31">
@@ -4174,6 +4840,9 @@
       <c r="E31">
         <v>39681.5</v>
       </c>
+      <c r="F31" t="str">
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32">
@@ -4191,6 +4860,9 @@
       <c r="E32">
         <v>0</v>
       </c>
+      <c r="F32" t="str">
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33">
@@ -4208,6 +4880,9 @@
       <c r="E33">
         <v>12676.1</v>
       </c>
+      <c r="F33" t="str">
+        <v>Amatsu included DR for sUSDC, sUSDS, SKY, while onchain, only events for SKY can be found. unknown which balances or events to use for sUSDC and sUSDS.</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34">
@@ -4225,6 +4900,9 @@
       <c r="E34">
         <v>1256</v>
       </c>
+      <c r="F34" t="str">
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35">
@@ -4242,6 +4920,9 @@
       <c r="E35">
         <v>0</v>
       </c>
+      <c r="F35" t="str">
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36">
@@ -4259,6 +4940,9 @@
       <c r="E36">
         <v>0</v>
       </c>
+      <c r="F36" t="str">
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37">
@@ -4276,6 +4960,9 @@
       <c r="E37">
         <v>174513</v>
       </c>
+      <c r="F37" t="str">
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38">
@@ -4293,6 +4980,9 @@
       <c r="E38">
         <v>0</v>
       </c>
+      <c r="F38" t="str">
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39">
@@ -4310,6 +5000,9 @@
       <c r="E39">
         <v>17129.9</v>
       </c>
+      <c r="F39" t="str">
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40">
@@ -4327,6 +5020,9 @@
       <c r="E40">
         <v>0</v>
       </c>
+      <c r="F40" t="str">
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
@@ -4342,6 +5038,9 @@
         <v/>
       </c>
       <c r="E41" t="str">
+        <v/>
+      </c>
+      <c r="F41" t="str">
         <v/>
       </c>
     </row>
@@ -4361,6 +5060,9 @@
       <c r="E42" t="str">
         <v/>
       </c>
+      <c r="F42" t="str">
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
@@ -4378,10 +5080,13 @@
       <c r="E43">
         <v>4813357.6</v>
       </c>
+      <c r="F43" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E43"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F43"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -4551,7 +5256,7 @@
         <v>0 (USDS-CLE)</v>
       </c>
       <c r="B6" t="str">
-        <v>ours only</v>
+        <v>soter only</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -4572,7 +5277,7 @@
         <v>1786.39</v>
       </c>
       <c r="I6" t="str">
-        <v>Chronicle farm — not tracked by Spark.</v>
+        <v>Chronicle farm — not tracked by Spark/BA.</v>
       </c>
     </row>
     <row r="7">
@@ -4696,7 +5401,7 @@
         <v>1 (USDS-CLE)</v>
       </c>
       <c r="B11" t="str">
-        <v>ours only</v>
+        <v>soter only</v>
       </c>
       <c r="C11">
         <v>5139.57</v>
@@ -4717,7 +5422,7 @@
         <v>29341.39</v>
       </c>
       <c r="I11" t="str">
-        <v>Chronicle farm — not tracked by Spark.</v>
+        <v>Chronicle farm — not tracked by Spark/BA.</v>
       </c>
     </row>
     <row r="12">
@@ -4812,7 +5517,7 @@
         <v>10</v>
       </c>
       <c r="B15" t="str">
-        <v>ours only</v>
+        <v>soter only</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -4841,7 +5546,7 @@
         <v>100</v>
       </c>
       <c r="B16" t="str">
-        <v>ours only</v>
+        <v>soter only</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -4920,7 +5625,7 @@
         <v>-1575.56</v>
       </c>
       <c r="I18" t="str">
-        <v/>
+        <v>Spark untagged Savings, had boosted DR applied by Amatsu.</v>
       </c>
     </row>
     <row r="19">
@@ -5181,7 +5886,7 @@
         <v>-2893.69</v>
       </c>
       <c r="I27" t="str">
-        <v/>
+        <v>Had boosted DR applied by Amatsu.</v>
       </c>
     </row>
     <row r="28">
@@ -5210,7 +5915,7 @@
         <v>0</v>
       </c>
       <c r="I28" t="str">
-        <v/>
+        <v>Had boosted DR applied by Amatsu.</v>
       </c>
     </row>
     <row r="29">
@@ -5239,7 +5944,7 @@
         <v>0</v>
       </c>
       <c r="I29" t="str">
-        <v/>
+        <v>Had boosted DR applied by Amatsu.</v>
       </c>
     </row>
     <row r="30">
@@ -5268,7 +5973,7 @@
         <v>0</v>
       </c>
       <c r="I30" t="str">
-        <v/>
+        <v>Had boosted DR applied by Amatsu.</v>
       </c>
     </row>
     <row r="31">
@@ -5326,7 +6031,7 @@
         <v>0</v>
       </c>
       <c r="I32" t="str">
-        <v/>
+        <v>Had boosted DR applied by Amatsu.</v>
       </c>
     </row>
     <row r="33">
@@ -5384,7 +6089,7 @@
         <v>0</v>
       </c>
       <c r="I34" t="str">
-        <v/>
+        <v>stUSDS. Amatsu/BA applied DR in Jan./Feb. then switched to 0.1% after. s/b 0.1% always applied.</v>
       </c>
     </row>
     <row r="35">
@@ -5790,7 +6495,7 @@
         <v>253.28</v>
       </c>
       <c r="I48" t="str">
-        <v/>
+        <v>Feb. and Mar. had no DR by Amatsu.</v>
       </c>
     </row>
     <row r="49">
@@ -5935,7 +6640,7 @@
         <v>0</v>
       </c>
       <c r="I53" t="str">
-        <v/>
+        <v>Amatsu included DR for sUSDC, sUSDS, SKY, while onchain, only events for SKY can be found. unknown which balances or events to use for sUSDC and sUSDS.</v>
       </c>
     </row>
     <row r="54">
@@ -6436,7 +7141,7 @@
         <v>-999999</v>
       </c>
       <c r="B71" t="str">
-        <v>ours only</v>
+        <v>soter only</v>
       </c>
       <c r="C71">
         <v>17418.88</v>
@@ -6595,7 +7300,7 @@
         <v>0 (spUSDC)</v>
       </c>
       <c r="B2" t="str">
-        <v>ours only</v>
+        <v>soter only</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -6618,7 +7323,7 @@
         <v>0 (stUSDS)</v>
       </c>
       <c r="B3" t="str">
-        <v>ours only</v>
+        <v>soter only</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -6641,7 +7346,7 @@
         <v>0 (sUSDC)</v>
       </c>
       <c r="B4" t="str">
-        <v>ours only</v>
+        <v>soter only</v>
       </c>
       <c r="C4">
         <v>14.3</v>
@@ -6664,7 +7369,7 @@
         <v>0 (sUSDS)</v>
       </c>
       <c r="B5" t="str">
-        <v>ours only</v>
+        <v>soter only</v>
       </c>
       <c r="C5">
         <v>79746.04</v>
@@ -6687,7 +7392,7 @@
         <v>0 (USDS-CLE)</v>
       </c>
       <c r="B6" t="str">
-        <v>ours only</v>
+        <v>soter only</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -6702,7 +7407,7 @@
         <v>324.57</v>
       </c>
       <c r="G6" t="str">
-        <v>Chronicle farm — not tracked by Spark.</v>
+        <v>Chronicle farm — not tracked by Spark/BA.</v>
       </c>
     </row>
     <row r="7">
@@ -6710,7 +7415,7 @@
         <v>0 (USDS-SKY)</v>
       </c>
       <c r="B7" t="str">
-        <v>ours only</v>
+        <v>soter only</v>
       </c>
       <c r="C7">
         <v>93.87</v>
@@ -6733,7 +7438,7 @@
         <v>0 (USDS-SPK)</v>
       </c>
       <c r="B8" t="str">
-        <v>ours only</v>
+        <v>soter only</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -6756,7 +7461,7 @@
         <v>1 (stUSDS)</v>
       </c>
       <c r="B9" t="str">
-        <v>ours only</v>
+        <v>soter only</v>
       </c>
       <c r="C9">
         <v>1800.55</v>
@@ -6779,7 +7484,7 @@
         <v>1 (sUSDS)</v>
       </c>
       <c r="B10" t="str">
-        <v>ours only</v>
+        <v>soter only</v>
       </c>
       <c r="C10">
         <v>81433.39</v>
@@ -6802,7 +7507,7 @@
         <v>1 (USDS-CLE)</v>
       </c>
       <c r="B11" t="str">
-        <v>ours only</v>
+        <v>soter only</v>
       </c>
       <c r="C11">
         <v>5139.57</v>
@@ -6817,7 +7522,7 @@
         <v>15593.34</v>
       </c>
       <c r="G11" t="str">
-        <v>Chronicle farm — not tracked by Spark.</v>
+        <v>Chronicle farm — not tracked by Spark/BA.</v>
       </c>
     </row>
     <row r="12">
@@ -6825,7 +7530,7 @@
         <v>1 (USDS-SKY)</v>
       </c>
       <c r="B12" t="str">
-        <v>ours only</v>
+        <v>soter only</v>
       </c>
       <c r="C12">
         <v>26939.34</v>
@@ -6848,7 +7553,7 @@
         <v>1 (USDS-SPK)</v>
       </c>
       <c r="B13" t="str">
-        <v>ours only</v>
+        <v>soter only</v>
       </c>
       <c r="C13">
         <v>14315.55</v>
@@ -6871,7 +7576,7 @@
         <v>2</v>
       </c>
       <c r="B14" t="str">
-        <v>ours only</v>
+        <v>soter only</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -6894,7 +7599,7 @@
         <v>10</v>
       </c>
       <c r="B15" t="str">
-        <v>ours only</v>
+        <v>soter only</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -6917,7 +7622,7 @@
         <v>100</v>
       </c>
       <c r="B16" t="str">
-        <v>ours only</v>
+        <v>soter only</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -6955,7 +7660,7 @@
         <v>-45362.23</v>
       </c>
       <c r="G17" t="str">
-        <v/>
+        <v>Spark untagged Savings, had boosted DR applied by Amatsu.</v>
       </c>
     </row>
     <row r="18">
@@ -7139,7 +7844,7 @@
         <v>-10434.71</v>
       </c>
       <c r="G25" t="str">
-        <v/>
+        <v>Had boosted DR applied by Amatsu.</v>
       </c>
     </row>
     <row r="26">
@@ -7162,7 +7867,7 @@
         <v>-28087.56</v>
       </c>
       <c r="G26" t="str">
-        <v/>
+        <v>Had boosted DR applied by Amatsu.</v>
       </c>
     </row>
     <row r="27">
@@ -7185,7 +7890,7 @@
         <v>-22460.06</v>
       </c>
       <c r="G27" t="str">
-        <v/>
+        <v>Had boosted DR applied by Amatsu.</v>
       </c>
     </row>
     <row r="28">
@@ -7208,7 +7913,7 @@
         <v>-87916.08</v>
       </c>
       <c r="G28" t="str">
-        <v/>
+        <v>Had boosted DR applied by Amatsu.</v>
       </c>
     </row>
     <row r="29">
@@ -7254,7 +7959,7 @@
         <v>-7889.26</v>
       </c>
       <c r="G30" t="str">
-        <v/>
+        <v>Had boosted DR applied by Amatsu.</v>
       </c>
     </row>
     <row r="31">
@@ -7300,7 +8005,7 @@
         <v>-52262.69</v>
       </c>
       <c r="G32" t="str">
-        <v/>
+        <v>stUSDS. Amatsu/BA applied DR in Jan./Feb. then switched to 0.1% after. s/b 0.1% always applied.</v>
       </c>
     </row>
     <row r="33">
@@ -7423,7 +8128,7 @@
         <v>206</v>
       </c>
       <c r="B38" t="str">
-        <v>ours only</v>
+        <v>soter only</v>
       </c>
       <c r="C38">
         <v>0</v>
@@ -7446,7 +8151,7 @@
         <v>214</v>
       </c>
       <c r="B39" t="str">
-        <v>ours only</v>
+        <v>soter only</v>
       </c>
       <c r="C39">
         <v>0</v>
@@ -7515,7 +8220,7 @@
         <v>223</v>
       </c>
       <c r="B42" t="str">
-        <v>ours only</v>
+        <v>soter only</v>
       </c>
       <c r="C42">
         <v>0</v>
@@ -7538,7 +8243,7 @@
         <v>224</v>
       </c>
       <c r="B43" t="str">
-        <v>ours only</v>
+        <v>soter only</v>
       </c>
       <c r="C43">
         <v>0</v>
@@ -7622,7 +8327,7 @@
         <v>3256.73</v>
       </c>
       <c r="G46" t="str">
-        <v/>
+        <v>Feb. and Mar. had no DR by Amatsu.</v>
       </c>
     </row>
     <row r="47">
@@ -7760,7 +8465,7 @@
         <v>-11298.53</v>
       </c>
       <c r="G52" t="str">
-        <v/>
+        <v>Amatsu included DR for sUSDC, sUSDS, SKY, while onchain, only events for SKY can be found. unknown which balances or events to use for sUSDC and sUSDS.</v>
       </c>
     </row>
     <row r="53">
@@ -7906,7 +8611,7 @@
         <v>2008</v>
       </c>
       <c r="B59" t="str">
-        <v>ours only</v>
+        <v>soter only</v>
       </c>
       <c r="C59">
         <v>0</v>
@@ -7952,7 +8657,7 @@
         <v>3000</v>
       </c>
       <c r="B61" t="str">
-        <v>ours only</v>
+        <v>soter only</v>
       </c>
       <c r="C61">
         <v>0</v>
@@ -7975,7 +8680,7 @@
         <v>3001</v>
       </c>
       <c r="B62" t="str">
-        <v>ours only</v>
+        <v>soter only</v>
       </c>
       <c r="C62">
         <v>0</v>
@@ -7998,7 +8703,7 @@
         <v>3333</v>
       </c>
       <c r="B63" t="str">
-        <v>ours only</v>
+        <v>soter only</v>
       </c>
       <c r="C63">
         <v>0.71</v>
@@ -8021,7 +8726,7 @@
         <v>4011</v>
       </c>
       <c r="B64" t="str">
-        <v>ours only</v>
+        <v>soter only</v>
       </c>
       <c r="C64">
         <v>0</v>
@@ -8044,7 +8749,7 @@
         <v>4012</v>
       </c>
       <c r="B65" t="str">
-        <v>ours only</v>
+        <v>soter only</v>
       </c>
       <c r="C65">
         <v>0</v>
@@ -8067,7 +8772,7 @@
         <v>9998</v>
       </c>
       <c r="B66" t="str">
-        <v>ours only</v>
+        <v>soter only</v>
       </c>
       <c r="C66">
         <v>0</v>
@@ -8090,7 +8795,7 @@
         <v>13425</v>
       </c>
       <c r="B67" t="str">
-        <v>ours only</v>
+        <v>soter only</v>
       </c>
       <c r="C67">
         <v>858.01</v>
@@ -8516,7 +9221,7 @@
         <v>-44356.89</v>
       </c>
       <c r="G14" t="str">
-        <v/>
+        <v>Spark untagged Savings, had boosted DR applied by Amatsu.</v>
       </c>
     </row>
     <row r="15">
@@ -8723,7 +9428,7 @@
         <v>-7979.33</v>
       </c>
       <c r="G23" t="str">
-        <v/>
+        <v>Had boosted DR applied by Amatsu.</v>
       </c>
     </row>
     <row r="24">
@@ -8746,7 +9451,7 @@
         <v>-28087.56</v>
       </c>
       <c r="G24" t="str">
-        <v/>
+        <v>Had boosted DR applied by Amatsu.</v>
       </c>
     </row>
     <row r="25">
@@ -8769,7 +9474,7 @@
         <v>-22460.06</v>
       </c>
       <c r="G25" t="str">
-        <v/>
+        <v>Had boosted DR applied by Amatsu.</v>
       </c>
     </row>
     <row r="26">
@@ -8792,7 +9497,7 @@
         <v>-87916.08</v>
       </c>
       <c r="G26" t="str">
-        <v/>
+        <v>Had boosted DR applied by Amatsu.</v>
       </c>
     </row>
     <row r="27">
@@ -8838,7 +9543,7 @@
         <v>-7889.26</v>
       </c>
       <c r="G28" t="str">
-        <v/>
+        <v>Had boosted DR applied by Amatsu.</v>
       </c>
     </row>
     <row r="29">
@@ -8884,7 +9589,7 @@
         <v>-52262.69</v>
       </c>
       <c r="G30" t="str">
-        <v/>
+        <v>stUSDS. Amatsu/BA applied DR in Jan./Feb. then switched to 0.1% after. s/b 0.1% always applied.</v>
       </c>
     </row>
     <row r="31">
@@ -9206,7 +9911,7 @@
         <v>3089.33</v>
       </c>
       <c r="G44" t="str">
-        <v/>
+        <v>Feb. and Mar. had no DR by Amatsu.</v>
       </c>
     </row>
     <row r="45">
@@ -9344,7 +10049,7 @@
         <v>-11298.53</v>
       </c>
       <c r="G50" t="str">
-        <v/>
+        <v>Amatsu included DR for sUSDC, sUSDS, SKY, while onchain, only events for SKY can be found. unknown which balances or events to use for sUSDC and sUSDS.</v>
       </c>
     </row>
     <row r="51">
